--- a/exports/data_base_lancar_17-07-2026.xlsx
+++ b/exports/data_base_lancar_17-07-2026.xlsx
@@ -2370,17 +2370,17 @@
       <c r="FF3" s="14" t="n"/>
       <c r="FG3" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="FH3" t="inlineStr">
         <is>
-          <t>17/07/2026 18:05:52</t>
+          <t>17/07/2026 22:54:20</t>
         </is>
       </c>
       <c r="FI3" t="inlineStr">
         <is>
-          <t>Tela HTML preenchida, mas Confirmar evolucao ainda esta desabilitado.</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="FJ3" t="inlineStr">
@@ -2761,17 +2761,17 @@
       <c r="FF4" s="14" t="n"/>
       <c r="FG4" t="inlineStr">
         <is>
-          <t>ERRO</t>
+          <t>FINALIZADO</t>
         </is>
       </c>
       <c r="FH4" t="inlineStr">
         <is>
-          <t>17/07/2026 19:36:48</t>
+          <t>17/07/2026 22:57:34</t>
         </is>
       </c>
       <c r="FI4" t="inlineStr">
         <is>
-          <t>Paginas sem check verde: Dados da Internação, Parecer do Auditor</t>
+          <t>SUCESSO</t>
         </is>
       </c>
       <c r="FJ4" t="inlineStr">
@@ -3204,6 +3204,21 @@
       <c r="FD6" s="14" t="n"/>
       <c r="FE6" s="14" t="n"/>
       <c r="FF6" s="14" t="n"/>
+      <c r="FG6" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t>17/07/2026 21:34:26</t>
+        </is>
+      </c>
+      <c r="FI6" t="inlineStr">
+        <is>
+          <t>Evolução já concluída no Salus; bloqueado novo lançamento.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -3454,6 +3469,21 @@
       <c r="FD7" s="14" t="n"/>
       <c r="FE7" s="14" t="n"/>
       <c r="FF7" s="14" t="n"/>
+      <c r="FG7" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH7" t="inlineStr">
+        <is>
+          <t>17/07/2026 21:34:26</t>
+        </is>
+      </c>
+      <c r="FI7" t="inlineStr">
+        <is>
+          <t>Evolução já concluída no Salus; bloqueado novo lançamento.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -3850,6 +3880,21 @@
       <c r="FD8" s="14" t="n"/>
       <c r="FE8" s="14" t="n"/>
       <c r="FF8" s="14" t="n"/>
+      <c r="FG8" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH8" t="inlineStr">
+        <is>
+          <t>17/07/2026 21:34:26</t>
+        </is>
+      </c>
+      <c r="FI8" t="inlineStr">
+        <is>
+          <t>Evolução já concluída no Salus; bloqueado novo lançamento.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="32" t="inlineStr">
@@ -4097,6 +4142,21 @@
       <c r="FD9" s="14" t="n"/>
       <c r="FE9" s="14" t="n"/>
       <c r="FF9" s="14" t="n"/>
+      <c r="FG9" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="FH9" t="inlineStr">
+        <is>
+          <t>17/07/2026 21:32:35</t>
+        </is>
+      </c>
+      <c r="FI9" t="inlineStr">
+        <is>
+          <t>Aguardando revisão; pular no processamento automático.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -4295,6 +4355,21 @@
       <c r="FD10" s="14" t="n"/>
       <c r="FE10" s="14" t="n"/>
       <c r="FF10" s="14" t="n"/>
+      <c r="FG10" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH10" t="inlineStr">
+        <is>
+          <t>17/07/2026 22:58:15</t>
+        </is>
+      </c>
+      <c r="FI10" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -4687,6 +4762,21 @@
       <c r="FD11" s="14" t="n"/>
       <c r="FE11" s="14" t="n"/>
       <c r="FF11" s="14" t="n"/>
+      <c r="FG11" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH11" t="inlineStr">
+        <is>
+          <t>17/07/2026 21:48:17</t>
+        </is>
+      </c>
+      <c r="FI11" t="inlineStr">
+        <is>
+          <t>Finalizado manualmente pelo usuário no Salus.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -4918,6 +5008,21 @@
       <c r="FD12" s="14" t="n"/>
       <c r="FE12" s="14" t="n"/>
       <c r="FF12" s="14" t="n"/>
+      <c r="FG12" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH12" t="inlineStr">
+        <is>
+          <t>17/07/2026 22:36:48</t>
+        </is>
+      </c>
+      <c r="FI12" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -5365,6 +5470,21 @@
       <c r="FD13" s="14" t="n"/>
       <c r="FE13" s="14" t="n"/>
       <c r="FF13" s="14" t="n"/>
+      <c r="FG13" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="FH13" t="inlineStr">
+        <is>
+          <t>17/07/2026 22:59:36</t>
+        </is>
+      </c>
+      <c r="FI13" t="inlineStr">
+        <is>
+          <t>Página Conduta Clínica não ficou verde; lote interrompido neste paciente.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -5614,6 +5734,21 @@
       <c r="FD14" s="14" t="n"/>
       <c r="FE14" s="14" t="n"/>
       <c r="FF14" s="14" t="n"/>
+      <c r="FG14" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH14" t="inlineStr">
+        <is>
+          <t>17/07/2026 22:37:35</t>
+        </is>
+      </c>
+      <c r="FI14" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -5845,6 +5980,21 @@
       <c r="FD15" s="14" t="n"/>
       <c r="FE15" s="14" t="n"/>
       <c r="FF15" s="14" t="n"/>
+      <c r="FG15" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH15" t="inlineStr">
+        <is>
+          <t>17/07/2026 22:43:26</t>
+        </is>
+      </c>
+      <c r="FI15" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -6101,6 +6251,21 @@
       <c r="FD16" s="14" t="n"/>
       <c r="FE16" s="14" t="n"/>
       <c r="FF16" s="14" t="n"/>
+      <c r="FG16" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH16" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:00:15</t>
+        </is>
+      </c>
+      <c r="FI16" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="23" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -6309,6 +6474,21 @@
       <c r="FD17" s="14" t="n"/>
       <c r="FE17" s="14" t="n"/>
       <c r="FF17" s="14" t="n"/>
+      <c r="FG17" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="FH17" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:01:12</t>
+        </is>
+      </c>
+      <c r="FI17" t="inlineStr">
+        <is>
+          <t>Secao 100002 nao carregou a tela esperada (Exame Físico).</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -6526,6 +6706,21 @@
       <c r="FD18" s="14" t="n"/>
       <c r="FE18" s="14" t="n"/>
       <c r="FF18" s="14" t="n"/>
+      <c r="FG18" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH18" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:10:40</t>
+        </is>
+      </c>
+      <c r="FI18" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -6785,6 +6980,21 @@
       <c r="FD19" s="14" t="n"/>
       <c r="FE19" s="14" t="n"/>
       <c r="FF19" s="14" t="n"/>
+      <c r="FG19" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH19" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:11:27</t>
+        </is>
+      </c>
+      <c r="FI19" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -7008,6 +7218,21 @@
       <c r="FD20" s="14" t="n"/>
       <c r="FE20" s="14" t="n"/>
       <c r="FF20" s="14" t="n"/>
+      <c r="FG20" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH20" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:15:24</t>
+        </is>
+      </c>
+      <c r="FI20" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -7411,6 +7636,21 @@
       <c r="FD22" s="14" t="n"/>
       <c r="FE22" s="14" t="n"/>
       <c r="FF22" s="14" t="n"/>
+      <c r="FG22" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH22" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:17:43</t>
+        </is>
+      </c>
+      <c r="FI22" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="23" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -7637,6 +7877,21 @@
       <c r="FD23" s="14" t="n"/>
       <c r="FE23" s="14" t="n"/>
       <c r="FF23" s="14" t="n"/>
+      <c r="FG23" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH23" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:18:33</t>
+        </is>
+      </c>
+      <c r="FI23" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -8118,6 +8373,21 @@
       <c r="FD24" s="14" t="n"/>
       <c r="FE24" s="14" t="n"/>
       <c r="FF24" s="14" t="n"/>
+      <c r="FG24" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="FH24" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:19:46</t>
+        </is>
+      </c>
+      <c r="FI24" t="inlineStr">
+        <is>
+          <t>Página Conduta Clínica não ficou verde; lote interrompido neste paciente.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -8341,6 +8611,21 @@
       <c r="FD25" s="14" t="n"/>
       <c r="FE25" s="14" t="n"/>
       <c r="FF25" s="14" t="n"/>
+      <c r="FG25" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH25" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:20:36</t>
+        </is>
+      </c>
+      <c r="FI25" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23" customHeight="1">
       <c r="A26" s="32" t="inlineStr">
@@ -8535,6 +8820,21 @@
       <c r="FD26" s="14" t="n"/>
       <c r="FE26" s="14" t="n"/>
       <c r="FF26" s="14" t="n"/>
+      <c r="FG26" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH26" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:21:27</t>
+        </is>
+      </c>
+      <c r="FI26" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -8558,7 +8858,92 @@
       <c r="E27" s="8" t="n">
         <v>21722</v>
       </c>
-      <c r="F27" s="8" t="n"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Atual:
+Paciente interna com queixa de cansaço de inicio recente e alteração do habito intestinal.
+- Portador de Vitiligo há cerca de 15 anos &gt; gostaria de passar por avaliação dermatológica especializada.
+- Em uso de Mounjaro desde jul/25, com perda ponderal de 12kg (90-&gt;78kg) &gt; ultima dose há 12 dias.
+- Cervicalgia cronica e recentemente lombociatalgia. Em abr/26 teve crise de lombociatalgia, procurou avaliação ortopédica tendo sido prescrito diprospan&gt; Refere que evoluiu com complicação oftalmológica ao corticoide.
+Queixa-se de piora da acuidade visual devido a miopia e astgmatismo, porém tem acompanhado com oftalmologista de goias
+AP:
+- DLP/hipertrigliceridemia há cerca de 1 ano
+  &gt; LpA 110nmol/L (nov/25)
+- Hiperferritinemia -&gt; nunca fez sangria, controlava com doação de sangue
+- Nega HAS / DM
+- Vitiligo há cerca de 15 anos
+- Rinite/Sinusite crônica
+- Atividade fisica regular 2x/sem, há 5 anos
+- Nega tabagismo.
+- Ex-etilista social, cessou há cerca de 1 ano
+- Cirurgias: ortognática.
+- Neurite optica bilateral há cerca de 10 anos, com necessidade de pulsoterapia.
+- Nega demais internações
+- Alergia: Nimesulida
+- Covid-19 leve, tomou 2 doses vacina.
+AF:
+- Pai Vitiligo
+- Mãe DLP e hipertrigliceridemia
+- Nega IAM / Cardiopatia
+- Avó materna AVC ~65 anos
+- Nega CA / tromboses
+Em uso de:
+1) Plenance Eze 20/10mg Tomar 1 comp VO 1x ao dia
+Mounjaro 2,5mg/sem -&gt; ultima dose em 31/05/26.
+Whey protein e creatina
+VitD 5000ui 1xd
+Durateston IM 1ª dose há cerca de 90 dias
+Fez uso de Indux por cerca de 30 dias e suspendeu
+#Evolucao:
+Paciente segue estavel clinica e hemodinamicamente, sem queixas no momento.
+Tc de seios da face com pequena quantidade de secrecao bolhosa no seio esfenoidal E &gt; infoma ser cronico. Faz uso de avamys.
+USG de tireoide com nodulo tirads 5 de 0.8x0.6x0.4cm &gt; discutid com equipe da endocrino e indicado PAAF. Aguarda resultado.
+EDA com esofagite e gastrite e colono com polpo 2mm.
+Sem intercorrencias no periodo.
+#Ao exame:
+BEG, LOTE, corado, hidratado, AAA, eupneico
+AR: MVF S/ RA
+ACV: RCR 2t BNF s/ sopros
+Abdome flacido, indolor a palpação, RHA+
+Extremidades sem edemas, sem empastamento de panturrilhas, BPP
+Exames externos:
+USG abdome 19/02/26
+Cisto simples rim D 0,7x0,6cm
+Teste genetico genera 13/02/26 - Risco aumentado de:
+- CA tireoide: gene TERT
+- Doença de Crohn
+- Fibrilação atiral
+- Gota
+- Melanoma
+- DAC
+Bioimpedancia 29/01/26
+Peso 83,9
+Massa muscular 37,8
+Massa gordura 17,6
+Labs 12/11/25
+hb 14,3  leuco 6040  plaq 179000  ferro 82  sat transf 28  b12 514  homocist 16(vr&lt;15) ur 43  cr 1,18  mg 2,0  vitd 41  glic 86  hba1c 5,6  triglic 137  ct 202  hdl 42  ldl 135   ac uric 5,1  tgo 16  tgp 28  ggt 18  fa 67  LpA 110   insulina 6,3  tsh 0,93  shbg 39  testo 534  psa 0,44  cortisol 8,2 
+Labs 24/04/25
+hb 15,6  leuco 6090  plaq 194000  pcr 0,117  ferro 108  ferritina 858  sat transf 37%  homocist 14,6 (vr 3,7-13,9)  ur 33  cr 1,08  b12 583   k 5,3  sodio 153   mg 2,2  pth 29  vitd 25  glic 90  hba1c 5,6    triglic 265   ct 259  hdl 36   ldl 175  ac uric 5,2  LpA 91  tsh 1,13  t3l 3,0  t4l 1,15  prolact 9,8  shbg 24  acth 15,9   testo 390  igf1 175  psa 0,42  cortisol 8,57  insuluna 11,2   tgp 40  tgo 19  bt 0,43  fa 84  ggt 28 
+Bioimpedancia 04/04/25
+Peso 90
+Massa muscular 39
+Massa gordura 21,8
+TE 02/06/23
+Teste submaximo sem resposta isquemica durante o esforço
+Resposta inotropica fisiológica
+Sem arritmias
+Excelente apitidão cardiorrespiratoria
+ECOTT 02/06/23
+ao 34  ae 37   ve 47x30
+s 9  pp 9  feve 65%
+normal 
+#conduta:
+- Aguarda laudo de PAAF de nodulo tireoidiano
+- Aguarda AP de EDA e colono
+- Aval da Dra Cristina abdala - sugerido dermatoscopia no consultorio e aval geneticista, porem paciente nao deseja fazer neste momento.
+- Aval da equipe do Dr. Francisco Sampaio. ALTA DIA 21/06 06:60</t>
+        </is>
+      </c>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
@@ -8569,21 +8954,39 @@
       <c r="N27" s="9" t="n"/>
       <c r="O27" s="9" t="n"/>
       <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="9" t="n"/>
-      <c r="S27" s="10" t="n"/>
+      <c r="Q27" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="R27" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="10" t="n"/>
       <c r="Y27" s="10" t="n"/>
-      <c r="Z27" s="10" t="n"/>
+      <c r="Z27" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="10" t="n"/>
       <c r="AC27" s="10" t="n"/>
       <c r="AD27" s="10" t="n"/>
-      <c r="AE27" s="10" t="n"/>
+      <c r="AE27" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF27" s="10" t="n"/>
       <c r="AG27" s="10" t="n"/>
       <c r="AH27" s="10" t="n"/>
@@ -8611,7 +9014,9 @@
       <c r="BD27" s="11" t="n"/>
       <c r="BE27" s="11" t="n"/>
       <c r="BF27" s="11" t="n"/>
-      <c r="BG27" s="11" t="n"/>
+      <c r="BG27" s="11" t="n">
+        <v>1.08</v>
+      </c>
       <c r="BH27" s="11" t="n"/>
       <c r="BI27" s="11" t="n"/>
       <c r="BJ27" s="11" t="n"/>
@@ -8715,6 +9120,21 @@
       <c r="FD27" s="14" t="n"/>
       <c r="FE27" s="14" t="n"/>
       <c r="FF27" s="14" t="n"/>
+      <c r="FG27" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="FH27" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:22:33</t>
+        </is>
+      </c>
+      <c r="FI27" t="inlineStr">
+        <is>
+          <t>Página Dados da Internação não ficou verde; lote interrompido neste paciente.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="23" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -8738,7 +9158,37 @@
       <c r="E28" s="8" t="n">
         <v>22622</v>
       </c>
-      <c r="F28" s="8" t="n"/>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AP: DM, estenose subaortica operada, ITU em internação passada
+Evolução: paciente em leito de UI, acompanhada, refere não ter mais colicas, nauseas e fezes com consistência pastosa e com formação de bolo fecal.
+Ao exame clínico: BEG, hidratada, corada, acianotica, afebril, anictérica
+Consciente e orientada
+2BNFRSSA, PA: 140x80mmHg, FC: 82bpm
+MV + sem RA, eupneica em AA
+Abdome flacido, rha +, indolor à palpação profunda, DB -
+Extremidades sem edemas de MMII
+Conduta:
+- Alta hospitalar com orientações quanto ao término de tratamento (flagyl e magnen b6 em domicilio). Entrego e oriento receituário. Oriento manter medicações de uso habitual, além das que foram entregue em receituario hoje.
+- Oriento sinais de alarme e retorno ao PS s/n
+- Oriento seguimento clínico de carater ambulatorial. 
+Evolução: paciente em leito de UI, acompanhada da cuidadora, refere consistencia das fezes pastosas, enfermeira relatou que tem consistencia e pastosa.
+Ao exame clínico: REG, hidratada, corada, acianotica, afebril, anictérica
+Consciente e orientada
+2BNFRSSA
+MV + sem RA, eupneica em AA
+Abdome flacido, rha +, doloroso a palpação profunda, DB -
+Extremidades sem edemas de MMII
+Conduta:
+- Mantenho flagyl VO por ora
+- Vigilancia hematimetrica e infecciosa
+- Laboratoriais na rotina
+- Estimulo deambulação
+- Reduzo buscopam
+- Reponho magnesio - 1,1 hoje
+- Associo ondasertrona antes do flagyl da noite conforme solicitado. ALTA DIA 16/07 12:41 </t>
+        </is>
+      </c>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
@@ -8749,23 +9199,55 @@
       <c r="N28" s="9" t="n"/>
       <c r="O28" s="9" t="n"/>
       <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="9" t="n"/>
-      <c r="S28" s="10" t="n"/>
-      <c r="T28" s="10" t="n"/>
-      <c r="U28" s="10" t="n"/>
-      <c r="V28" s="10" t="n"/>
+      <c r="Q28" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="R28" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>REG – Regular Estado Geral</t>
+        </is>
+      </c>
+      <c r="T28" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="U28" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="V28" s="10" t="n">
+        <v>82</v>
+      </c>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="10" t="n"/>
       <c r="Y28" s="10" t="n"/>
-      <c r="Z28" s="10" t="n"/>
-      <c r="AA28" s="10" t="n"/>
+      <c r="Z28" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
+      <c r="AA28" s="10" t="inlineStr">
+        <is>
+          <t>Deambulando</t>
+        </is>
+      </c>
       <c r="AB28" s="10" t="n"/>
       <c r="AC28" s="10" t="n"/>
       <c r="AD28" s="10" t="n"/>
-      <c r="AE28" s="10" t="n"/>
+      <c r="AE28" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF28" s="10" t="n"/>
-      <c r="AG28" s="10" t="n"/>
+      <c r="AG28" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH28" s="10" t="n"/>
       <c r="AI28" s="10" t="n"/>
       <c r="AJ28" s="10" t="n"/>
@@ -8895,6 +9377,21 @@
       <c r="FD28" s="14" t="n"/>
       <c r="FE28" s="14" t="n"/>
       <c r="FF28" s="14" t="n"/>
+      <c r="FG28" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH28" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:23:23</t>
+        </is>
+      </c>
+      <c r="FI28" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -8918,7 +9415,58 @@
       <c r="E29" s="8" t="n">
         <v>23075</v>
       </c>
-      <c r="F29" s="8" t="n"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Primoinfecção CMV 
+-  Hepatite / Esplenomegalia / Linfonodomegalia 
+- Provável doença invasiva ( viremia &gt; 100mil + úlcera duodenal)
+09/07: PCR CMV - 209 UI/ml
+02/07: PCR CMV - 8.310 UI/ml
+27/06: PCR CMV - 24.900 UI/ml
+19/06: PCR CMV - 129.000 UI/ml
+# DRC agudizada: Cr basal em torno de 2,0
+Congestão pulmonar em manejo
+# ITU tratada
+- 28/06 URC E faecalis Ampi S 
+- Sem sinais clínicos ou radiológicos de pielonefrite 
+AP
+# DRPAD, Transplante renal com doador falecido 25/11/25
+# Neoplasia de prostata, 12/12/25 PO ressecção transuretral de prostata + retirada do duplo J
+#  Linfocitose monoclonal B subtipo indolente 
+Recebe: Valcyte 450mg 1x dia
+              ANTES Ganciclovir 2,5mg/kg/dia ( In 20/06- 11/07)
+              GCSF em 13/07
+Prévio: Ampicilina 30/06-08/07
+ISS: Prednisona 5mg/dia + Tacrolimo 3-0-3
+Controles: Afebril
+PA e FC estáveis
+Diurese: presente, não quantificada
+Evacuação: 2x
+Bem clinicamente, sem queixas
+Ao exame físico: BEG, corado, hidratado
+Oroscopia sem lesoes
+ MV+ sem RA
+RCR 2T BNF ss aparentes
+Abdome normotenso, doloroso à palpação profunda de região epigastrica, RHA+
+MMII sem edemas. Panturrilhas livres
+Lab: Sem rotina de lab hoje 
+09/07: PCR CMV - 209 UI/ml
+02/07: PCR CMV - 8.310 UI/ml
+28/06: URC E. faecalis multi S
+27/06: PCR CMV - 24.900 UI/ml
+19/06: PCR CMV - 129.000 UI/ml
+17/06: URC neg
+09/06: URC neg
+26/05: URC E. faecalis multi S
+07/05: URC E. faecalis multi S
+Imagem: 
+09/07 - EDA: mucosa antral possui erosões planas em moderada quantidade. Na região do corpo vemos alguns pólipo sésseis, de superfície irregular, variando entre 2 a 8 mm de diâmetro. O bulbo duodenal tem a sua anatomia preservada, distensibilidade adequada e superfície mucosa com cicatriz de úlcera na face anterior justa-pilórica. 
+02/07: TC abdome - bexiga com moderada repleção, com alterações inflamatórias caracterizadas previamente por espessamento da parede vesical e densificação da gordura adjacente. Novo aumento das dimensões do baço (índice esplênico de 996; era 636; normal até 480). Fígado com dimensões aumentadas, contornos regulares e atenuação preservada. Formações hepáticas hipoatenuantes esparsas, subcentimétricas, inespecíficas, prováveis cistos. Linfonodomegalias no tronco celíaco / hilo hepático, paraórticas e ilíacas bilaterais, medindo até 4,1 x 3,3 cm.
+]02/07: TC tórax - aumento das dimensões das linfonodomegalias torácicas, indeterminadas. Surgiram discretas opacidades em vidro fosco esparsas no lobo inferior direito, inespecíficas, que podem ter natureza inflamatória incipiente ou em resolução. Surgiram alguns micronódulos pulmonares não calcificados menores que 0,3 cm, inespecíficos. 
+CD: Alta hospitalar pela infectologia com retorno breve no consultório. ALTA DIA 15/07 13:26
+Orientações</t>
+        </is>
+      </c>
       <c r="G29" s="9" t="n"/>
       <c r="H29" s="9" t="n"/>
       <c r="I29" s="9" t="n"/>
@@ -8929,9 +9477,19 @@
       <c r="N29" s="9" t="n"/>
       <c r="O29" s="9" t="n"/>
       <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="9" t="n"/>
-      <c r="S29" s="10" t="n"/>
+      <c r="Q29" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="R29" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T29" s="10" t="n"/>
       <c r="U29" s="10" t="n"/>
       <c r="V29" s="10" t="n"/>
@@ -9075,6 +9633,21 @@
       <c r="FD29" s="14" t="n"/>
       <c r="FE29" s="14" t="n"/>
       <c r="FF29" s="14" t="n"/>
+      <c r="FG29" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH29" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:24:14</t>
+        </is>
+      </c>
+      <c r="FI29" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -9098,7 +9671,42 @@
       <c r="E30" s="8" t="n">
         <v>23101</v>
       </c>
-      <c r="F30" s="8" t="n"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+HPMA: Ha 3 dias sintomas gripais leves ha 1 dia piora do padrão respiratórios e taquicardia além de febre, encaminhado do consultório para exames e avaliação
+Recebe:
+Dieta oral geral 
+Soro 70/100
+Zinnat 12/12h DI:24/06      (Recebeu Ceftriaxona  DI: 21/06-24/06)
+Aerolin Spray 100mcg/dos 4 Puffs 4/4h 
+Luftal 75mg/mL gotas: 10 gts 6/6h
+Soro fisiológico 0,9%: 5 ml Nasal de 6 em 6 horas
+Controles:
+PA: 96x53 - 114x44 (67 - 84) mmHg FC: 121 - 129 bpm Tx: 36,1 - 36,2 ºC FR: 29 - 42 irpm Glicemia: sem registro Dor: 0, 0, 0 SatO2: 92 - 98 %
+Culturas e pesquisas virais:
+Painel viral 19/06: Rinovirus e VSR positivos
+Influenza A neg B negativo 
+ Cultura de urina  negativo
+Exames laboratóriais:
+18/06/2026 HSL — Gli 103 | Na 141 K 4,6 | CT 0,22 (BD 0,09 BI 0,13) | Hb 11,9 Ht 34,5 | Leuco 13790 Neutro 7626 Linf 4964 Mono 1034 Eos 138 Baso 28 | Plaq 305000 | U 14 Creat 0,22 | TGO 34 TGP 15 GGT 15 | CaT 10,9 CaI 1,48 | PCR 17,7 | Fibrinogênio 616 | Lactato 13,6 | Troponina 12,6 | TP 12,3 INR 1,07 | TTPA 29,2 Relação 0,97 | 
+Urina 1 alterada: proteínas 0,75, corpos cetônicos 150, cristais de oxalato de cálcio frequentes 
+19/06/2026 Hb 11,1 HT 33 Leucocitos 14660 (48%seg - 0,3%eo - 0,3%baso - 45%linf - 6,4% mono) Plaquetas 248mil CaT 10,4 CaI 1,36 Cloro 102 Troponina 6,99 MG 2,2 PCR 15,30 K 4,2 Na 135
+Exame de imagem:
+Ecocardiograma (20/06): dentro da normalidade 
+Exame fisico:
+REG, corado, hidratado, acianotico, anicterico, afebril ao toque, ativo e reativo
+MV presente bilateralmentem sibilos raros e TSD discreto
+BRNF em 2 tempo sem sopro, TEC &lt;2", pulsos presentes
+Abdome plano, RHA presente, indolor a palpação superficial e profunda, DB negativo
+Otoscopia a direita hiperemia e abaulado 
+Conduta:
+- Precisou de oxigenio durante a noite - alta breve 
+- Esta sem oxigenio e bom padrão respiratório durante o dia. Observar necessidade de oxigenio
+Resuma estes dados, ALTA DIA 26/06 17:35 
+</t>
+        </is>
+      </c>
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
@@ -9109,14 +9717,34 @@
       <c r="N30" s="9" t="n"/>
       <c r="O30" s="9" t="n"/>
       <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="9" t="n"/>
-      <c r="S30" s="10" t="n"/>
-      <c r="T30" s="10" t="n"/>
-      <c r="U30" s="10" t="n"/>
-      <c r="V30" s="10" t="n"/>
-      <c r="W30" s="10" t="n"/>
-      <c r="X30" s="10" t="n"/>
+      <c r="Q30" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>REG – Regular Estado Geral</t>
+        </is>
+      </c>
+      <c r="T30" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="U30" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="V30" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="W30" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="X30" s="10" t="n">
+        <v>92</v>
+      </c>
       <c r="Y30" s="10" t="n"/>
       <c r="Z30" s="10" t="n"/>
       <c r="AA30" s="10" t="n"/>
@@ -9151,7 +9779,9 @@
       <c r="BD30" s="11" t="n"/>
       <c r="BE30" s="11" t="n"/>
       <c r="BF30" s="11" t="n"/>
-      <c r="BG30" s="11" t="n"/>
+      <c r="BG30" s="11" t="n">
+        <v>0.22</v>
+      </c>
       <c r="BH30" s="11" t="n"/>
       <c r="BI30" s="11" t="n"/>
       <c r="BJ30" s="11" t="n"/>
@@ -9255,6 +9885,21 @@
       <c r="FD30" s="14" t="n"/>
       <c r="FE30" s="14" t="n"/>
       <c r="FF30" s="14" t="n"/>
+      <c r="FG30" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH30" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:25:04</t>
+        </is>
+      </c>
+      <c r="FI30" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -9278,7 +9923,93 @@
       <c r="E31" s="8" t="n">
         <v>24559</v>
       </c>
-      <c r="F31" s="8" t="n"/>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Paciente com adenocarcinoma intestinal com metástases hepáticas, sob quimioterapia, estando no momento no 4 ciclo.
+Teve como complicações do tratamento antineoplásico, necrose da parede intestinal após o primeiro ciclo, que culminou com retirada da alça intestinal afetada. Na segunda e terceira pós QT teve mucosite oral importante, melhor com laser.
+Teve também, confusão mental por uma série de eventos isquemicos cerebrais, tratado com anticoagulação plena, com melhora.
+No momento, 5 dia após o termino da ultima QT, cpom mucosite discreta, melhor com laser
+Por dor abdominal fez tomo sendo constatado calculo renal. Conduta espectante!
+Anticoagulado pleno com Clexane
+Paciente hoje muito deprimido, com intensão de parar o tratamento, e ir para casa
+Refere dores abdominais e sangramento após pequenas punções
+Muito graveHMA: Paciente acompanhado por familiares que referem que no dia 21/06, por volta das 10h da manhã, após retornar de caminhada, referiu mal estar inespecífico associado a confusão mental. Refere manutenção da queixa ao longo do dia, evoluindo com sonolência excessiva desde então. Realizou QT há 3 dias para tratamento de CA de intestino (Bevacizumabe + FOLFOXIRI com redução de irinotecano e sem bolus de 5FU). Nega sintomas gripais, febre.
+AP:
+Adenocarcinoma indiferenciado metastático para fígado NTRK-/HER-/Enzimas de reparo preservadas
+Trombose de veia hepática/cava
+PO 13/05 Perfuração intestinal aguda - colectomia + ileostomia
+TEP bilateral sem piora parâmetros ventilatórios - achado de TC abdome de 25/05/26
+Meds em ajuste:
+-Levetiracetam 500mg 2xd (23/06)
+-HNF em BIC (24/06) &gt; Enoxaparina 60mg 12x12h &gt; 60mg - 80 mg
+-Lexapro 5mg (29/06) &gt; 10mg 1xd (06/07)
+NS LVT 05/07 - 11.6
+ATB:
+Meropenem 1g 8/8h (D0 11/07)
+Tazocin 4,5g 6/6h (D0 22/06 - 01/07)
+EVOLUÇÃO:
+Paciente no leito, acomp. pela mãe.
+Persiste com dificuldade para dormir. Pensamento deprimido, fala sobre querer morrer e não mais utilizar quimioterapia.
+Recebe NPP, mas em programação de desmame. Teve uma melhor aceitação da dieta VO.
+Por mucosite oral, faz fotobiomodulação terapeutica, bem como outros cuidados prescritos pela Odontologia.
+Diurese espontânea. Evacuação por ileostomia presente em 16/07.
+Últimos exames laboratoriais demonstraram persistência de disfunção hepática, anemia com plaquetopenia e DHE (mas comparativamente estáveis).
+Avaliaçao Clínica Médica e Urologia (14/07): conversado com Dr Gromatsky - Nefrolitíase com cálculo em JUV D 4 mm e moderada dilatação do sistema coletor a montante. Por ora mantida conduta conservadora. Urocultura de 11/07 fechou negativa. Hemocultura de 11/07 segue parcial negativa. Procalcitonina 2,24 em 11/07. Início de meropenem em 11/07, manutenção de anticoagulação plena. 
+- TC de crânio 10/07 - alterações evolutivas, redução de edema, sem novos eventos.
+ -TC de crânio (30/06): discreta redução de edema.
+-DTC 28/06: recanalização parcial de segmento distal M2 E / sem alterações de fluxo em supino
+-TC de cranio(23/06): não evidencia alterações evolutivas significativas. Observam-se hipoatenuações lineares nos hemisférios cerebelares, que podem ou não ter etiologia artefatual.
+-TC de cranio(24/06): nova area isquemica em territorio de divisao inferior de ACM E e ACP E. Oclusão M2 distal esquerda e P2/3 esquerda.
+-TC de cranio(25/06): estavel em relação ao exame de 24/06
+-RM de crânio(23/05): Múltiplos focos de alteração de sinal com restrição á difusão em territórios de fronteira. Destaca-se o comprometimento da transição parieto-occipital à direita
+-RM de crânio + AngioRM(25/05): Sem areas adicionais isquemicas em comparação com TC do dia 25 - nova area isquemica em territorio de divisao inferior de ACM E e ACP E; Angio Venosa sem alterações. Angio arterial com oclusão M2 distal e P2/P3 esq
+-TC de tórax: aumento derrame pleural a direita.
+-AngioTCs arterial e venosa normais, porém demonstraram hipoatenuação subcortical e córtico-subcortical parietal e peritrigonal à direita, de aspecto inespecífico
+-EEG: Desorganização difusa; registro de ocasionais surtos de ondas lentas, na faixa delta, irregulares, de projeção nas regiões anteriores, bilaterais, com predomínio à esquerda.
+-ECO TT: NDN
+-DTC: reserva vascular preservada, sem embolização espontanea
+-Holter 24h(23/06): Ritmo de base sinusal, ectopia ventricular e supraventricular rara, ausência de correlação sintoma-eletrocardiográfico
+Ao exame neurológico:
+Vigil, parcialmente orientado em tempo e espaço (porém troca palavras, possivelmente errando orientação por afasia), afasia mista predominio compreensão, atenção basica preservada.
+Força grau V global, sensibilidade superficial preservada
+Marcha sem alterações, coordenação apendicular de difícil avaliação por confusão
+PIFR, MOE preservada, mímica facial sem alterações, hemianóptico à D.
+Ausência de sinais meníngeos
+Impressão: Paciente com antecedente de neoplasia colorretal evoluindo com quadro de encefalopatia associado a afasia e múltiplos focos isquêmicos corticais e em território de ACM E/ACP E com sinal dos três territórios - Trombofilia paraneoplásica? Relacionado a Bevacizumabe ?
+Condutas - Discutida com Dr. Rogério Tuma:
+- Por dificuldade em adormecer, prescrevemos mirtazapina 7,5 mg à noite (16/07).
+- Por queixa de dor atual, solicito que seja realizado resgate com dipirona e, se não melhorar, morfina.
+- Já em seguimento medicina bucal por provável mucosite + analgesia simples de horário + resgate de morfina SOS.
+ - Mantenho LVT IV em decorrência de náuseas, transicionaremos para VO quando melhor controle sintomático.
+- Quando optado por transição anticoagulação oral, ponderar inicialmente uso de Marevan devido a maior facilidade de reversão se necessário.
+ - Ajustada dose de lexapro 10mg (vigilância função hepática) (06/07).
+- Autorizado mobilização no leito, sentar em poltrona e ir ao banheiro em cadeira de rodas - evitar hipo ou hipertensão. 
+- Reabilitação fisio e fono linguagem. Seguimento Psico.
+- Seguimento Onco, Hemato, CM.
+- Explico programação para familiares, cientes e concordantes. 
+**Em discussão com equipe de hemodinâmica(Dr Fausto e Dr Igor), tendo em vista vaso distal(M2), íctus &gt;12h, plaquetopenia importante(por volta de 30.000) e delimitação de área isquêmica, optado por contraindicar procedimento de trombectomia mecânica tendo em vista risco de transformação hemorrágica e maior deterioração do quadro neurológico - explico condutas a familiar jacy, sem conflitos(24/06/26)
+EXAMES:
+**TC crânio controle 10/07:
+Análise comparativa com exame de 30 de junho de 2026 que mostra: Significativa redução das hipodensidades parenquimatosas no opérculo têmporo-occipital esquerdo, com melhor demarcação córtico subcortical, de sulcos corticais e desaparecimento do efeito de massa com reexpansão do corno posterior do ventrículo lateral correspondente.
+** TC de crânio (30/06): Análise em relação a exame anterior de 25 de junho de 2026 que mostra: Hipoatenuação córtico-subcortical têmporo-parieto-occipital esquerda, correspondendo a parte do território de divisão inferior da artéria cerebral média esquerda e parte do território da artéria cerebral posterior esquerda compatível com lesão isquêmica recente. Há discreto apagamento dos sulcos corticais regionais. Não foram identificados focos hemáticos. Tênue hipoatenuação subcortical e corticossubcortical do lóbulo parietal inferior / transição parietoccipital à direita, sem evidente efeito expansivo, compatível com insulto isquêmico em fase de evolução subaguda. Tênues focos hipodensos esparsos nos centros semiovais / coroas radiadas bilaterais, em correlação com ressonância magnética do crânio de 25 de junho de 2026, também representando focos de isquemia recente. Sistema ventricular de morfologia e dimensões conservadas. Demais sulcos corticais e cisternas basais com aspecto preservado. Restante do parênquima encefálico com morfologia e atenuação normais. Não há sinais de hemorragia intracraniana recente nem de coleções extra-axiais. * Comparativamente ao de 25 de junho de 2026 nota-se discreta redução do efeito expansivo relacionada a extensa área de insulto isquêmico recente no hemisfério cerebral esquerdo com discreta ampliação de sulcos corticais. Demais aspectos inalterados.
+** EEG: 1. Desorganização difusa da atividade elétrica cerebral, com predomínio na região temporal esquerda; 2. Registro de ocasionais surtos de ondas lentas, na faixa delta, irregulares, de projeção nas regiões anteriores, bilaterais, com predomínio à esquerda
+** RM de crânio: Múltiplos focos de alteração de sinal com restrição á difusão distribuídos nos hemisférios cerebrais, predominando em localização corticossubcortical / justacortical, compatíveis com insultos isquêmicos recentes em territórios de fronteira. Destaca-se o comprometimento do lóbulo parietal inferior / transição parieto-occipital à direita, onde se observa apagamento dos espaços liquóricos, além de realce ao meio de contraste, indicando fase de evolução subaguda. Não se observam sinais de sangramento intracraniano. Sistema ventricular de aspecto, dimensões e sinal normais. Demais sulcos corticais e fissuras encefálicas com amplitude de aspecto normal. Restante do parênquima encefálico de morfologia e características de sinal conservadas.
+** Angiotomografia arterial intracraniana: sem alterações significativas. As imagens dirigidas ao encéfalo demonstraram hipoatenuação subcortical e córtico-subcortical parietal e peritrigonal à direita, de aspecto inespecífico, sem evidente efeito expansivo. A critério clínico, o estudo de ressonância magnética pode trazer informações adicionais.
+** Angiotomografia venosa intracraniana: Não há evidência de trombose venosa recente.
+**ECO TT(23/06): FE 68%/AE 28/Refluxo discreto da valva tricúspide. Função sistólica biventricular preservada.
+**DTC(23/06):Sem evidência de embolização encefálica arterio-arterial. Múltiplos focos sugestivos de insultos isquêmicos nos hemisférios cerebrais, corticossubcortical / justacortical, principalmente em territórios de fronteira Ausência de estenose crítica, oclusão e hipofluxo cerebrovascular como mecanismos de isquemia encefálica. Paciente em tratamento oncológico evolui com insultos isquêmicos nos hemisférios cerebrais, corticossubcorticais e justacorticais, principalmente em territórios de fronteira. Breath Holding Index: 0,70 na artéria cerebral média direita. Breath Holding Index: 0,68 na artéria cerebral média esquerda. Breath Holding Index: 0,69 na artéria basilar. Pressão arterial: 115 / 80 mmHg; frequência cardíaca: 100 bpm. Observações Reserva microvascular encefálica preservada Ausência de baixa reserva cerebrovascular como mecanismo de isquemia encefálica. Paciente em tratamento oncológico evolui com insultos isquêmicos nos hemisférios cerebrais, corticossubcortical / justacortical, principalmente em territórios de fronteira.
+**TC de cranio + AngioTC(24/06): Hipoatenuação córtico-subcortical têmporo-parieto-occipital esquerda, correspondendo a parte do território de divisão inferior da artéria cerebral média esquerda e parte do território da artéria cerebral posterior esquerda pela compatível com lesão isquêmica recente. Há discreto apagamento dos sulcos corticais regionais. Não foram identificados focos hemáticos. Hipoatenuação subcortical e corticossubcortical do lóbulo parietal inferior / transição parietoccipital à direita, sem evidente efeito expansivo, com discreto realce cortical pós-contraste, compatível com insulto isquêmico em fase de evolução subaguda. Oclusão segmentar de ramo M2 da artéria cerebral média esquerda, com reenchimento distal, discretamente tardio em relação ao restante do sistema arterial. Oclusão focal segmentar na transição P2-P3 da artéria cerebral posterior esquerda e outra oclusão em segmento P3 da mesma artéria.
+**TC de cranio(25/06): Comparativamente ao de 24 de junho de 2026 não se observam alterações evolutivas significativas, consideradas as diferenças técnicas.
+**RM de crânio + AngioRM: Área de restrição a difusão com alto sinal no T2/FLAIR córtico-subcortical têmporo-parieto-occipital esquerda, correspondendo a parte do território de divisão inferior da artéria cerebral média esquerda e parte do território da artéria cerebral posterior esquerda compatível com lesão isquêmica recente. Há discreto apagamento dos sulcos corticais regionais e compressão sobre o corno posterior do ventrículo lateral deste lado.Múltiplos focos de alteração de sinal com restrição á difusão distribuídos nos hemisférios cerebrais, predominando em localização corticossubcortical / justacortical, compatíveis com insultos isquêmicos recentes em territórios de fronteira.Destaca-se o comprometimento do lóbulo parietal inferior / transição parieto-occipital à direita, onde se observa apagamento dos espaços liquóricos, além de realce ao meio de contraste, indicando fase de evolução subaguda.
+Não se observam sinais de sangramento intracraniano.Restante do sistema ventricular de aspecto, dimensões e sinal normais.Demais sulcos corticais e fissuras encefálicas com amplitude de aspecto normal.Restante do parênquima encefálico de morfologia e características de sinal conservadas.
+Oclusão segmentar de ramo M2 da artéria cerebral média esquerda, ramo inferior da divisão inferior, iniciando cerca de 0,2 cm após a bifurcação e com extensão de cerca de 1 cm, com reenchimento arterial distal, discretamente tardio em relação ao restante do sistema arterial.Oclusão focal segmentar na transição P2-P3 da artéria cerebral posterior esquerda com fluxo lento / redução do sinal de fluxo dos ramos distais.Demais segmentos das artérias cerebrais anteriores, artérias cerebrais médias, artéria basilar e artérias cerebrais posteriores de trajeto, calibre e fluxo preservados.
+**DTC: Hemodinâmica encefálica evidencia assimetria de velocidades médias de fluxo sanguíneo em artérias cerebrais médias, com valores menores em porção distal (M2) à esquerda, indicando recanalização com algum grau de estreitamento luminal, sem determinar hipofluxo (Vm ACME M2: 41 cm/s; M1 ACME: 51 cm/s e ACMD: 57 cm/s). Sem sinais de acometimento de pequenas artérias encefálicas. Índice de pulsatilidade varia entre 0,8 a 1,0 (VR &lt; 1,2). Sem sinais sugestivos de estenoses críticas em porções proximais das artérias do Polígono de Willis. Fluxo anterógrado em todos os segmentos analisados. Pressão arterial: 123 / 86 mmHg; frequência cardíaca: 108 bpm. Observações: Assimetria de fluxo em porção distal (M2) de artéria cerebral média esquerda, que pode estar relacionada à recanalização parcial de segmento distal, sem evidência de hipofluxo.
+Sem sinais sugestivos de comprometimento da autorregulação do fluxo sanguíneo encefálico. O teste de apneia voluntária (Breath Holding Test) não foi realizado por falta de compreensão do paciente, não sendo possível avaliar a vasorreatividade ao CO2, contudo, paciente sem sinais de estenoses críticas intracranianas e sem hipofluxo cerebral, mesmo em segmento distal de artéria cerebral média esquerda.
+Sem sinais sugestivos de comprometimento da autorregulação do fluxo sanguíneo encefálico. O teste de apneia voluntária (Breath Holding Test) não foi realizado por falta de compreensão do paciente, não sendo possível avaliar a vasorreatividade ao CO2, contudo, paciente sem sinais de estenoses críticas intracranianas e sem hipofluxo cerebral, mesmo em segmento distal de artéria cerebral média esquerda.
+Sistema vertebrobasilar intracraniano pérvio, incluindo as artérias cerebrais posteriores, sem sinais de estenose crítica ou hipofluxo. Ausência de insuficiência vertebrobasilar como fator de isquemia encefálica.
+Sem evidência de embolização encefálica arterio-arterial</t>
+        </is>
+      </c>
       <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
@@ -9289,12 +10020,20 @@
       <c r="N31" s="9" t="n"/>
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="9" t="n"/>
+      <c r="Q31" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S31" s="10" t="n"/>
       <c r="T31" s="10" t="n"/>
       <c r="U31" s="10" t="n"/>
-      <c r="V31" s="10" t="n"/>
+      <c r="V31" s="10" t="n">
+        <v>108</v>
+      </c>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="10" t="n"/>
       <c r="Y31" s="10" t="n"/>
@@ -9308,7 +10047,11 @@
       <c r="AG31" s="10" t="n"/>
       <c r="AH31" s="10" t="n"/>
       <c r="AI31" s="10" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="inlineStr">
+        <is>
+          <t>Oral</t>
+        </is>
+      </c>
       <c r="AK31" s="10" t="n"/>
       <c r="AL31" s="10" t="n"/>
       <c r="AM31" s="10" t="n"/>
@@ -9322,7 +10065,11 @@
       <c r="AU31" s="10" t="n"/>
       <c r="AV31" s="10" t="n"/>
       <c r="AW31" s="10" t="n"/>
-      <c r="AX31" s="10" t="n"/>
+      <c r="AX31" s="10" t="inlineStr">
+        <is>
+          <t>Ostomia Intestinal</t>
+        </is>
+      </c>
       <c r="AY31" s="11" t="n"/>
       <c r="AZ31" s="11" t="n"/>
       <c r="BA31" s="11" t="n"/>
@@ -9435,6 +10182,21 @@
       <c r="FD31" s="14" t="n"/>
       <c r="FE31" s="14" t="n"/>
       <c r="FF31" s="14" t="n"/>
+      <c r="FG31" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH31" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:25:59</t>
+        </is>
+      </c>
+      <c r="FI31" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23" customHeight="1">
       <c r="A32" t="inlineStr">
@@ -9458,7 +10220,21 @@
       <c r="E32" s="8" t="n">
         <v>25890</v>
       </c>
-      <c r="F32" s="8" t="n"/>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>Há 2 dias com náuseas, vômitos e dores na cabeça e estômago. AP: CA de testículo com meta hepática.. O Tito está bem melhor hoje. Parou de vomitar e esta aceitando um pouco melhor o alimento. Se queixa hoje de piora de su8as parestesias pela quimioterapia-oxaliplatina. Melhora da azia e refluxo
+Sinais vitais normais
+Ao exame:
+BEG, disposto, corado e eupneuico
+cabeça: ndn
+Tórax: MV+ sem RA
+Cor: BRNF sem sopro
+Abdome: obeso e flácido
+Extremidades: ndn. Paciente muito melhor.
+Sem queixas no momento
+Exame físico: sem alterações</t>
+        </is>
+      </c>
       <c r="G32" s="9" t="n"/>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
@@ -9469,9 +10245,19 @@
       <c r="N32" s="9" t="n"/>
       <c r="O32" s="9" t="n"/>
       <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="9" t="n"/>
-      <c r="S32" s="10" t="n"/>
+      <c r="Q32" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T32" s="10" t="n"/>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
@@ -9615,6 +10401,21 @@
       <c r="FD32" s="14" t="n"/>
       <c r="FE32" s="14" t="n"/>
       <c r="FF32" s="14" t="n"/>
+      <c r="FG32" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH32" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:26:49</t>
+        </is>
+      </c>
+      <c r="FI32" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="23" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -9998,7 +10799,42 @@
       <c r="E35" s="8" t="n">
         <v>27174</v>
       </c>
-      <c r="F35" s="8" t="n"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">História Clínica :  Readmissao na uco 02/07 - paciente retorna a unidade calmo colaborativo em ajuste de medicacoes neuro/psiquiatricas 
+Admissão - UTI Cardiológica 29/06/26  
+Paciente com antecedente de HAS, etilismo importante e tabagismo e há 20 dias ficou internado em  Goiânia devido a queda de cavalo associada a TCE e hemorragia intracraniana (mesencéfalo/tálamo à esquerda), sem indicação cirúrgica. Recebeu alta com melhora parcial dos déficits neurológicos (hemiparesia D, disartria), teve abstinência importante durante internação prévia. Internado nesta unidade desde 21/06, sem seguimento com Psiquiatria, Neurologia e Cardiologia. Encaminhado a UTI hoje devido a quadro de agitação psicomotora grave, com queda do leito e necessidade de uso de medicações parenterais. Admitido vigil, calmo, discurso confuso, disartria presente. Eupneico em AA, estável do ponto de vista hemodinâmico.  
+ Objetivo de cuidado conforme discutido com paciente e/ou familiares/ responsáveis, em caso de deterioração clínica:  
+ Status Pleno. Paciente candidato a medidas de suporte artificial de vida (RCP, IOT, etc.). :  sim  
+ Paciente candidato a medidas clínicas não-invasivas. Contraindicadas medidas invasivas de suporte artificial de vida. :  não  
+ Garantir controle de sintomas e permitir processo de morte de forma mais natural e mais confortável possível. :  não  
+ Paciente com necessidade de controle de sintomas:  
+ Equipe Médica :  Roberto Kalil Filho, Rogerio Tuma  
+ Alergias :  Nega alergia alimentar,Nega existência de Alergias, 
+ Diagnósticos e Lista de problemas :  1) Agitação psicomotora de difícil controle - 29/06/26 
+&gt; Abstinência alcóolica/nicotina  
+2) TCE + hemorragia intracraniana - 06/26 
+&gt; Sem indicação de abordagem, TC de controle em 30/6 com evidência de reabsorção do hematoma e melhora do edema.  
+3) Broncopneumonia 
+Rocefin (28/06-06/07)  
+ Antecedentes Pessoais :  HAS  
+Cx: lipoaspiração, abdominoplastia, colecistectomia   
+Tabagismo - 3 maços por dia  
+Etilismo - 3 garrafas de whisky   
+Alergia - sulfa  
+ Diagnósticos Sindrômicos durante a internação  
+ Profilaxias  
+ Úlcera de Estresse :  sim  
+ Profilaxia para TEV mecânica :  sim  
+ Avaliação TEV não se aplica. Paciente menor de 18 anos. :  não  
+ Evolução  
+ Evolução/Impressão Clínica :  Paciente estável hemodinamicamente. 
+Sem ATB. 
+Bom controle de agitação.  
+ Condutas :  Segue conforme orientações das equipes assistentes 
+Programação de alta DIA 11/07 17:00 </t>
+        </is>
+      </c>
       <c r="G35" s="9" t="n"/>
       <c r="H35" s="9" t="n"/>
       <c r="I35" s="9" t="n"/>
@@ -10009,8 +10845,14 @@
       <c r="N35" s="9" t="n"/>
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="R35" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S35" s="10" t="n"/>
       <c r="T35" s="10" t="n"/>
       <c r="U35" s="10" t="n"/>
@@ -10023,9 +10865,17 @@
       <c r="AB35" s="10" t="n"/>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="10" t="n"/>
+      <c r="AE35" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF35" s="10" t="n"/>
-      <c r="AG35" s="10" t="n"/>
+      <c r="AG35" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH35" s="10" t="n"/>
       <c r="AI35" s="10" t="n"/>
       <c r="AJ35" s="10" t="n"/>
@@ -10155,6 +11005,21 @@
       <c r="FD35" s="14" t="n"/>
       <c r="FE35" s="14" t="n"/>
       <c r="FF35" s="14" t="n"/>
+      <c r="FG35" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH35" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:27:39</t>
+        </is>
+      </c>
+      <c r="FI35" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="23" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -10178,7 +11043,38 @@
       <c r="E36" s="8" t="n">
         <v>27385</v>
       </c>
-      <c r="F36" s="8" t="n"/>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Paciente com antecedente de DAC não obstrutiva, interna com cansaço de inicio recente.TEM ALERGIA AAS, faz uso de plavix.Parou ha 6dias.
+Antecedentes
+COVID-19 (01/2021 01/2022) - oligossintomáticos / assintomáticos, sem critérios de gravidade
+- HAS
+- DLP
+- Doença Arterial Coronariana
+- DRGE (SIC)
+- PO (2017) - Abdordagem cirurgica por Diverticulite Complicada.
+- PSG (2023) - SAHOS moderada, SARVAS moderada (não realizado exame com CPAP)
+- Dor crônica em coluna lombar (refere melhora com Fisioterapia e Pilates, nunca tendo realizado nenhum procecimento - SIC)
+- Atividade fisica: caminhada, fisioterapia, Pilattes
+- Ex-tabagista (cessou há mais de 30 anos)
+- Etilismo social (2-3x na semana)
+- Familiar: tio - DAC (ATC). Nega antecedente familiar de CA.
+- Alergia a AAS, Sulfa de Dipirona
+# MUC:
+Acertil 5mg 1xd, Plavix 75mg 1xd, Rosuvastatina 40mg 1xd, Ezetimiba 10mg 1xd
+# Exames anteriores:
+- RNM de coração (11/2023): Câmaras cardíacas com dimensões normais. Função sistólica biventricular preservada. Ausência de fibrose miocárdica. Viabilidade miocárdica preservada.
+- Cate (10/2022): CD irreg, DP e VP irreg, TCE sem lesões, DA irreg, Dg1 50%, Dg2 irreg, Cx irreg, Mg irreg. Lesão discreta no segmento médio da artéria primeira diagonal ao ultrassom intracoronário (IVUS)
+# Ao exame:
+- Geral: BEG, corado, hidratado, acianótico
+- Neuro: Consciente, orientado, sem déficits
+- Cardiovasc: RCR, bulhas NF em 2T sem sopros, TEC&lt;3s
+- Resp: MV presente bilat sem RA, eupneico
+- Abdome: normotenso, sem massas, sem VCM, RHA normais
+- Extremidades: sem edema, sem sinais de TVP
+Cd:Discutido em visita, pelos sintomas clinicos, lesao coronariana em torno 50% no cate de 2022, considerando riscos e beneficios, indicado estratificação invasiva.Paciente concorda com procedimento.O mesmo será feito pelo Dr Fabio sandoli, peço reserva uco . ALTA DIA 23/06 15:43</t>
+        </is>
+      </c>
       <c r="G36" s="9" t="n"/>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
@@ -10189,24 +11085,50 @@
       <c r="N36" s="9" t="n"/>
       <c r="O36" s="9" t="n"/>
       <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="9" t="n"/>
-      <c r="S36" s="10" t="n"/>
+      <c r="Q36" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R36" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T36" s="10" t="n"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="10" t="n"/>
       <c r="Y36" s="10" t="n"/>
-      <c r="Z36" s="10" t="n"/>
+      <c r="Z36" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="10" t="n"/>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="10" t="n"/>
+      <c r="AE36" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF36" s="10" t="n"/>
-      <c r="AG36" s="10" t="n"/>
-      <c r="AH36" s="10" t="n"/>
+      <c r="AG36" s="10" t="inlineStr">
+        <is>
+          <t>Suporte não invasivo</t>
+        </is>
+      </c>
+      <c r="AH36" s="10" t="inlineStr">
+        <is>
+          <t>CPAP</t>
+        </is>
+      </c>
       <c r="AI36" s="10" t="n"/>
       <c r="AJ36" s="10" t="n"/>
       <c r="AK36" s="10" t="n"/>
@@ -10335,6 +11257,21 @@
       <c r="FD36" s="14" t="n"/>
       <c r="FE36" s="14" t="n"/>
       <c r="FF36" s="14" t="n"/>
+      <c r="FG36" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH36" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:28:30</t>
+        </is>
+      </c>
+      <c r="FI36" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -10358,7 +11295,93 @@
       <c r="E37" s="8" t="n">
         <v>27434</v>
       </c>
-      <c r="F37" s="8" t="n"/>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Atual:
+- Precordialgia
+DAC crônica + doença microvascular
+CATE (24/6/26): DA com stent e irregularidades, Dg com stent e irregularidades . Cx com irregularidades, MgE com stent e irregularidades. CD com stent com lesão de 30%, DP e VP com lesões discretas
+- Dorsalgia
+- Disfunção renal crônica
+HPMA:
+Paciente coronariopata procura PS com queixa de desconforto torácico há 24h, com episódios intermitente em aperto e resolução espontânea. 
+No PS, troponina 38 &gt; 40. Eco mantendo disfunção segmentar inferior, semelhante a exame anterior de abril/2025;
+Recebeu isordil e paracetamol no primeiro atendimento com resolução da dor.
+AP:    
+# Síndrome coronariana aguda: ATC + balão farmacológico intrastent em MgE em 15/2/25 guiada por IVUS
+# DAC + ATC CD + IAMSST (2022) + ATC Dg e balão farmacológico na DA +
+Angina microvascular (Stents pérvios em Cate 03/2023)
+# HAS de dificil controle / DLP
+# DRC
+# TVP MIE há 10a e em Maio/24
+# Cefaleia cervicogênica / Ateromatose de basilar? Lesao carotídea assintomática
+# Distensão abdominal - DRGE não erosiva, bulboduodenite/ doença celíaca
+# Vasoespasmo em AA basilar e cerebrais médias - melhora com vasodilatador e redução dos anti-hipertensivos
+# DAOP com intervenção percutânea + stent em MI
+# Neuroestimulador medular implantado em 11/2021 (Abbott)
+# Denervação renal em 05/21
+# Em 4/5/2022 - Protese peniana
+# Lombalgia crônica / PO Neurólise e infiltração anestésica cervical e lombosacral - 05/10/2024
+# PO Implante de bomba intratecal 17/04/25
+# 14/02 PO de resscção de lipoma com envolvimento muscular, sem intercorrencias. 
+# DRC agudizada (hipotensao procedimento) 
+# FA ARV (16/02) revertida - primeiro episodio 
+ALERGIAS:
+Atorvastatina
+Micropore
+Evolução
+Pcte sem queixas de dor torácica, fazendo reabilitacao.
+Cate em 24/6/26 sem lesões importantes - mantido tratamento clinico
+Melhora da dor lombar
+Trocado clorana por firialta e anlodipino por enalapril, iniciado dapaglifozina em 6/7
+Creatinina em elevação discreta - Suspensa DAPA em 10/7/26
+Evacuação presente
+Ao exame:
+- G15, orientado, hidratado
+- RCR, bem perfundido.
+- Eupnéico em AA
+- MV+ sem RA
+- Abdome inocente, RHA+
+- MMII edema discreto de tornozelo
+- Diurese espontânea
+- Afebril, sem ATB
+EXAMES COMPLEMENTARES
+LAB (25/6/26): Troponina T ultrassensível94,9 (33,50)Sódio143 (140)Potássio4,6 (4,0)Uréia86 (83)Creatinina2,40 (2,42)
+LAB (27/06): Troponina T ultrassensível109 (108);Sódio139 (139);Potássio4,2 (4,2);Uréia101 (89);Creatinina2,54 (2,55)
+LAB (28/6/26): Troponina T ultrassensível111 (109)Sódio141 (139)otássio4,4 (4,2)réia22 (101)Creatinina2,83 (2,54)Gaso venoso - pH
+7,34 (7,32)Gaso venoso - pO251 (76)Gaso venoso - pCO249 (49)Gaso venoso - Bicarbonato26 (25)Gaso venoso - BE0 (-1,4)Gaso venoso - Saturação O279 (95)
+LAB (29/6/26): Troponina T ultrassensível102,00 (111)Hemoglobina12,7 (12,3)Leucócitos7970 (6850)Plaquetas190000 (155000)
+Sódio142 (141)Potássio4,4 (4,4)Uréia122 (122)Creatinina2,68 (2,83)PCR0,37 (0,20)
+LAB (29/6/26): Sódio139 (142)Potássio4,7 (4,4)Uréia111 (122)Creatinina2,55 (2,68)Gaso venoso - pH,31 (7,34)Gaso venoso - pO241 (51)Gaso venoso - pCO252 (49)Gaso venoso - Bicarbonato26 (26)Gaso venoso - Saturação O261
+(79)
+LAB (03/07/26): Sódio142 (140);Potássio5,0 (4,8);Creatinina2,83 (2,70);Gaso venoso - pH7,25 (7,31) Gaso venoso - Bicarbonato26 (26);Gaso venoso - Saturação O233 (61)
+LAB (4/7/26): Hemoglobina11,5 (12,7)Leucócitos7190 (7970)Plaquetas186000 (190000)Sódio138 (142)Potássio5,0 (5,0)Uréia121 (115)Creatinina2,86 (2,83)
+USG doppler aa renais. sem PLACAS
+LAB (5/7/26): Sódio138 (138)Potássio5,3 (5,0)Uréia120 (121)Creatinina2,91 (2,86)
+LAB (6/7/26): Sódio139 (138)Potássio5,3 (5,3)Uréia119 (120)Creatinina2,82 (2,91
+LAB (8/7/26): otássio5,2 (5,4)Uréia123 (111)Creatinina3,06 (2,80)
+LAB (9/7/26): ódio138 (139)Potássio5,4 (5,2)Uréia119 (123)Creatinina3,16 (3,06)
+LAB (10/7/26): otássio5,4 (5,4)Uréia120 (119)Creatinina3,37 (3,16)
+LAB (11/7/26): Hemoglobina11,3 (11,5)Sódio139 (138)Potássio5,4 (5,4)Uréia126 (120)Creatinina3,49 (3,37)
+LAB (12/7/26): Hemoglobina11,3 (11,5)Sódio39 (138)Potássio5,4 (5,4)Uréia126 (120)Creatinina3,49 (3,37)
+LAB (13/7/26): Potássio5,1 (5,5)Uréia119 (118)Creatinina3,37 (3,24)
+LAB (14/7/26): Potássio5,5 (5,1)Uréia125 (119)Creatinina3,38 (3,37)
+LAB (15/7/26): Potássio5,8 (5,5)Uréia122 (125)Creatinina3,30 (3,38)
+LAB (16/7/26): Sódio138 (139)Potássio5,2 (5,8)Creatinina3,16 (3,30)
+LAB (17/7/26): ódio138 (138)Potássio5,5 (5,2)Uréia121 (122)Creatinina3,27 (3,16
+CD:
+Dieta pobre em K; Lokelma
+Trocado clorana por firialta em 25/6. Anlo por enalapril 01/7. 
+Iniciado dapaglifozina em 6/7/26; suspensa em 10/7 pela piora da função renal
+Laxativo
+HNF
+Fisioterapia
+FISIATRIA com fisio no centro de reabilitação
+Acompanhamento da nefrologia e do grupo da DOR
+Paciente ciente e de acordo com as medidas
+Exame laboratorial diário.</t>
+        </is>
+      </c>
       <c r="G37" s="9" t="n"/>
       <c r="H37" s="9" t="n"/>
       <c r="I37" s="9" t="n"/>
@@ -10369,8 +11392,14 @@
       <c r="N37" s="9" t="n"/>
       <c r="O37" s="9" t="n"/>
       <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="9" t="n"/>
+      <c r="Q37" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R37" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
       <c r="U37" s="10" t="n"/>
@@ -10383,9 +11412,17 @@
       <c r="AB37" s="10" t="n"/>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
+      <c r="AE37" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
+      <c r="AG37" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH37" s="10" t="n"/>
       <c r="AI37" s="10" t="n"/>
       <c r="AJ37" s="10" t="n"/>
@@ -10411,9 +11448,13 @@
       <c r="BD37" s="11" t="n"/>
       <c r="BE37" s="11" t="n"/>
       <c r="BF37" s="11" t="n"/>
-      <c r="BG37" s="11" t="n"/>
+      <c r="BG37" s="11" t="n">
+        <v>3.27</v>
+      </c>
       <c r="BH37" s="11" t="n"/>
-      <c r="BI37" s="11" t="n"/>
+      <c r="BI37" s="11" t="n">
+        <v>7.25</v>
+      </c>
       <c r="BJ37" s="11" t="n"/>
       <c r="BK37" s="11" t="n"/>
       <c r="BL37" s="11" t="n"/>
@@ -10515,6 +11556,21 @@
       <c r="FD37" s="14" t="n"/>
       <c r="FE37" s="14" t="n"/>
       <c r="FF37" s="14" t="n"/>
+      <c r="FG37" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH37" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:29:22</t>
+        </is>
+      </c>
+      <c r="FI37" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="23" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -10538,7 +11594,56 @@
       <c r="E38" s="8" t="n">
         <v>27715</v>
       </c>
-      <c r="F38" s="8" t="n"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ipo evolução :   UTI Cardiológica / UAIC  
+ Transferência :  não  
+ História Clínica :  # 14/06/2026 - ADMISSAO UAIC -&gt; TAQUICARDIA VENTRICULAR INSTAVEL  
+&gt; &gt; &gt; PACIENTE EM 13/06/2026 EVOLUINDO COM DESCONFORTO TORACICO E DISPNEIA, PROCUROU EMERGENCIA DO SAO LUIZ ANALIA FRANCO ONDE FOI DIAGNOSTICADO COM TAQUICQARDIA VENTRICULAR INSTAVEL, DURANTE PREPARAÇÃO PARA DESFIBRILAÇÃO VENTRICULAR SEGUE A UMA PARADA CARDIACA EM TAQUICARDIA VENTRICULAR SEM PULSO, APÓS DOIS MINUTOS DE MANOBRAS DE RESSUSCITAÇÃO CARDIOPULMONAR E PRIMEIRO CHOQUE, RETORNA A CIRCULAÇÃO ESOPNTANEA ASSOCIADA A MULTIPAS EXTRASSISTOLES VENTRICULARES. PACIENTE ENTUBADO, SEDADO, INICIADA AMIODARONA E LIDOCAINA E ENCAMINHADO A UTI DAQUELE HOSPITAL, FAMILIARES ENTRAM EM CONTATO COM MEDICO PROPRIO DR FERNANDO MACHADO QUE SOLICITA TRANFERENCIA AO HOSPITAL SIRIO LIBANES.  
+ Objetivo de cuidado conforme discutido com paciente e/ou familiares/ responsáveis, em caso de deterioração clínica:  
+ Status Pleno. Paciente candidato a medidas de suporte artificial de vida (RCP, IOT, etc.). :  sim  
+ Paciente candidato a medidas clínicas não-invasivas. Contraindicadas medidas invasivas de suporte artificial de vida. :  não  
+ Garantir controle de sintomas e permitir processo de morte de forma mais natural e mais confortável possível. :  não  
+ Paciente com necessidade de controle de sintomas:  
+ Equipe Médica :  FERNANDO MACHADO  
+ Alergias :  Nega existência de Alergias, 
+Nega existência de Alergias, 
+Nega alergia alimentar,Nega existência de Alergias, 
+ Diagnósticos e Lista de problemas :  # 2° PO de implante de CDI  
+# TAQUICARDIA VENTRICULAR INSTAVEL  
+# PCR TAQUICARDIA VENTRICULAR SEM PULSO 2MIN  
+ Antecedentes Pessoais :  * SARCOIDOSE SISTEMIA 
+* BAV PRIMEIDO + BRD  
+ Diagnósticos Sindrômicos durante a internação  
+ Profilaxias  
+ Úlcera de Estresse :  sim  
+ Profilaxia para TEV farmacológica :  sim  
+ Avaliação TEV não se aplica. Paciente menor de 18 anos. :  não  
+ Evolução  
+ Evolução/Impressão Clínica :  #Evolução Diurna UAIC - 20/06/26 
+Paciente em 2° PO de implante de CDI em bom estado geral, lúcido e orientado. Sem  intercorrências no período.  
+# Controles:  
+- Temp: 35,0-36,2°C 
+- PAM: 71-95 mmHg 
+- FC: 54-63bpm 
+- FR: 10-26irpm 
+- Sat: 94-100% 
+- Dextro: 98 
+- Diurese: 8001 ml + perdas  
+- BH: -407 ml 
+- Evacuação: 1x pastosa 
+# Exame físico:  
+- Beg, corado, hidratado, anicterico, acianotico, afebril.  
+- AP: MVF sem RA, Spo2 97% em ar ambiente.  
+- AC: BRNF em 2t, em ritmo sinusal. FC 65bpm, PAM 82mmHg.  
+- Abdome: Flácido, rha +  indolor a palpação. Dieta geral. 
+- Ext: livres sem edemas. TEC &lt; 3s.  
+- Hemato/ Infeccioso: Hb 13,9  Ht 41,1%  Leuco 13010 (Neut 90,3%)  Plaq 140mil  PCR 0,5   
+- Renal/ Metabólico: Ur 53  Cr 1,15  Na 139  K 4,4  Cai 1,25  P 4,0  Mg 1,8  pH 7,40  HCO3 27  BE +1.2  
+ Condutas :  # Conduta conforme discutido com equipe titular: 
+- Alta para casa alta dia 20/06 14:41  </t>
+        </is>
+      </c>
       <c r="G38" s="9" t="n"/>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
@@ -10549,23 +11654,53 @@
       <c r="N38" s="9" t="n"/>
       <c r="O38" s="9" t="n"/>
       <c r="P38" s="9" t="n"/>
-      <c r="Q38" s="9" t="n"/>
-      <c r="R38" s="9" t="n"/>
-      <c r="S38" s="10" t="n"/>
+      <c r="Q38" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="R38" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T38" s="10" t="n"/>
       <c r="U38" s="10" t="n"/>
-      <c r="V38" s="10" t="n"/>
-      <c r="W38" s="10" t="n"/>
-      <c r="X38" s="10" t="n"/>
-      <c r="Y38" s="10" t="n"/>
-      <c r="Z38" s="10" t="n"/>
+      <c r="V38" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="W38" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="X38" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="Y38" s="10" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="Z38" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA38" s="10" t="n"/>
       <c r="AB38" s="10" t="n"/>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
-      <c r="AE38" s="10" t="n"/>
+      <c r="AE38" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF38" s="10" t="n"/>
-      <c r="AG38" s="10" t="n"/>
+      <c r="AG38" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH38" s="10" t="n"/>
       <c r="AI38" s="10" t="n"/>
       <c r="AJ38" s="10" t="n"/>
@@ -10591,9 +11726,13 @@
       <c r="BD38" s="11" t="n"/>
       <c r="BE38" s="11" t="n"/>
       <c r="BF38" s="11" t="n"/>
-      <c r="BG38" s="11" t="n"/>
+      <c r="BG38" s="11" t="n">
+        <v>1.15</v>
+      </c>
       <c r="BH38" s="11" t="n"/>
-      <c r="BI38" s="11" t="n"/>
+      <c r="BI38" s="11" t="n">
+        <v>7.4</v>
+      </c>
       <c r="BJ38" s="11" t="n"/>
       <c r="BK38" s="11" t="n"/>
       <c r="BL38" s="11" t="n"/>
@@ -10695,6 +11834,21 @@
       <c r="FD38" s="14" t="n"/>
       <c r="FE38" s="14" t="n"/>
       <c r="FF38" s="14" t="n"/>
+      <c r="FG38" t="inlineStr">
+        <is>
+          <t>AGUARDANDO_CID</t>
+        </is>
+      </c>
+      <c r="FH38" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:30:12</t>
+        </is>
+      </c>
+      <c r="FI38" t="inlineStr">
+        <is>
+          <t>Demais páginas preenchidas; falta apenas definir o CID antes da confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -10718,7 +11872,65 @@
       <c r="E39" s="8" t="n">
         <v>28260</v>
       </c>
-      <c r="F39" s="8" t="n"/>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paciente estável, ainda com necessidade de DVA
+sonolento 
+obstrução de JJT
+controles: afebril, evac -, diurese + 1460
+recebe: levofloxacino 
+             prednisona 10 mg 
+AO exame 
+Em uso de noradrenalaina 3 mL/h
+Ap resp: MV+ bilat com roncos em ar ambiente Sat: 97%
+MMII: edema 1+/4+
+exames 
+CST: E.coli
+PCR: 6,8
+cd: 
+troca de GTT amanha
+reposição de eletrolitos 
+desmame de noradrenalina 
+vigilância neurológica 
+Atual: 
+# Sincope por quadro disautonomico/hipotensão postural multifatorial (idoso, uso de betabloqueador, desidratação, provavel neuropatia diabética)
+--&gt; Eco com  função biventricular preservada
+--&gt; Cintilografia miocárdica sem isquemia estresse-induzida 
+--&gt; TC de crânio com sinais de AVCi cerebelar prévio
+--&gt; Doppler de Aorta com aneurisma fusiforme de 4,2 cm.
+--&gt; Doppler transcraniano com sinais de disautonomia
+--&gt; Holter: Ritmo sinusal, presença de 15 pausas maiores que 2,0 segundos. Ectopias ventriculares raras. Ectopias supraventriculares raras 
+---&gt; Holter (pós 7 dias de suspensão de betabloqueador): Ritmo sinusal, presença de 9 pauseas maiores que 2,0 segundos, a mais londa com duração de 2,4 segundos relacionada a ectopia supraventricular bloqueada.
+# Anemia macrocítica por IRC? (com vitB12 e ácido fólico normais, IST 29% e Ferritina &gt; 500)
+--&gt; EDA: Formação vascular anômala (angiectasia) no corpo alto. Lesão elevada irregular no corpo alto. Realizado biópsias. Bulboduodenite leve. 
+--&gt; Colono: Angiectasia do cólon ascendente. Proctopatia actínica. 
+Antecedentes:
+- DAC com revascularização miocardica cirurgica aos 46 anos
+- HAS/DLP
+- DM2 insulinodependente
+- IRC pré-dialitica
+- Cancer de prostata com tratamento conservador (bloqueio hormonal) em 2024
+--&gt; uso de degarelix
+- Nega alergias
+- Ex-tabagista há 40 anos
+# Evolução:
+Paciente sem intercorrências. Sinais vitais estáveis. Exames laboratoriais sem alterações evolutivas significativas.
+Ao exame: BEG, hidratado, eupneico
+MV+ sem RA
+RCR, boa perfusão periferica
+abdome flacido, timpanico
+MMII: sem edema
+Impressão: Sincope provavelmente multifatorial (disautonomia por DM, uso de medicamentos - Bbloq, ARM - anemia macrocítica por DRC?).
+Conduta discutida com o Dr. Cardoso:
+- Alta hospitalar. Explico ao paciente e à sua esposa sobre o diagnóstico de doença do nó sinusal e a necessidade de seguimento regular devido ao risco de implante de MP
+- Mantenho Florinefe 0,100 mg/dia e uso de meias elasticas
+- Suspendo AAS até o resultado da biópsia
+- Deixo protetor gástrico
+- Concilio nesina MET
+Resuma estes dados
+</t>
+        </is>
+      </c>
       <c r="G39" s="9" t="n"/>
       <c r="H39" s="9" t="n"/>
       <c r="I39" s="9" t="n"/>
@@ -10729,26 +11941,52 @@
       <c r="N39" s="9" t="n"/>
       <c r="O39" s="9" t="n"/>
       <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="9" t="n"/>
-      <c r="S39" s="10" t="n"/>
+      <c r="Q39" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R39" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T39" s="10" t="n"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
       <c r="X39" s="10" t="n"/>
       <c r="Y39" s="10" t="n"/>
-      <c r="Z39" s="10" t="n"/>
+      <c r="Z39" s="10" t="inlineStr">
+        <is>
+          <t>Letárgico</t>
+        </is>
+      </c>
       <c r="AA39" s="10" t="n"/>
       <c r="AB39" s="10" t="n"/>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="10" t="n"/>
+      <c r="AE39" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF39" s="10" t="n"/>
-      <c r="AG39" s="10" t="n"/>
+      <c r="AG39" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH39" s="10" t="n"/>
       <c r="AI39" s="10" t="n"/>
-      <c r="AJ39" s="10" t="n"/>
+      <c r="AJ39" s="10" t="inlineStr">
+        <is>
+          <t>Enteral</t>
+        </is>
+      </c>
       <c r="AK39" s="10" t="n"/>
       <c r="AL39" s="10" t="n"/>
       <c r="AM39" s="10" t="n"/>
@@ -10875,6 +12113,21 @@
       <c r="FD39" s="14" t="n"/>
       <c r="FE39" s="14" t="n"/>
       <c r="FF39" s="14" t="n"/>
+      <c r="FG39" t="inlineStr">
+        <is>
+          <t>FINALIZADO</t>
+        </is>
+      </c>
+      <c r="FH39" t="inlineStr">
+        <is>
+          <t>17/07/2026 23:31:08</t>
+        </is>
+      </c>
+      <c r="FI39" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="23" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -10898,7 +12151,59 @@
       <c r="E40" s="8" t="n">
         <v>28284</v>
       </c>
-      <c r="F40" s="8" t="n"/>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo evolução :  UTI/UCG  
+ Transferência :  não  
+ História Clínica :  # Admissão UTI ala II - 24/06/26 # 
+Idoso frágil, totalmente dependente para ABVDs (KPS 20) com doença de Parkinson avançada, com dieta por GTT, vem proveniente do PS com relato de ter broncoaspirado hoje por volta das 6h da manhã, evoluindo em seguida com dessaturação. Chega no hospital dessaturando a despeito de uso de O2 em MNR e hipotenso. Aberto protocolo sepse e realizadas medidas. É admitido na UTI sonolento, gemente, não contactuante (basal?), hipotenso e mal perfundido com nora 0,5mcg/kg/min, em MNR 10L/min mantendo StO2 ~ 90%, com cianose central.  
+ Objetivo de cuidado conforme discutido com paciente e/ou familiares/ responsáveis, em caso de deterioração clínica:  
+ Status Pleno. Paciente candidato a medidas de suporte artificial de vida (RCP, IOT, etc.). :  não  
+ Paciente candidato a medidas clínicas não-invasivas. Contraindicadas medidas invasivas de suporte artificial de vida. :  sim  
+ Obs: :  DNI / DNR / não TSR   
+ Garantir controle de sintomas e permitir processo de morte de forma mais natural e mais confortável possível. :  não  
+ Paciente com necessidade de controle de sintomas:  
+ Sim :  não  
+ Controlados :  sim  
+ Não se aplica :  não  
+ Dor :  sim  
+ Dispneia :  sim  
+ Equipe Médica :  Ronaldo Adib Kairalla  
+ Alergias :  Dipirona,Tipo de Reação: Erupção Cutânea 
+Nega alergia alimentar,Nega existência de Alergias, 
+ Diagnósticos e Lista de problemas :  - Choque séptico de foco pulmonar 
+   &gt; Broncoaspiração  
+- IRA KDIGO II (melhor)  
+ Antecedentes Pessoais :  - Doença de Parkinson: totalmente dependente para ABVDs   
+- GTT jan/2024   
+- BCP aspirativa de repetição   
+- Disautonomia   
+- Amaurose bilateral   
+- DM2  
+ Diagnósticos Sindrômicos durante a internação  
+ Choque séptico :  sim  
+ Demência :  sim  
+ Profilaxias  
+ Úlcera de Estresse :  sim  
+ Profilaxia para TEV farmacológica :  sim  
+ Avaliação TEV não se aplica. Paciente menor de 18 anos. :  não  
+ Evolução  
+ Evolução/Impressão Clínica :  Abertura ocular espontânea,  não verbaliza 
+Recebe entacapona, zoloft, ebix, exelon e prolopa.  
+AA, confortável 
+Noradrenalina 0,04 mcg/kg/min  PAM 60 mmHg  Bem perfundido 
+Dieta enteral. Via gastrica aberta - 500ml 
+Diurese espontânea 800ml 
+Afebril 
+Levofloxacina D3 
+Clexane profilático  
+ Condutas :  - Desmame de DVA para PAM ~60mmHg 
+- Manter via gástrica aberta 
+- Vigilância infecciosa e neurológica 
+- Reposição de potássio  
+</t>
+        </is>
+      </c>
       <c r="G40" s="9" t="n"/>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
@@ -10909,8 +12214,14 @@
       <c r="N40" s="9" t="n"/>
       <c r="O40" s="9" t="n"/>
       <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
-      <c r="R40" s="9" t="n"/>
+      <c r="Q40" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R40" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S40" s="10" t="n"/>
       <c r="T40" s="10" t="n"/>
       <c r="U40" s="10" t="n"/>
@@ -10918,17 +12229,29 @@
       <c r="W40" s="10" t="n"/>
       <c r="X40" s="10" t="n"/>
       <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
+      <c r="Z40" s="10" t="inlineStr">
+        <is>
+          <t>Letárgico</t>
+        </is>
+      </c>
       <c r="AA40" s="10" t="n"/>
       <c r="AB40" s="10" t="n"/>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
+      <c r="AE40" s="10" t="inlineStr">
+        <is>
+          <t>Tubo</t>
+        </is>
+      </c>
       <c r="AF40" s="10" t="n"/>
       <c r="AG40" s="10" t="n"/>
       <c r="AH40" s="10" t="n"/>
       <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="inlineStr">
+        <is>
+          <t>Enteral</t>
+        </is>
+      </c>
       <c r="AK40" s="10" t="n"/>
       <c r="AL40" s="10" t="n"/>
       <c r="AM40" s="10" t="n"/>
@@ -10949,8 +12272,16 @@
       <c r="BB40" s="11" t="n"/>
       <c r="BC40" s="11" t="n"/>
       <c r="BD40" s="11" t="n"/>
-      <c r="BE40" s="11" t="n"/>
-      <c r="BF40" s="11" t="n"/>
+      <c r="BE40" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BF40" s="11" t="inlineStr">
+        <is>
+          <t>Noradrenalina</t>
+        </is>
+      </c>
       <c r="BG40" s="11" t="n"/>
       <c r="BH40" s="11" t="n"/>
       <c r="BI40" s="11" t="n"/>
@@ -11078,7 +12409,48 @@
       <c r="E41" s="8" t="n">
         <v>29044</v>
       </c>
-      <c r="F41" s="8" t="n"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HMA - Paciente refere piora da tontura habitual (labirintite previa) com mudança do aspecto e associação com dor de cabea em aperto em região parietal bilateral - quadro esse iniciado há alguns dias. No dia 21/06 iniciou com falta de apetite e mal estar evoluindo para aumento do numero de evacuações e consistencia mais branda que a habitual (3 durante o dia de 22/06) associado a nauseas sem vomitos evoluindo em 23/06 com dor abdominal. Em 23/06 - evacuou uma vez. Nega sintomas respiratórios.
+AP: 
+- Massa Tumoral cística - operada -- Ooferectomia laparoscópica direita + Rafia de laceração em reto e colostomia protetora (30/11/23). - Coleção abdominal - TC abd (04/04/24) coleção ao redor da anastomose em sigmoide &gt;&gt; Tratamento conservador com meropenem -- Ressutura parede abdominal + tela de prolene + dreno de Blake (11/04/24) -- Drenagem de coleção mesentérica no plano da fossa ilíaca esquerda orientada por tomografia computadorizada (30 ml secreção purulenta) - 22/04/24 - Massa Tumoral cística - operada -- Fechamento de colostomia em Alça de Sigmoide com anastomose colo-cólica (26/03/24) 
+- POt de Revisão de artroplastia de quadril E com retirada de componentes e implante de prótese - ARTHRON E (Dr. Rudelli) - Prótese femur D 2005 - POT de implante de prótese total joelho - 2012 - Ca mama op + RT ano 2000 
+- DPOC / Hipotireoidismo / DRGE / SAOS / HAS / DLP  
+- DAC não obstrutiva: escore moderado com placa discreta em ADA 
+Avaliação
+HIdratada, bem alerta, bom estado geral.
+estavel hemodinamicamente
+auscultura pulmonar sem alterações importantes
+abdome doloroso a palpação de hipocondrio esquerdo, porém brando e depressivel, sem visceromegalias palpaveis.
+conduta
+TC sem contraste de seios da face, Torax r abdome, laboratorio
+gecamol
+sem antibiótico por oroa até avaliação de exames. 
+HMA:  Paciente refere quadro de diarreia há 2 dias associada a cólica abdomina, sem novo episódios diarreicos hoje. Nega febre, sintomas respiratorios ou urinarios. Reduzido recentemente olmetec de 20mg para 10mg, após resultado de MAPA. 
+Refere indisposição pela manhã, melhora cerca de 11h da manhã; associado tontura ao se levantar, sensação de mareado com náuseas, que melhora ao longo do dia. Aumentou a dose labirin há cerca de 3 semanas.
+Refefe fazer uso do CPAP por cerca de 4 horas por noite.
+AP: 
+- Massa Tumoral cística - operada -- Ooferectomia laparoscópica direita + Rafia de laceração em reto e colostomia protetora (30/11/23). - Coleção abdominal - TC abd (04/04/24) coleção ao redor da anastomose em sigmoide &gt;&gt; Tratamento conservador com meropenem -- Ressutura parede abdominal + tela de prolene + dreno de Blake (11/04/24) -- Drenagem de coleção mesentérica no plano da fossa ilíaca esquerda orientada por tomografia computadorizada (30 ml secreção purulenta) - 22/04/24 - Massa Tumoral cística - operada -- Fechamento de colostomia em Alça de Sigmoide com anastomose colo-cólica (26/03/24) 
+- POt de Revisão de artroplastia de quadril E com retirada de componentes e implante de prótese - ARTHRON E (Dr. Rudelli) - Prótese femur D 2005 - POT de implante de prótese total joelho - 2012 - Ca mama op + RT ano 2000 
+- DPOC / Hipotireoidismo / DRGE / SAOS / HAS / DLP 
+- DAC não obstrutiva: escore moderado com placa discreta em ADA 
+Medicamentos de uso contínuo: 
+Cymbalta 60 mg; Rivotril 2 mg; neozine 2 gotas; AAS; ezetimiba; Olmetec 20 mg; Syntroid 50 mcg; labirin 24 mg/d; 
+Exame neurológico:
+Vigil, atenção básica preservada
+Motor: força grau 5 global
+Sensibilidade superficial sem alterações 
+Coordenação: apendicular preservadas, Romberg negativo, certa instabilidade ao fechar os olhos
+NNCC: PIFR, MOE sem alterações, ausência de nistagmo mimica facial simétrica
+Impressão: GECA? ITU?
+Conduta - discutida com Dr Rogerio Tuma:
+- Programação alta hospitalar hoje - orientada agendar retorno ambulatorial precoce com Dr Tuma
+- Mantenho labirin 24 mg 12/12h e associo novamente meclin 25 mg/n (23/06)
+- Seguimento conjunto com Equipe infectologia Dr David Uip e Cardiologia Dr Kalil
+- Explico impressão e condutas a paciente. ALTA DIA 23/06 21:30
+</t>
+        </is>
+      </c>
       <c r="G41" s="9" t="n"/>
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
@@ -11089,8 +12461,14 @@
       <c r="N41" s="9" t="n"/>
       <c r="O41" s="9" t="n"/>
       <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="9" t="n"/>
+      <c r="Q41" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="R41" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S41" s="10" t="n"/>
       <c r="T41" s="10" t="n"/>
       <c r="U41" s="10" t="n"/>
@@ -11105,8 +12483,16 @@
       <c r="AD41" s="10" t="n"/>
       <c r="AE41" s="10" t="n"/>
       <c r="AF41" s="10" t="n"/>
-      <c r="AG41" s="10" t="n"/>
-      <c r="AH41" s="10" t="n"/>
+      <c r="AG41" s="10" t="inlineStr">
+        <is>
+          <t>Suporte não invasivo</t>
+        </is>
+      </c>
+      <c r="AH41" s="10" t="inlineStr">
+        <is>
+          <t>CPAP</t>
+        </is>
+      </c>
       <c r="AI41" s="10" t="n"/>
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="10" t="n"/>
@@ -11122,7 +12508,11 @@
       <c r="AU41" s="10" t="n"/>
       <c r="AV41" s="10" t="n"/>
       <c r="AW41" s="10" t="n"/>
-      <c r="AX41" s="10" t="n"/>
+      <c r="AX41" s="10" t="inlineStr">
+        <is>
+          <t>Ostomia Intestinal</t>
+        </is>
+      </c>
       <c r="AY41" s="11" t="n"/>
       <c r="AZ41" s="11" t="n"/>
       <c r="BA41" s="11" t="n"/>
@@ -11258,7 +12648,55 @@
       <c r="E42" s="8" t="n">
         <v>29166</v>
       </c>
-      <c r="F42" s="8" t="n"/>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paciente com antecedente de sobrepeso, hipotireoidismo, uso de cigarro eletronico ha 11 anos, rinite cronica. Interna por alteração de hábito intestinal e pirose. Refere que que realizou avaliação com geneticista no paciente que orientou exame de endoscopia. 
+Foi avaliado pela Dra Claudia na internação passada devido a sobrepeso. Refere estar sem uso de analogo de GLP1 desde maio. 
+AP: 
+Hipotireoidismo
+Rinite 
+Intolerância à gluten 
+Roncos / SAOS? 
+Ansiedade
+TDAH sem tratamento específico 
+Uso de Mounjaro há um ano 
+Cirurgias: 2 septoplastias / Fratura punho esquerdo / Fratura em mão direta
+Atropelado aos 13 anos ~ TCE grave, 30 dias internado ~ sem sequelas. 
+Tabagista de VAPE 
+Etilista social, pouca quantidade
+Pratica musculação 3x na semana 
+Nega alergias medicamentosas
+Infecção por covid 19 leve; 2 doses 
+Não sabe dizer se teve catapora 
+Caxumba na infância
+Já usou balão gástrico para emagrecer. 
+AF: 
+Mãe saudável 
+Pai HAS / DAC 
+Irmão saudável 
+Nega filhos 
+Avô materno Leucemia e DM 
+Nega história de AVC, morte súbita ou trombose
+Em uso de: 
+Euthyrox 50 mcg 1cp oral uma vez ao dia 
++
+Minoxidil + Dutasterida + Formula para cabelo 
++
+Donaren 50mg SOS
++
+Retratutide &gt; 08/05/2026. 
+Exame físico:
+pact internou previamente decidimos manter PT4 50, suspender retratutida e usar contrave 2cp ao dia ate o ret para EDA/colono
+Com mounjaro perdeu previamente peso e manteve 92kg 
+Tem padrão alimentar ruim, alterna jejum prolongado e compulsãoa  noite, muito fast food
+Não usou contrave como recomendado 
+Exames desta internação: 
+18/06/26: urina 1 sem alteações | LDL 112 | TG 119 | Cr 0,95 | U 28 | Hb glicada 5,4% | Hb 15,6 | Leuco 4010 | Plaq 208.000 | Mg 2,0 | PCR 2,94 |
+Condutas
+Inicio na alta mounjaro 5mg + contrave 2cp ao dia
+Nos falaremos em 15 dias para ajuste. ALTA DIA 23/06 23:06 </t>
+        </is>
+      </c>
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
@@ -11269,8 +12707,14 @@
       <c r="N42" s="9" t="n"/>
       <c r="O42" s="9" t="n"/>
       <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
-      <c r="R42" s="9" t="n"/>
+      <c r="Q42" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S42" s="10" t="n"/>
       <c r="T42" s="10" t="n"/>
       <c r="U42" s="10" t="n"/>
@@ -11311,7 +12755,9 @@
       <c r="BD42" s="11" t="n"/>
       <c r="BE42" s="11" t="n"/>
       <c r="BF42" s="11" t="n"/>
-      <c r="BG42" s="11" t="n"/>
+      <c r="BG42" s="11" t="n">
+        <v>0.95</v>
+      </c>
       <c r="BH42" s="11" t="n"/>
       <c r="BI42" s="11" t="n"/>
       <c r="BJ42" s="11" t="n"/>
@@ -11438,7 +12884,44 @@
       <c r="E43" s="8" t="n">
         <v>29771</v>
       </c>
-      <c r="F43" s="8" t="n"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HPMA: Paciente interna com quadro de piora de cansaço, tosse e dor retroesternal há 4 dias, com piora hoje. Refere queda há 4 dias, sem TCE. Realizadas tomografias na admissão e ECG. Admito na UTI cardiológica com quadro de Sindrome coronariana aguda, realizado dose de ceftriaxone no PA por relato de febre em casa e TC de tórax com sinais de broncopatia inflamatória. A entrada na UTI com sinais de congestão pulmonar, não tolerando decúbito e má perfusão, iniciado dobutamina, VNI e furosemida EV. Quanto a SCA, considerando idade avançada, fragilidade, multiplas comorbidades, disfunção renal e elevado risco de complicações periprocedimento, optado por tratamento clínico e medidas de suporte. Mantido com dupla antiagregação plaqueária e estatina. 
+Paciente acordado no momento da avaliação, mantendo melhora importante do padrão respiratório, em uso de CNO2 a 1l/min e VNI para exercicio. Estável hemodinamicamente, em uso de dobutamina 5 mcg e tridil 3 ml/h, boa perfusão periférica, microhemodinamica adequada. Radiografia de torax, melhora da congestão. Diurese presente, com função renal estável com discreta ascensão Cr 2,65&gt;2,67 e Ur 87&gt;93, recebendo furosemida 3amp 6/6h, BH negativo (-1000 ml). Abdomen globoso, flácido, evacuação presente. Afebril, com marcadores inflamatórios estáveis, em uso de tazocin e teicoplanina. Culturas parciais negativas. Peso hoje 69,5 kg. Recebendo dieta pastosa, conforme orientação da fono.   
+CONDUTA: 
+- Mantenho aldactone 50 mg/dia, forxiga e deixo furosemida 3 amp 6/6h. Objetivando BH negativo (-1000 ml), manter peso 70kg. 
+- Desmame de dobutamina 3 mcg/kg/min. Avaliaremos levosimendan amanhã.  
+- Peso diário.  
+- Seguimento com a fono, progressão de dieta oral. 
+- Fisioterapia respiratória e motora, sentar em poltrona. 
+- Mantido DAPT. 
+- Suporte intensivo.Paciente em leito de UTI, apresentando melhora clínica, acordado, consciente e orientado. Nega queixas.  
+Hemodinamicamente compensado às custas de Dobutamina 5 mcg/Kg/min, perfusão preservada, parâmetros micro-hemodinâmicos adequados. Vasodilatação com Tridil conforme tolerância pressórica.  
+Diurese em SVD (1150 ml) com estímulo com furosemida em bólus, função renal em piora lenta progressiva, hoje Cr 2,6. 
+Hb estável, sem exteriorização de sangramentos. Profilaxia TEV com HNF, recebe DAPT com AAS e Clopidogrel por SCA.    
+Afebril, em uso de ATB de amplo espectro, PCR em queda, culturas negativas (parciais). 
+Recebe dieta pastosa com boa tolerância, evacuação presente, euglicêmico.  
+Dispositivos: SVD 25/06 | PICC MSD 25/06   
+ATB:  
+- Tazocin (07/07) 
+- Teicoplanina (12/07) 
+Controles 12h: PAM 84-65 | T. máx 36,7 | FC 71-60 | FR 47-17 | Glicemias 139-119 | SpO2 99-91  
+Exame físico: 
+- GERAL: REG, normocorado, acianótico, anictérico, afebril   
+- NEURO: colaborativo ao exame, ECG 15, pupilas IFR, sem déficits focais  
+- ACV: RCR em 2T, sem sopros.  TJ- 
+- AR: MV reduzido em bases, com EC bibasais discretos, em melhora. Sem esforço, em CN 1L/min 
+- ABD: Flácido, normotenso, indolor. Sem massas/megalias.   
+- EXT: sem edemas; TEC preservado, panturrilhas livres. 
+Conduta: 
+- Mantido Dobutamina 5mcg/Kg/min e Vasodilatação com Tridil (tentativa de progressão conforme tolerância pressórica).  
+- Proposta de realização de levosimendan em segundo momento após descongestão.  
+- Controle de BH - manter negativo por ora. 
+- Se insônia ou agitação - Precedex noturno. 
+- Suporte intensivo.  
+ </t>
+        </is>
+      </c>
       <c r="G43" s="9" t="n"/>
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="9" t="n"/>
@@ -11449,20 +12932,52 @@
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
       <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
-      <c r="R43" s="9" t="n"/>
-      <c r="S43" s="10" t="n"/>
+      <c r="Q43" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R43" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>REG – Regular Estado Geral</t>
+        </is>
+      </c>
       <c r="T43" s="10" t="n"/>
       <c r="U43" s="10" t="n"/>
-      <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="n"/>
+      <c r="V43" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="W43" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="X43" s="10" t="n">
+        <v>91</v>
+      </c>
       <c r="Y43" s="10" t="n"/>
-      <c r="Z43" s="10" t="n"/>
+      <c r="Z43" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA43" s="10" t="n"/>
-      <c r="AB43" s="10" t="n"/>
-      <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
+      <c r="AB43" s="10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AC43" s="10" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="AD43" s="10" t="inlineStr">
+        <is>
+          <t>PICC</t>
+        </is>
+      </c>
       <c r="AE43" s="10" t="n"/>
       <c r="AF43" s="10" t="n"/>
       <c r="AG43" s="10" t="n"/>
@@ -11482,16 +12997,30 @@
       <c r="AU43" s="10" t="n"/>
       <c r="AV43" s="10" t="n"/>
       <c r="AW43" s="10" t="n"/>
-      <c r="AX43" s="10" t="n"/>
+      <c r="AX43" s="10" t="inlineStr">
+        <is>
+          <t>SVD - Sonda vesical de demora</t>
+        </is>
+      </c>
       <c r="AY43" s="11" t="n"/>
       <c r="AZ43" s="11" t="n"/>
       <c r="BA43" s="11" t="n"/>
       <c r="BB43" s="11" t="n"/>
       <c r="BC43" s="11" t="n"/>
       <c r="BD43" s="11" t="n"/>
-      <c r="BE43" s="11" t="n"/>
-      <c r="BF43" s="11" t="n"/>
-      <c r="BG43" s="11" t="n"/>
+      <c r="BE43" s="11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BF43" s="11" t="inlineStr">
+        <is>
+          <t>Dobutamina</t>
+        </is>
+      </c>
+      <c r="BG43" s="11" t="n">
+        <v>2.6</v>
+      </c>
       <c r="BH43" s="11" t="n"/>
       <c r="BI43" s="11" t="n"/>
       <c r="BJ43" s="11" t="n"/>
@@ -11500,8 +13029,16 @@
       <c r="BM43" s="11" t="n"/>
       <c r="BN43" s="11" t="n"/>
       <c r="BO43" s="11" t="n"/>
-      <c r="BP43" s="12" t="n"/>
-      <c r="BQ43" s="12" t="n"/>
+      <c r="BP43" s="12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="BQ43" s="12" t="inlineStr">
+        <is>
+          <t>Tazocin; Teicoplanina</t>
+        </is>
+      </c>
       <c r="BR43" s="12" t="n"/>
       <c r="BS43" s="12" t="n"/>
       <c r="BT43" s="12" t="n"/>
@@ -11618,7 +13155,40 @@
       <c r="E44" s="8" t="n">
         <v>29800</v>
       </c>
-      <c r="F44" s="8" t="n"/>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Funcionalidade: parcialmente dependente para atividades básicas
+Cognição preservada
+Cuidadora principal: filha 
+Atual: 
+1. Síndrome gripal + broncoespasmo
+- Covid e Influenza negativos 
+- Pneumonia bacteriana? 
+2. Queda da própria altura 
+3. DRC agudizada
+4. Delirium hiperativo 
+5. Pneumoperitôneo
+- Dor abdominal em 11/07 madrugada
+- TC abdominal com pneumoperitôneo
+HMA: Há 3 dias tosse produtiva, com piora progressiva, apresentando expectoração espessa e amarelo claro. Ontem teve queda da própria altura, com trauma em joelho e quadril direitos. Conseguiu deambular após, porém hoje evolui com dor e incapacidade de andar. Trazido de ambulância - hipoxêmico à chegada - sat. O2: 79% AA, afebril, estável hemodinamicamente. Aberto protocolo sepse - foco pulmonar. 
+AP:
+HAS 
+DM 
+FA prévia - sem anticoagulaçao (caidor crônico)
+DAC - IAM 1991/2014 e 2018 com ATC de ADA/ Fev 2021 ACD ocluida com demais sem lesões obstrutivas e stents pérvios/ Tentativa de ATC de ACD sem sucesso 
+Estenose de canal vertebral Osteoporose - Fratura de úmero D com tto cirúrgico em jan/2021 
+Ex tabagista - cessou há 30 anos Ca de próstata - em uso de casodex
+MUC: 
+Ancoron Ezetimiba Jardiance Selozok rosuvastatina casodex furosemida
+Evolução: 
+Pela manhã, sou contactada por equipe de UTI que paciente apresentou instabilidade hemodinamica importante durante a madrugada, tendo sido necessário aumento progressivo de DVA, evoluindo com FA instavel e cardioversão. Posteriomente, paciente evoluiu com PCR em assistolia, realizados 8 ciclos de RCP, sem sucesso.
+Diante do quadro clínico de paciente, fragilidade prévia, DVA em doses otimizadas e refratariedade clínica, optamos por suspensão de manobras de reanimação. 
+Óbito às 6h55
+Causa do óbito:
+2. Choque séptico refratário 
+1. Isquemia mesentérica com perfuração de alça</t>
+        </is>
+      </c>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
@@ -11629,8 +13199,14 @@
       <c r="N44" s="9" t="n"/>
       <c r="O44" s="9" t="n"/>
       <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="9" t="n"/>
-      <c r="R44" s="9" t="n"/>
+      <c r="Q44" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="R44" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
       <c r="U44" s="10" t="n"/>
@@ -11639,7 +13215,11 @@
       <c r="X44" s="10" t="n"/>
       <c r="Y44" s="10" t="n"/>
       <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="10" t="n"/>
+      <c r="AA44" s="10" t="inlineStr">
+        <is>
+          <t>Deambulando</t>
+        </is>
+      </c>
       <c r="AB44" s="10" t="n"/>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -12023,7 +13603,106 @@
       <c r="E46" s="8" t="n">
         <v>30692</v>
       </c>
-      <c r="F46" s="8" t="n"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data e Hora da realização da APA :  24/06/2026 18:23:00  
+ Código Paciente :  3019459  
+ Atendimento :  17799956  
+ Complexidade Cirúrgica :  Média  
+ Procedimento(s) proposto(s) :  Epistaxe - cauterização da artéria esfenopalatina por videoendoscopia Lado: Bilateral (ambos) 
+ Sinais Vitais  
+ PA máx :  135  
+ PA mín :  85  
+ FR :  18  
+ FC :  72  
+ Temp :  36,4  
+ Peso :  85  
+ Dor :  0  
+ Altura(cm) :  180  
+ IMC :       26.23  
+ Histórico de Saúde (Clique com o botão direito e depois "Inserir e obter registros EHR") :  Arritmia 
+DLP 
+Hiperuricemia  
+ Capacidade Funcional :  &gt;4 METS *(Sobe dois lances de escada ou caminha por mais de 100m  no plano sem parar por dispneia)  
+ Exame físico cardiopulmonar alterado? :  não  
+  Outros exames físicos alterados? (Digestivo, genitourinário, sistema nervoso central, neuro músculo esquelético) :  não  
+ Antecedentes Cirúrgicos / Anestésicos (Clique com o botão direito e depois "Inserir e obter registros EHR") :  OutrasCirurgia:ureterolitiase   Tipo: 
+OutrasCirurgia:septoplastia   Tipo: 
+ColecistectomiaCirurgia:09/2025 
+ Intercorrências Anestesicas :  Não  
+ Dificuldade para intubar :  não  
+ Hipertermia maligna :  não  
+ Reação alérgica :  não  
+ Náuseas e Vômitos :  não  
+ Dificuldade p/ despertar :  não  
+ Faz uso de medicamento anticoagulantes? :  Não  
+ Faz uso de medicamento análogo do GLP1 (Ozempic, Wegovy, Mounjaro ou similares) :  Não  
+ Medicamentos de uso domiciliar (Clique com o botão direito e depois "Inserir e obter registros EHR") :  Concor 
+Zyloric 
+Lipless 
+Quetiapina  
+ Medicamentos/Suplementos de uso hospitalar. (Prescrições atuais) :  Soro glicosado 5% Sol 250mL - Dose: 250 ml - Última Adm.: 24/06/2026 17:16:51 
+ Alergias/ Reações Adversas (Clique com o botão direito e depois "Inserir e obter registros EHR") :  Alimentos:Frutos do Mar- 
+Iodo  
+ Hábitos  
+ Possui hábitos? :  sim  
+ Consumo de Álcool :  sim  
+ Observações :  Socialmente  
+ Antecedentes Neoplásicos  
+ Possui Antecedentes Neoplasicos? :  Não  
+ RT Prévia :  não  
+ QT Prévia :  não  
+ Tratamento Cirúrgico Prévio :  não  
+ Exames Laboratoriais  
+ Dados Laboratoriais: :  Paciente sem exames  
+ ECG :  Sem ECG  
+ Via Aérea  
+ Possui antecedente de via aérea difícil? :  Não  
+ Presença de Barba :  Não  
+ Antec. cirurgia ou RT Cervical :  Não  
+ Ausência de dentes :  Não  
+ Prótese dentária :  Não  
+ Abertura Oral :  &gt; 3cm  
+ Mandíbula :  Normal  
+ Mobilidade Atlanto Occipital :  Normal  
+ Distância Tireomentoniana :  &gt; 6,5cm  
+ Circunferência do Pescoço :  Normal  
+ Mallampatti :  III  
+ Condição dentária :  Boa  
+ Condição dentária  
+ Acessos  
+ Dificuldade para colher exames / venóclise :  Não  
+ Jejum iniciado às:  
+ Sólidos :  24/06/2026 12:00:00  
+ Líquidos :  24/06/2026 12:00:00  
+ Oriento início de jejum para às:  
+ Paciente sem jejum completo ou estômago cheio :  não  
+ Paciente elegível para o protocolo de abreviação de jejum? :  não  
+ Fatores de Risco para NVPO (Náuseas e vômitos pós operatório)  
+ Não Fumante :  sim  
+ Escore :  Escore menor ou igual a 2 - Um ou dois fatores de risco  
+ Recomendações :  Administrar 2 medicamentos de classes distintas  
+ Riscos  
+ ASA :  2  
+ Calcular riscos [Para recalcular, marcar o NÃO e sem seguida SIM novamente.] :  Sim  
+ Risco Clínico :  Risco Padrão (Equivalente ASA 1 ou 2 - possui menos de 70 anos e não possui comorbidades)  
+ Risco de VAD :  Risco Alto  
+ Risco de Broncoaspiração :  Risco Padrão  
+ Risco de Trauma Dentário :  Risco Alto  
+ Risco Acentuado de Sangramento :  Não  
+ Risco de Acesso Venoso Difícil :  Risco Padrão  
+ Risco de Ventilação Difícil :  Risco Padrão  
+ Risco de Delirium :  Risco Padrão  
+ Técnica Anestésica  
+ Geral :  sim  
+ Medicação Pré Anestésica :  não  
+ Se sim, a prescrição deve ser realizada no portal medico [PEP]  
+ Planejamento de Analgesia Pós operatório  
+ Reserva de UTI :  não  
+ Reserva de hemocomponentes :  não. Alta dia 24/06/2026 20:45  
+</t>
+        </is>
+      </c>
       <c r="G46" s="9" t="n"/>
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
@@ -12034,15 +13713,27 @@
       <c r="N46" s="9" t="n"/>
       <c r="O46" s="9" t="n"/>
       <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="9" t="n"/>
-      <c r="R46" s="9" t="n"/>
+      <c r="Q46" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="R46" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S46" s="10" t="n"/>
       <c r="T46" s="10" t="n"/>
       <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
+      <c r="V46" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="W46" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n">
+        <v>36.4</v>
+      </c>
       <c r="Z46" s="10" t="n"/>
       <c r="AA46" s="10" t="n"/>
       <c r="AB46" s="10" t="n"/>
@@ -12203,7 +13894,34 @@
       <c r="E47" s="8" t="n">
         <v>31038</v>
       </c>
-      <c r="F47" s="8" t="n"/>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo de Acionamento :  Não Urgência  
+ Motivo do Acionamento :  Ordem telefônica  
+ T(°C) :  35  
+ FC(bpm) :  81  
+ PAS(mmHg) :  106  
+ PAD(mmHg) :  65  
+ FR(irpm) :  18  
+ SaO2(%) :  97  
+ HMA :  A pedido da equipe assistente, incluo na prescrição: 
+receituário de papa-nicolau.  
+Atendo prontamente o pedido com a ressalva do tempo de levar fisicamente o pedido à enfermaria.  
+Enfermagem e equipe assistente confirmam a não necessidade de avaliação clínica presencial da nossa equipe neste momento. 
+- Realizada repetição da solicitação para comunicação em alça fechada 
+-  .  
+ Conduta :  1) realizo receituário de papa-nicolau.  
+----------------------------------------------------------------------------------------------------------  
+ Transferência para outra Unidade :  Não  
+ Houve contato com algum membro da equipe médica responsável pelo paciente? :  Contato realizado  
+ Nome do médico contactado :  Dra Natalia Arão.   
+ Elegível para protocolo institucional? :  Não  
+ Paciente Thais Adura Pepe esteve internada no Hospital Sírio Libanês no período de 25 a 26 de junho de 2026 devido a quadro de cansaço, dispnéia, sensação de coração acelerado e fraqueza de início recente e caráter progressivo.
+Submetida a exames e identificado anemia ferropriva secundária a menorragia.
+A paciente evoluiu bem durante a internação e recebeu alta com orientações, receita médica e retorno ambulatorial em 3 dias.Alta dia 26/06/2026 9:15
+</t>
+        </is>
+      </c>
       <c r="G47" s="9" t="n"/>
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
@@ -12214,8 +13932,14 @@
       <c r="N47" s="9" t="n"/>
       <c r="O47" s="9" t="n"/>
       <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="R47" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S47" s="10" t="n"/>
       <c r="T47" s="10" t="n"/>
       <c r="U47" s="10" t="n"/>
@@ -12383,7 +14107,67 @@
       <c r="E48" s="8" t="n">
         <v>31077</v>
       </c>
-      <c r="F48" s="8" t="n"/>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>HMA: paciente com antecedente de labirintopatia e epilepsia e estado de mal em contexto de endocardite + meningoencefalite. Já apresentou hiponatremia em contexto medicamentoso no passado, mantendo natremias levemente reduzidas. Internação recente em maio/2026. Realizou exames recentes em sua cidade que demonstrou uma ITU. Indicado Clavulin BD iniciado hoje antes do almoço. Por volta das 15h, começou a sentir tudo rodar, associado a náuseas, e diarreia, vômitos. Aferida PA, que estava muito alta (PAS 200 sic). Foi medicada com sintomáticos. Nega febre. Continua com vertigem e nauseada, com soluços e pontadas ocasionais na região mastoidea esquerda.
+Nesta semana apresentou outros picos pressóricos assintomática - PAS chegando a 200.
+AP: Endocardite infecciosa + pleocitose e estado de mal não convulsivo - meningoencefalite? (2021) / DAC com ATC 2021 / epilepsia focal / tremor essencial / QPA no começo de 2021 com período prolongado de restrição a mobilidade / Catarata
+MEDS:
+Keppra 750mg 3x/dia
+Clobazam 10mg noite
+Labirin 16mg 12x12h
+Domperidona 10mg antes das refeições
+Inzelm 20m jejum
+Livalo 2mg noite
+Ezetimiba 10mg noite
+Valsartana 80mg 12x12h
+Clopidogrel almoço
+Alenia 12/400 manhã
+Meds em ajuste:
+Labirin 16mg 2xd &gt; 16mg 3xd (26/06)
+Meclin 25mg 1xd (26/06)&gt; SN (04/07)
+NaCl 500mg 2xd (26/06) &gt; 1g 1xd (02/07)
+Keppra 750 mg 3xd&gt; 750-500-750 mg (01/07)
+Dramin 10 gts 8/8h&gt; SOS (30/06)
+EVOLUÇÃO:
+Paciente no leito, acomp. por familair.
+Sono noturno preservado.
+Durante visita vigil e cooperativa, com sintomas bem controlados. 
+Mantendo boa evolução e deambulação com fisio. 
+Controles estáveis. Evac 1x ontem e 1x hoje, em uso repoflor. 
+U1 controle sem alt.
+Mero 26/06 - 03/07
+Labs Na 124 &gt; 127&gt;129 &gt; 127 &gt; 129&gt; 127
+Sódio urinário 16,64 mEq/g (VR 42-332). Osm urinaria: 550 mOsm/Kg;  Osm sérica 270 mOsm/Kg
+NS Levetiracetam (27/06): 55,6
+TC de crânio - estável
+Torax - sem sinais de BCP
+Abdome - pequena hernia epigastrica 1,3cm
+Seios face - sinusopatia
+Ao exame neurológico:
+- Vigil, orientada, atenção preservada, sem alteração de linguagem.
+- PIFR, acuidade visual diminuída bilateralmente, MOE sem alterações, campos visuais preservados, mímica facial simétrica, sem nistagmos. 
+- Força grau IV em dimídio esquerdo. ROTs normoativos, exceto aquileus hipoativos.
+- Sensibilidade superficial e vibratória diminuída em dimídio esquerdo.
+- Índex-nariz com tremor leve à esquerda durante todo o movimento.
+- Tremor de ação em MMSS, sem bradicinesia.
+- Marcha não testada
+Impressão: tontura + vertigem e náuseas, associado a ingesta de medicação (clavulin)
+Conduta - Definida pelo chefe da equipe:
+- Alta com seguimento ambulatorial precoce, solicito exames laboratoriais para realizar ambulatorialmente
+- Lesão glútea por Herpes Simples - prescrevo Valaciclovir 1 g de 12 em 12 horas por 7 dias
+- Susp tamarine e entro com repoflor (03/07)
+- Guiado pelo NS reduzo Keppra 750-500-750 mg (01/07) 
+- Ajustado labirin para 16mg 3xd (26/06)
+- Prescrevo meclin SN (04/07)
+- Mantenho com Nacl 1g/dia (26/06)
+- Seguimento fisio motora e analgésica. 
+- Vigilância neurologica
+EXAMES:
+**TC crânio Alargamento difuso de sulcos corticais, fissuras encefálicas e cisternas basais, bem como do sistema ventricular supratentorial. Tênues hipodensidades da substância branca dos hemisférios cerebrais, sem efeito expansivo, inespecíficas. Restante do parênquima encefálico com atenuação preservada. Não há sinais de hemorragia intracraniana recente ou de coleções extra-axiais. Calcificações parietais nos segmentos intracavernosos das carótidas internas. Pequeno osteoma junto à tábua óssea interna craniana frontal esquerda. Impressão diagnóstica: Em comparação ao exame de 25/04/2026 não se observam alterações evolutivas significativas.
+**TC tórax Ateromatose difusa. Stents coronarianos. Estruturas vasculares do mediastino com calibre externo conservado. Demais estruturas mediastinais preservadas. Não se identificam linfonodomegalias mediastinais. Brônquio segmentar apical do lobo superior direito originário à partir do brônquio fonte direito (variante anatômica). Discreto espessamento difuso de paredes brônquicas. Alguns micronódulos pulmonares menores que 0,4 cm esparsos, uns calcificados (estes residuais) e os demais inespecíficos. Atelectasias lineares esparsas. Ausência de derrame pleural significativo. Impressão: Comparativamente ao exame anterior de 25/04/2026 não se observam alterações evolutivas significativas. Alta dia 04/07/2026 15:50</t>
+        </is>
+      </c>
       <c r="G48" s="9" t="n"/>
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
@@ -12394,17 +14178,29 @@
       <c r="N48" s="9" t="n"/>
       <c r="O48" s="9" t="n"/>
       <c r="P48" s="9" t="n"/>
-      <c r="Q48" s="9" t="n"/>
-      <c r="R48" s="9" t="n"/>
+      <c r="Q48" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="R48" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S48" s="10" t="n"/>
-      <c r="T48" s="10" t="n"/>
+      <c r="T48" s="10" t="n">
+        <v>200</v>
+      </c>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
       <c r="W48" s="10" t="n"/>
       <c r="X48" s="10" t="n"/>
       <c r="Y48" s="10" t="n"/>
       <c r="Z48" s="10" t="n"/>
-      <c r="AA48" s="10" t="n"/>
+      <c r="AA48" s="10" t="inlineStr">
+        <is>
+          <t>Deambulando</t>
+        </is>
+      </c>
       <c r="AB48" s="10" t="n"/>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -12563,7 +14359,80 @@
       <c r="E49" s="8" t="n">
         <v>31825</v>
       </c>
-      <c r="F49" s="8" t="n"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>HPMA: Sente que coração fica desparado constantemente. Gripe forte há cerca de 1 mês -&gt; FC 140-160bpm. Sat 87% -&gt; Acha que ainda está com sinusite -&gt; não tomou antibiótico -&gt; fez viagem pra Argentina após e com voo piorou - controlou cefaleia com paracetamol. 
+Há cerca de 2 meses, em viagem, não levou Inzelm e fez uso de omeprazol -&gt; relata ter tido dor precordial de forte intensidade após café da manhã - relata que ao sentar melhora. Teve um episodio de dor precordial em talvez um pico emocional também. Tem feito caminhadas - sente que fica ofegante - não tolera muito esforço. Esta com dor no ombro D -&gt; não tem feito musculação. Sente as vezes zumbido no ouvido E - geralmente quando movimenta cabeça - não nota piora após gripe. Acha que está mais inchada. Intestino mais constipado - geralmente precisa de Naturetti 
+ Equipes envolvidas: Mauricio Scanavaca // Rogério Tuma // Cyrillo 
+Prescrição de alta 
+1) BuPROPiona Tomar 300 mg Oral Uma vez ao dia 
+2) QUEtiapina Tomar 25 mg Oral Noite 
+3) Aspirina Prevent Tomar 100 mg Oral Uma vez ao dia 
+4) CLONAzepam 2,5mg/mL Tomar 12 gts Oral Noite 
+5) Eliquis Tomar 5 mg Oral 12 em 12 horas 
+6) Ezetimiba Tomar 10 mg Oral Uma vez ao dia 
+7) Livalo Tomar 4 mg Oral Uma vez ao dia 
+8) Magnen B6 722,2/1mg Cp rev Tomar 1 cp re Oral 12 em 12 horas -&gt; Relata que não sabe se está tomando 
+9) Pantoprazol Tomar 40 mg Oral Manhã -&gt; Inzelm 20mg 
+10) Valdoxan 25 
+11) Selozok 25mg Tomar 1 comp Oral Uma vez ao dia 
+&gt; aldactone 25mg Tomar 1 cp oral uma vez ao dia  
+ Objetivo de cuidado conforme discutido com paciente e/ou familiares/ responsáveis, em caso de deterioração clínica:  
+ Status Pleno. Paciente candidato a medidas de suporte artificial de vida (RCP, IOT, etc.). :  sim  
+ Paciente candidato a medidas clínicas não-invasivas. Contraindicadas medidas invasivas de suporte artificial de vida. :  não  
+ Garantir controle de sintomas e permitir processo de morte de forma mais natural e mais confortável possível. :  não  
+ Paciente com necessidade de controle de sintomas:  
+ Equipe Médica :  Roberto Kalil Filho  
+ Alergias :  Nega existência de Alergias, 
+Chocolate, melão, melancia, pepino, 
+ Diagnósticos e Lista de problemas :  Piora do cansaço 
+Miocardite pós quadro gripal 
+FA de baixa resposta com piora clínica - CVE em 29/06 com sucesso 
+Dor em ombro D  
+ Antecedentes Pessoais :  # AP: 
+- Dislipidemia - Lpa 220nmol/l 
+- Ablação de flutter 06/03/2026 
+- Wake-up stroke 09/11/25 não trombolisado -&gt; AngioTC: Oclusão de ACMD M2 - Rogerio Tuma 
+- Angioplastia de Carótida Interna Direita  (13/11/25) - Jose Guilherme Caldas 
+- PO (22/08/23) de retirada de Tumoração em átrio direito (característica de tecido gorduroso + Muscular) - Dr Fabio Jatene -&gt; Ritmo juncional pós cirurgia - marcapasso provisório 
+- Lesão lipomatosa em atrio D - estável desde 2024 
+- Nodulo de papila duodenal maior &gt; adenoma - ressecado em 09/2024 (Dr. Fernando Marson) 
+- PO (03/24): Troca de protese mamaria bilateral: delocada em cirurgia cardiaca previa - plastico Marcelo Sampaio (internação 17 a 20/03/24) 
+- Melanoma 2x (perna e costas) - ultimo 2022 
+- Ex tabagista desde nov 2025 
+- COVID (2020, 2023) - Em 2020 não precisou internar, mas apresentou comprometimento pulmonar SIC (sem necessidade de O2)  
+ Diagnósticos Sindrômicos durante a internação  
+ Profilaxias  
+ Avaliação TEV não se aplica. Paciente menor de 18 anos. :  não  
+ Evolução  
+ Evolução/Impressão Clínica :  #Evolução Uco# 
+Paciente estavel hemodinamicamente, sem intercorrencias, mantendo bom padrao respiratorio em ar ambiente. 
+Segue afebril, pcr em queda/ estavel,  em uso de atb ( zinnat d5). 
+Função renal estavel. 
+Recebe eliquis 5mg 2x + colchicina 
+s/ lab  
+ECG de controle - Ritmo  juncional  (ainda em fase de recuperação pos sedação) 
+ECG 30/06/2026   - ritmo atrial / sinusal estável.  
+Estável, mantendo FC em torno  de 60 a 70 bpm 
+Controle 
+Afebril 
+PA e Fc estaveis 
+BH 440 
+DUperdas 
+Exame físico: PA (mmHg)121 / 66PAM (mmHg)88FC(bpm)72T (ºC)36 
+Corada, hidratada, eupneica, orientada  
+RCR, 2T, sem sopros  FC 60  
+MV+, sem RA  
+Abd: inocente  
+Ext: ppp, sem edema ou cianose  
+ Condutas :  CD: 
+Recorrencia  da TA  pos ablação em 03/2026 em paciente com lipoma que envolve Atrios e septo com RM mostranso edema e fibrose em segumento infersseptal medio  
+- manter colchicina e amiodarona  100mg  - Holter e lab de controle em 30 dias  
+programação de alta hj  
+Suporte uco  
+    Alta dia 01/07/2026 15:40</t>
+        </is>
+      </c>
       <c r="G49" s="9" t="n"/>
       <c r="H49" s="9" t="n"/>
       <c r="I49" s="9" t="n"/>
@@ -12574,12 +14443,20 @@
       <c r="N49" s="9" t="n"/>
       <c r="O49" s="9" t="n"/>
       <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="9" t="n"/>
+      <c r="Q49" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="R49" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S49" s="10" t="n"/>
       <c r="T49" s="10" t="n"/>
       <c r="U49" s="10" t="n"/>
-      <c r="V49" s="10" t="n"/>
+      <c r="V49" s="10" t="n">
+        <v>60</v>
+      </c>
       <c r="W49" s="10" t="n"/>
       <c r="X49" s="10" t="n"/>
       <c r="Y49" s="10" t="n"/>
@@ -12588,9 +14465,17 @@
       <c r="AB49" s="10" t="n"/>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="10" t="n"/>
+      <c r="AE49" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF49" s="10" t="n"/>
-      <c r="AG49" s="10" t="n"/>
+      <c r="AG49" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH49" s="10" t="n"/>
       <c r="AI49" s="10" t="n"/>
       <c r="AJ49" s="10" t="n"/>
@@ -12743,7 +14628,38 @@
       <c r="E50" s="8" t="n">
         <v>31866</v>
       </c>
-      <c r="F50" s="8" t="n"/>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>HD: Provável Linfoma de células do Manto
+&gt; Clínica: Sintomas constitucionais + linfocitose + esplneomgelia sintomática + linfonodomegalias periféricas discreta
+&gt; IFT SP (HIAE GO - 18/06/26): 50,9% de células B anômalas, CD5+ (forte), CD11c+ (fraco), CD20+ (forte), CD79b+ (moderado), CD22+ (moderado), CD23+ (moderado), FMC-7+ (fraco), Lambda + (moderado); CD10-, CD25-, CD38-, CD43-, CD103-, CD123-, Cd200-. Conclusão: Linfoma de células do Manto?
+&gt; PET-CT (24/06/26 - HSL): aguarda laudo
+&gt; IFT SP 26/6/26 HSL: aguarda laudo 
+# HPMA: Paciente com antecedente de neoplasia renal de células claras, atualmente em remissão, evolui com sintomas consticuionais, linfonodomegalias e esplenoemgalia sintomática. IFT de SP externa sugestiva de LCM.
+# AP
+Neoplasia renal de células claras - tratamento previo com pembrolizumabe
+Hipotiroidismo (Hashimoto) 
+# MUC
+Frontal 0,5mg/dia
+LT4 125mcg
+Arcalion 
+# Evolução: avalio paciente no leito, acompanhado da esposa Mônica no momento da visita. Clinicamente estável. Realizada ontem biópsia por radiointervenção de linfonodo axilar esquerdo, sem intercorrências. Recebeu no período noturno Rituximabe, com queixa apenas de eritema autolimitado nos pés, sem demais intercorrências. Queixa-se de dor leve em região cervical posterior. 
+# Ao exame: 
+BEG, corado, hidratado eupneico, afebril
+Linfonodomegalias palpáveis em região inguinal e axilares bilaterais de até 2,5cm. 
+ACV BRNF em 2 tempos, sem sopros
+AR: MV+ bilateralmente, sem ruídos adventícios 
+ABD: Baço palpável a 3 polpas digitais do RCE.
+# Exames complementares 
+- 27/6/26: beta2microglobulina 3,0 
+- Sorologias 26/6/26: anti-HBs 55,9, HBsAg NR, HCV NR, HIV NR
+- EcoTT 26/6/26: FE 70%, Aumento discreto de raiz aórtica e aorta ascendente. Insuficiência aórtica discreta. Cavidades cardíacas de dimensões normais. Espessura miocárdica normal. Índice de massa miocárdica normal. Ventrículo esquerdo apresenta função sistólica preservada, não sendo observadas alterações na contratilidade segmentar de parede. Índices de função diastólica normais. Ventrículo direito apresenta função sistólica normal (TAPSE = 30mm). Valva mitral apresenta aspecto e movimentação normais das cúspides. O estudo Doppler e mapeamento com fluxo em cores demonstram refluxo de grau mínimo. Valva aórtica trivalvular com válvulas finas, abertura e mobilidade preservadas. O estudo Doppler e mapeamento com fluxo em cores demonstram refluxo de grau discreto. Valva tricúspide apresenta aspecto e movimentação normais das cúspides. O estudo Doppler e mapeamento com fluxo em cores demonstram refluxo de grau discreto. Valva pulmonar apresenta aspecto e movimentação normais das válvulas. O estudo Doppler e mapeamento com fluxo em cores são normais. Pressão sistólica pulmonar estimada em 25 mmHg (VR &lt; 35 mmHg), a pressão no átrio direito presumida em 03 mmHg e a velocidade máxima do refluxo tricúspide de 2,34 m/s (VR ≤ 2,8 m/s). Veia cava inferior de diâmetro normal (16mm) e variação respiratória &gt; 50%. Seios aórticos (45mm - 22mm/m²) e aorta ascendente (42mm - 20mm/m²) com aumento discreto. Pericárdio sem sinais de derrame
+# Conduta:
+- Realizado Rituximabe 26/6/26 sem intercorrências. Em programação de início de Acalabrutinibe 
+- Alta hospitalar com retorno ambulatorial próxima semana com Dr. Celso Arrais para checar resultados de exames pendentes
+- Aguarda: laudo PET CT 24/6/26 | IFSP 26/6/26 | AP + IHQ Bx linfonodo axilar E (SUV 9,8 2,5cm) 26/6/26 | EFP 27/6/26 | Anti-HBc total 27/6/26 . Alta dia 27/06/2026 11:42</t>
+        </is>
+      </c>
       <c r="G50" s="9" t="n"/>
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
@@ -12754,9 +14670,19 @@
       <c r="N50" s="9" t="n"/>
       <c r="O50" s="9" t="n"/>
       <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
-      <c r="R50" s="9" t="n"/>
-      <c r="S50" s="10" t="n"/>
+      <c r="Q50" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="R50" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T50" s="10" t="n"/>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
@@ -12768,7 +14694,11 @@
       <c r="AB50" s="10" t="n"/>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
-      <c r="AE50" s="10" t="n"/>
+      <c r="AE50" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF50" s="10" t="n"/>
       <c r="AG50" s="10" t="n"/>
       <c r="AH50" s="10" t="n"/>
@@ -12923,7 +14853,54 @@
       <c r="E51" s="8" t="n">
         <v>31873</v>
       </c>
-      <c r="F51" s="8" t="n"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>HMA :  Sou chamado a pedido da médica responsável para avaliar paciente por extravasamento de contraste ocorrido ontem durante tomografia, acometendo MSD.. 
+Paciente refere estar assintomático, não sente dor no local, está com movimentação normal no membro e nas mãos, nega parestesia.  
+Ao exame, apresenta edema2+ localizado em fossa antecubital com extensão para terço distal do braço e terço proximal do antebraço, sem sinais flogísticos, não doloroso à palpação, mobilidade articular do cotovelo preservada, pulsos cheios e boa perfusão periférica.  
+ Conduta :  1) Discutido com Dra. Isabela, que orienta solicitar USG de partes moles. Manter medidas locais orientadas pela equipe da radiologia. 
+----------------------------------------------------------------------------------------------------------  
+ Transferência para outra Unidade :  Não  
+ Houve contato com algum membro da equipe médica responsável pelo paciente? :  Contato realizado  
+ Nome do médico contactado :  Dra. Isabela  
+ Elegível para protocolo institucional? :  Não  
+ HPMA: Paciente relata dor em articulações do joelho com diagnóstico prévio de osteoartrite e tratamento com fisioterapia e infiltração com melhora parcial. Passou hoje em nova avaliação ortopédica com Dr Marcelo Filardis (HIAE). Paciente realizou RM de joelho em Ribeirão Preto e mostrou ao especialista porém não trouxe hoje. Confirmada osteoartrite com orientação de tratamento conservador com joelheira, fisioterapia e crioterapia. Ultima internação no HSL há 6 meses por pneumotórax espontâneo. 
+AP: 
+- Internação 20/11-28/11/25: PO (22/11/25) Segmentectomia extra-anatômica envolvendo a base parenquimatosa da bolha à D + Pleurectoma - Dr Angelo Fernandes 
+&gt; PO (16/11/25) drenagem pneumotórax espontâneo à D (Hospital São Lucas - Ribeirão Preto) 
+- DAC c/ POT RM (1998) e ATC -&gt; última ATC em Maio/25: 3 stents farmac Cx/MgE1, DP (pós anastomose com PVS) e em enxerto PVS-Dg - Hipotireoidismo 
+- Glicemia alterada 
+- Flutter em ACO com Eliquis 
+- DPOC 
+- HPB - cirurgia há &gt;10 anos (Dr Luciano Nesrallah) 
+- Ex Tabagista, cessou há 40 anos 
+ALÉRGICO À QUINOLONA 
+Em uso de: 
+1) Pantoprazol 40mg Tomar 40 mg Oral Manhã
+2) Synthroid Tomar 137 mcg Oral Jejum
+3) Eliquis Tomar 5 mg oral 12/12h
+4) Aradois Tomar 50 mg oral 12/12h
+5) Trezete 20/10mg Tomar 1 comp oral 1x ao dia 
+6) Norvasc Tomar 10 oral oral 1x ao dia
+7) Selozok Tomar 50 mg oral 12/12h
+8) Natrilix SR 1,5mg Tomar 1 comp oral manha
+9) Ancoron 200mg Tomar 01cp de 12/12h de segunda a sexta 
+Monjauro há 3 dias 
+Exame físico: 
+RCR 2T BNF SS 
+MV preservado sRA 
+Abdome flácido indolor 
+MMII sem edemas 
+TEC 2 seg 
+ECG consultório hoje: Flutter atrial de baixa resposta, FC 47bpm 
+Conduta: 
+- Solicito laboratório, ECG. 
+- ECOTT e USGs a serem realizados amanhã.
+- Angiotcs a serem realizadas hoje. 
+- EDA e colonoscopia há 2 anos em Ribeirão Preto com retirada de 1 pólipo, benigno SIC. Não realizaremos neste momento. Uso de monjauro há 3 dias e em uso de ACO. 
+. ALTA DIA 26/06/2026 13:46</t>
+        </is>
+      </c>
       <c r="G51" s="9" t="n"/>
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="9" t="n"/>
@@ -12934,12 +14911,20 @@
       <c r="N51" s="9" t="n"/>
       <c r="O51" s="9" t="n"/>
       <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
-      <c r="R51" s="9" t="n"/>
+      <c r="Q51" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="R51" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S51" s="10" t="n"/>
       <c r="T51" s="10" t="n"/>
       <c r="U51" s="10" t="n"/>
-      <c r="V51" s="10" t="n"/>
+      <c r="V51" s="10" t="n">
+        <v>47</v>
+      </c>
       <c r="W51" s="10" t="n"/>
       <c r="X51" s="10" t="n"/>
       <c r="Y51" s="10" t="n"/>
@@ -13103,7 +15088,61 @@
       <c r="E52" s="8" t="n">
         <v>31918</v>
       </c>
-      <c r="F52" s="8" t="n"/>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Paciente interna devido a cansaço e refere palpitações esporádicas. Alpem disso refere por vezes queimação em hemitorax esquerdo, sem fatores de piora ou melhora
+Em acompanhamento ginecologico com Dr Nilton Roberto que orientou manter Tibolona e orientou associar anel vaginal com liberação lenta de testosterona 1x/mes 
+AP:
+Hipotireoidismo (nodulo previo -&gt; PAAF benigno)
+Anemia ferropriva
+Sincopes previas SIC
+DAC não obstrutiva (cate 05/2023)-&gt; DG1 (41%) e CX (41%)
+Nega HAS, DM, DLP
+Alergia (por contato); prurido as vezes com antiinflamatórico
+Sedentária
+Ex tabagista (parou há 30 anos)
+Nega etilismo
+Cirurgias: colecistectomia, apendicectomia, cesárea, bariátrica, cirurgia plástica, lifting facial em jun/22, lifting facial e cervical em jun/24
+Furunculose glútea
+COVID 2022 - sintomas leves
+Herpes zoster 2022
+AF: pai HAS/ morte subita aos 68 anos, mãe AVC aos 70 anos. Tia câncer de intestino aos 60 anos
+Em uso de:
+1) Rosuvastina
+Tomar 10 mg Oral Noite
+2) Synthroid 112mcg
+Tomar 112 mcg Oral Manhã 
+3) Aymee (vilazodona) 20mg (Pelo Dr. Paulo Camis)
+4) Clonazepam 0,25mg
+5) Clopidogrel 75mg (Pelo Neuro - ateromatose intracraniana)
+Tomar 01 cp via oral 1x ao dia
++
+VitD 5000ui 1x/dia
+Creatina
+Palatinose
+Polivitaminico
+Ozempic 0,25 SC 1x/sem
+Tibolona 2,5mg 1x/dia
+Anel vaginal testoterona
+Nega alergias medicamentosas, nega alergia a contraste
+Evolução: 
+Evolui bem, estável, sem queixas hoje. 
+EF:
+Corada, hidratada
+BRNF em 2T, sem sopros
+MV+, sem RA
+Abdome inocente
+Extremidades sem edema
+EXAMES FLEURY
+LABS 09/06/26: UR 32 G 89 CR 0,87 PCR 0,15 TGO 32 TGP 37 GGT 12 FA 57 BT 0,29 PTN TOTAL 6,3 ALB 4 COAGULOGRAMA NORMAL NA 143 K 4,7 UR 32 CAI 1,2 MG 2,1 FOSFO 3,9 LDL 63 COELST TOTAL 113 HDL 36 TRIGLIC 49 HB1AC 5,7 AC URICO 4,9 HB 13 LEUCO 4630 PLQ 264000 FERRITINA 62 IST 24 FERRO 81 VITB12 547 AC FOLICO 11 HOMOCISTEINA 9 TSH 2,5 T4L 1,5TESTO 3 PTH 37 VIT D 24
+ELETROFORRESE DE PTN NORMAIS
+Condutas:
+Aguara ECO hoje
+Reavaliar alta após exames 
+Na alta programaremos exame de holter ambulatorialmente
+Realizou exame de mamografia, usg de mama e transvaginal no fleury hoje - aguarda laudo. Alta dia 26/06/2026 18:05</t>
+        </is>
+      </c>
       <c r="G52" s="9" t="n"/>
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
@@ -13114,8 +15153,14 @@
       <c r="N52" s="9" t="n"/>
       <c r="O52" s="9" t="n"/>
       <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
-      <c r="R52" s="9" t="n"/>
+      <c r="Q52" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="R52" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
@@ -13156,7 +15201,9 @@
       <c r="BD52" s="11" t="n"/>
       <c r="BE52" s="11" t="n"/>
       <c r="BF52" s="11" t="n"/>
-      <c r="BG52" s="11" t="n"/>
+      <c r="BG52" s="11" t="n">
+        <v>0.87</v>
+      </c>
       <c r="BH52" s="11" t="n"/>
       <c r="BI52" s="11" t="n"/>
       <c r="BJ52" s="11" t="n"/>
@@ -13283,7 +15330,43 @@
       <c r="E53" s="8" t="n">
         <v>32554</v>
       </c>
-      <c r="F53" s="8" t="n"/>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Paciente evoluindo estável hemodinamicamente , confortável em ar ambiente, SEM QUEIXAS. - hematoma em região de frontal direita, palpebras a direita e infraorbitário D.  
+CONTROLES - Afebril, PA = 100X60 - 130X80 FC = 76 - 80 DIURESE = perdas  
+Ao Exame: 
+BEG, CHAAAE PA 120x70 FC 66 bpm SpO2 98% AA , presença de hematoma subgaleal a direita 
+MV + bilat sem RA,  
+BRNF 2t sem sopros  
+Abdome: indolor, RHA presente. 
+mmii sem edema 
+RNM Crânio: Leve acentuação das vias circulação liquórica em detrimento parênquima encefálico, sem predomínio regional evidente. Alterações focais de sinal esparsas na substância branca cerebral bilateral, inespecíficas, podem representar focos de gliose e/ou microangiopatia. Espessamento das partes moles extracranianas frontais e periorbitárias superiores à direita, no contexto clínico de provável natureza contusional. Sinusopatia esfenoidal esquerda, com tênue nível líquido.Tortuosidade difusa dos ramos arteriais supra-aórticos e cervicais. Sinais incipientes de ateromatose carotídea e vertebral, sem condicionar estenoses focais significativas. 
+EEG: sem anormalidade 
+Eco TT: FE preservada. DDVE tipo I. 
+ECG: ARV  
+TC Cranio/Seios da face: Hematoma subgaleal frontal à direita. Fratura cominutiva do osso nasal e do processo frontal da maxila à direita, com desalinhamento estimado com cerca de 1 mm entre os fragmentos, bem como sinais de fratura do septo nasal e laterorrinia esquerda. Espessamento e densificação da pele da região nasal bilateralmente e da mucosa nasal à direita. 
+DTC - Principais exames da internação: 
+DTC (30/06): apenas ateromatose carotídea direita sem estenose significativa; padrão circulatório encefálico adequado; ausência de insuficiência vertebrobasilar; sem evidência de embolia encefálica arterioarterial; teste de microbolhas positivo para comunicação direita-esquerda de moderada condutância; Evidência funcional de disautonomia microcirculatória encefálica. 
+RM de crânio (29/06): apenas alterações de partes moles de natureza contusional frontal e periorbital direita.  AngioRM arterial e venosa: sem alterações significativas.  
+ Condutas :  Aguarda termino de Holter 24h 
+Hoje TILT TEST 
+Vigilancia de ritmo.HMA: Paciente conta que há mais de 20 anos sente instabilidade ao levantar rapidamente e que sempre precisa levantar com cuidado e devgar. Hoje, por volta das 12h, após se levantar rapidamente, apresentou síncope, com queda e TCE (fratura de maxila/ osso nasal). Logo após a queda já acordou rapidamente, orientada em tempo e espaço, e nao apresentou déficits neurológicos, abalos de membros e nem liberação esfincteriana.
+Antecedentes Pessoais :
+- TEP e TVP em nov/2021 - uso de Eliquis por 1 ano (refere investigação de trombofilia - negativa; não realizou PET)
+- Hipotireoidismo
+- Enxaqueca em uso de Zoloft e Engalit
+- Febre familiar do mediterrâneo (diagnóstico por teste genético) : uso de colchicina - apendicectomia 29/03/25
+- neurite occipital
+Em uso de cymbalta 60mg, colchicina, pregabalina 75 mg/d, monjauro 7,5mg (ultima dose dia 26/06
+Evolução:
+Paciente em leito sem acompanhantes.
+Sono noturno preservado.
+Durante visita vigil e cooperativa, sem recorrência de sintomas.
+Controles estáveis, PA oscilar - evento de 90/60
+Sem labs hoje  
+. Alta dia 01/07/2026 18:53</t>
+        </is>
+      </c>
       <c r="G53" s="9" t="n"/>
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="9" t="n"/>
@@ -13294,23 +15377,49 @@
       <c r="N53" s="9" t="n"/>
       <c r="O53" s="9" t="n"/>
       <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
-      <c r="R53" s="9" t="n"/>
-      <c r="S53" s="10" t="n"/>
-      <c r="T53" s="10" t="n"/>
-      <c r="U53" s="10" t="n"/>
-      <c r="V53" s="10" t="n"/>
+      <c r="Q53" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="R53" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
+      <c r="T53" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="U53" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="V53" s="10" t="n">
+        <v>66</v>
+      </c>
       <c r="W53" s="10" t="n"/>
-      <c r="X53" s="10" t="n"/>
+      <c r="X53" s="10" t="n">
+        <v>98</v>
+      </c>
       <c r="Y53" s="10" t="n"/>
       <c r="Z53" s="10" t="n"/>
       <c r="AA53" s="10" t="n"/>
       <c r="AB53" s="10" t="n"/>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
-      <c r="AE53" s="10" t="n"/>
+      <c r="AE53" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF53" s="10" t="n"/>
-      <c r="AG53" s="10" t="n"/>
+      <c r="AG53" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH53" s="10" t="n"/>
       <c r="AI53" s="10" t="n"/>
       <c r="AJ53" s="10" t="n"/>
@@ -13463,7 +15572,44 @@
       <c r="E54" s="8" t="n">
         <v>32586</v>
       </c>
-      <c r="F54" s="8" t="n"/>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>HDs:
+Síncope desliga-liga
+Politrauma com TCE e HSDA 
+AngioCT coronaria suspeita de lesão de tronco
+HMA:
+Paciente por volta das 14h00 vitima de acidente automobilitico, carro vs anteparo. 
+Relata que estava dirigindo quando na Rodovia Castelo Branco e quando percebeu estava sendo atendido pela 
+equipe de emergencia da Rodovia. Refere que não apresntou prodromos ou quaisquer outros sintomas. 
+Atendido na cena, já com consciencia recobrada e foi encaminhado ao Hospital de Araçariguama. Lá foi atendido, realizado exames e liberado para dar continuidade ao atendimento neste hospital. 
+Familiares relatam que nos últimos dias, funcionária vem percebendo que paciente vem apresentando confusão temporal, não habitual. 
+Genro relata que já apresentou quadro de síncope semelhante há aproximadamente 4 anos durante episodio de COVID.
+AP:
+- HAS
+- DLP
+- Insônia
+- Déficit cognitivo leve
+MUC:
+Anlodipino 5mg 2x/dia
+Repatha 
+Dozemast 
+Isotretinoina 2x semana (?)
+Donaren 50mg 
+Inzelm 20mg 
+Desloratadina 5mg
+Rivotril para dormir (irregular)
+Evolução:
+Paciente clinicamente bem, sem sintomas cardiovasculares no período, TC de cranio estavel
+Ao exame:
+BEG, corado, hidratado
+MV + sem RA AA confortável 
+RCR em 2T sem sopros
+ABD - flácido e indolor
+Equimose em região periorbital a esquerda praticamente reabsorvida
+Sutura em região supraorbitária E com boa cicatrização. Alta dia 09/07/2026 17:43</t>
+        </is>
+      </c>
       <c r="G54" s="9" t="n"/>
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
@@ -13474,9 +15620,19 @@
       <c r="N54" s="9" t="n"/>
       <c r="O54" s="9" t="n"/>
       <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="9" t="n"/>
-      <c r="R54" s="9" t="n"/>
-      <c r="S54" s="10" t="n"/>
+      <c r="Q54" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T54" s="10" t="n"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
@@ -13823,7 +15979,45 @@
       <c r="E56" s="8" t="n">
         <v>32601</v>
       </c>
-      <c r="F56" s="8" t="n"/>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HD:
+# 17º PO drenagem de hematoma subdural bilateral maior E 
+# hipotensão liquorica com fistula liquorica - coleção laminar extensa cervical ate toracica 
+# 11 º POTratamento para fístula liquorica (blood patch e cola)
+# Evolução:
+Paciente na UCG, acompanhado de esposa. 
+persiste lentificado mas afebril T max 37,4C 
+as vezes tem difucldade para manipular os talheres 
+D1 vanco e mero 
+ainda sem foco identificado .
+ EF = desperto, orientado, algo desatento e lentificado 
+sustenta bem os membros, mantendo diminuição de velocidade a E OE: Melhora da OIN 
+sem ataxia
+Horner à D - semiptose  sem miose 
+RFM presente 
+TC cranio 13/7: - discrto aumento da coleção subdural a D antes 0,8 cm e hj 1,0 cm mas mantendo  redução dos sinais de hipotensão liquórica, com reexpansão das cisternas da fossa posterior, aumento da distância mamilo pontina e redução do rebaixamento do tronco encefálico. Reexpansão dos cornos temporais dos ventrículos laterais. Reabsorção parcial do pneumocrânio com predomínio bifrontal. 
+TC cranio 15/7:  A análise comparativa com estudo realizado em 13/07/2026 evidencia: Aumento das dimensões da coleção extra-axial subdural hemisférica direita, com atenuação heterogênea e espessura de até 1,3 cm no plano coronal (media 1,0 cm no mesmo nível no estudo anterior), determinando compressão sobre o parênquima encefálico e redução da amplitude do corno frontal do ventrículo lateral deste lado, com desvio de estruturas da linha mediana para a esquerda, estimado em 0,7 cm, no plano do septo pelúcido. Semelhante a coleção extra-axial subdural hemisférica esquerda, com atenuação heterogênea, exibindo áreas hiperatenuantes de permeio e espessura de até 0,7 cm no plano coronal. 
+CD: Manter antibioticoterapia, vigilância infecciosa
+culturas neg
+ RNM de coluna cervical e toracica  recidiva da filstula
+cd npvp procedimento em 4 dias - 96 hs de atb e afebril .n  Evolução diurna UCG 
+Realizou TC de cranio de controle hoje  
+Neuro: vigil, orientado, sem cefaleia. Hemiparesia IV + a esquerda 
+Em uso de Levatiracetan 750mg 2x 
+AR: MVUA s/ RA, eupneico em ar ambiente 
+ACV: Sinusal, estável sem DVA. TEC &lt;3s  
+TGI: Abdome flacido, indolor, dieta  via oral , evacuou 
+R/M Du espontanea espontâneo; Cr 0,97  
+H/I: Afebril; Vancomicina + meropenem. PCR   queda  
+HMC PN  
+HNF  
+ Condutas :  - Aumentado dose de vancomicina por pk/pd 
+- Conforme neurologia, manter repouso relativo. Liberado para ir ao banheiro. Evitar caminhar fora do leito 
+- Programação de novo blood-patch + cola no dia 20-21/07  
+</t>
+        </is>
+      </c>
       <c r="G56" s="9" t="n"/>
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="n"/>
@@ -13834,8 +16028,14 @@
       <c r="N56" s="9" t="n"/>
       <c r="O56" s="9" t="n"/>
       <c r="P56" s="9" t="n"/>
-      <c r="Q56" s="9" t="n"/>
-      <c r="R56" s="9" t="n"/>
+      <c r="Q56" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="R56" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S56" s="10" t="n"/>
       <c r="T56" s="10" t="n"/>
       <c r="U56" s="10" t="n"/>
@@ -13848,12 +16048,24 @@
       <c r="AB56" s="10" t="n"/>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
-      <c r="AE56" s="10" t="n"/>
+      <c r="AE56" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF56" s="10" t="n"/>
-      <c r="AG56" s="10" t="n"/>
+      <c r="AG56" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH56" s="10" t="n"/>
       <c r="AI56" s="10" t="n"/>
-      <c r="AJ56" s="10" t="n"/>
+      <c r="AJ56" s="10" t="inlineStr">
+        <is>
+          <t>Oral</t>
+        </is>
+      </c>
       <c r="AK56" s="10" t="n"/>
       <c r="AL56" s="10" t="n"/>
       <c r="AM56" s="10" t="n"/>
@@ -13876,7 +16088,9 @@
       <c r="BD56" s="11" t="n"/>
       <c r="BE56" s="11" t="n"/>
       <c r="BF56" s="11" t="n"/>
-      <c r="BG56" s="11" t="n"/>
+      <c r="BG56" s="11" t="n">
+        <v>0.97</v>
+      </c>
       <c r="BH56" s="11" t="n"/>
       <c r="BI56" s="11" t="n"/>
       <c r="BJ56" s="11" t="n"/>
@@ -14134,7 +16348,11 @@
       <c r="AB57" s="10" t="n"/>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="10" t="n"/>
+      <c r="AE57" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF57" s="10" t="n"/>
       <c r="AG57" s="10" t="inlineStr">
         <is>
@@ -15305,7 +17523,33 @@
       <c r="E62" s="8" t="n">
         <v>33772</v>
       </c>
-      <c r="F62" s="8" t="n"/>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>HPMA: Paciente refere que ha cerca de 1 semana iniciou com quadro de dor e abaulamento em região glutea a esquerda. Nega febre e saida de secreção pelo anus na ocasiao. Procurou PS do sirio e foi liberada com cefadroxila. Refere ter feito uso da medicação, porém retorna ontem devido a persistencia da dor e aumento do abaulamento gluteo. Nega procedimentos esteticos no local, nega febre, nega descarga purulenta pelo anus/pele
+AP: Nega comorbidades
+Alergia: Buscopam e plasil 
+Nega MUC 
+Nega cirurgias previas 
+Avaliação: Paciente em leito de enfermaria, estavel clinica e hemodinamicamente, com nauseas e dor em gluteo a esquerda 
+EF: 
+REG, CHAAA
+Abdome: plano, flacido, indolor a palpação
+Região glutea: Presença de abaulamento endurecido, sem ponto de flutuação e hiperemia local, doloroso. Paciente nao tolera toque retal por dor 
+Labs:
+28/06: Hb 12,2/ leuco 13430/ plaquetas 360000/ Cr 0,75/ PCR 43/ U 25
+TC abdome e pelve 28/06/26: Densificação dos planos adiposos glúteos à esquerda, na sua porção medial e inferior, se estendendo até a fossa isquioanal esquerda. Nota-se provável trajeto fistuloso com a região anal, na sua parede lateral esquerda. Não há coleções bem delimitadas (lâminas líquidas não coletadas). Bexiga com pequena repleção e conteúdo homogêneo. Ausência de líquido livre na pelve. Não se identificam linfonodomegalias pélvicas. 
+Rm pelve 28/06: Coleção de contornos lobulados no subcutâneo da região glútea esquerda, estendendo-se para a região perianal e para a fossa isquioanal ipsilateral, com provável exteriorização pela superfície cutânea do sulco interglúteo à esquerda. Apresenta limites parcialmente imprecisos e volume estimado em cerca de 60 mL. Associa-se edema dos planos adiposos adjacentes à coleção supracitada, de aspecto inflamatório. Nota-se aparente orifício mucoso localizado às 2 horas do canal anal (de avaliação limitada pelas alterações inflamatórias relacionadas à coleção supracitada, cerca de 2,0 cm da borda anal e aparente continuidade com a coleção. 
+Impressão: Paciente com abscesso perianal mais profundo à pele, com provavel fistula as 2hs vista em rm de pelve 
+#Conduta:
+-Jejum + soro de manutenção 
+-Solicito labs hoje com coagulograma 
+-Indicado exame sob narcose .+ drenagem de abscesso em CC hoje as 18:00 hs 
+-Explico sobre procedimento, bem como possibilidade de drenos e sedenho, tempo de internação, possiveis complicações e proximos passos no tratamento. Paciente e acompanhante (Sra Graça) cientes e concordantes 
+-Assino termo cirurgico 
+-Demarco lateralidade conforme orientado pela equipe de enfermagem 
+ALTA DIA 30/06/2026 8:55</t>
+        </is>
+      </c>
       <c r="G62" s="9" t="n"/>
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="9" t="n"/>
@@ -15316,9 +17560,19 @@
       <c r="N62" s="9" t="n"/>
       <c r="O62" s="9" t="n"/>
       <c r="P62" s="9" t="n"/>
-      <c r="Q62" s="9" t="n"/>
-      <c r="R62" s="9" t="n"/>
-      <c r="S62" s="10" t="n"/>
+      <c r="Q62" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="R62" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>REG – Regular Estado Geral</t>
+        </is>
+      </c>
       <c r="T62" s="10" t="n"/>
       <c r="U62" s="10" t="n"/>
       <c r="V62" s="10" t="n"/>
@@ -15358,7 +17612,9 @@
       <c r="BD62" s="11" t="n"/>
       <c r="BE62" s="11" t="n"/>
       <c r="BF62" s="11" t="n"/>
-      <c r="BG62" s="11" t="n"/>
+      <c r="BG62" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="BH62" s="11" t="n"/>
       <c r="BI62" s="11" t="n"/>
       <c r="BJ62" s="11" t="n"/>
@@ -15485,7 +17741,62 @@
       <c r="E63" s="8" t="n">
         <v>34138</v>
       </c>
-      <c r="F63" s="8" t="n"/>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>HPMA: Paciente internado devido quadro recente de dor abdominal persistente, em hipocondrio direito. Teve diagnóstico de pancreatite aguda em 21/06/26 e ficou internado em Salvador para investigação.
+AP:
+- Nega comorbidades
+- Cirurgia bariatrica
+- Exerese de Tu cerebral há 30 anos &gt; acompanha com Dr. Milberto (nao quis que o chamasse neste momento)
+- Nega tabagismo
+- Etilista (uso de destilado diariamente)
+- MUC: Venvanse 70 mg/manhã
+- Alergias: AAS, camarão
+#Ao exame:
+BEG, LOTE, corado, hidratado, AAA, eupneico
+AR: MVF s/ RA
+ACV: RCR 2t BNF s/ sopros
+Abdome flacido, indolor a palpaçao, RHA+
+Extremidades sem edemas, sem empastamento de panturrilhas, BPP
+Labs prévios:
+lipase 1602 / amilase 150 / Cr 1,25 / Ur 52 / K 5 / Na 141 / TGO 42 / TGP 28 / GGT 23
+21/06 lipase 622 / amilase 97
+Conduta:
+ALTA HOJE
+Solicito ECG, ECOTT, USGs e angiotomos hoje
+EDA, ECOEDA e colono amanha com equipe do Dr. Raul Cutait
+Solicito aval do Dr. Parise e da Dra Fanny
+Fez uso de mounjaro no dia 20/06/26. 
+HPMA:
+Paciente internado devido quadro recente de dor abdominal persistente, em hipocondrio direito - diagnóstico de pancreatite aguda em 21/06 - ficou internado em Salvador para investigação. No momento, assintomático.
+Paciente nega qualquer sintoma relacionado a trombose
+Conta viagens frequentes para EUA, além de viagem de carro frequente para Itabuna (6 horas de duração)
+AP:
+- Nega comorbidades
+- Cx: bariatrica
+- MUC: Venvanse 70 mg/manhã
+- Alergias: AAS, camarão, grãos
+- Faz uso de destilados diariamente há 05 anos
+- Nega tabagismo
+AF
+Pai falaceu por CA pancreas aos 73 anos - nega trombose
+Mãe hígida aos 73 anos
+2 irmãos
+  1 irmã CA de mama aos 50 anos
+  1 irmão higido
+1 casa de filho
+Nega evento trombótico na família
+Labs prévios:
+lipase 1602 / amilase 150 / Cr 1,25 / Ur 52 / K 5 / Na 141 / TGO 42 / TGP 28 / GGT 23
+21/06 lipase 622 / amilase 97
+Conduta discutida com Dr Cyrllo:
+- Solicito pesquisa de trombofilia
+- Paciente quer realizar PET em outro momento
+- Nesse momento, oriento apenas profilaxia em situações de risco
+- Reforço a importância do retorno ambulatorial para checar exames e definiçãod a melhor estratégi aticoagulante
+Alta dia 29/06/2026 21:10</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="n"/>
       <c r="H63" s="9" t="n"/>
       <c r="I63" s="9" t="n"/>
@@ -15496,21 +17807,39 @@
       <c r="N63" s="9" t="n"/>
       <c r="O63" s="9" t="n"/>
       <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="9" t="n"/>
-      <c r="R63" s="9" t="n"/>
-      <c r="S63" s="10" t="n"/>
+      <c r="Q63" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="R63" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T63" s="10" t="n"/>
       <c r="U63" s="10" t="n"/>
       <c r="V63" s="10" t="n"/>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="10" t="n"/>
       <c r="Y63" s="10" t="n"/>
-      <c r="Z63" s="10" t="n"/>
+      <c r="Z63" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA63" s="10" t="n"/>
       <c r="AB63" s="10" t="n"/>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
-      <c r="AE63" s="10" t="n"/>
+      <c r="AE63" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF63" s="10" t="n"/>
       <c r="AG63" s="10" t="n"/>
       <c r="AH63" s="10" t="n"/>
@@ -15538,7 +17867,9 @@
       <c r="BD63" s="11" t="n"/>
       <c r="BE63" s="11" t="n"/>
       <c r="BF63" s="11" t="n"/>
-      <c r="BG63" s="11" t="n"/>
+      <c r="BG63" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="BH63" s="11" t="n"/>
       <c r="BI63" s="11" t="n"/>
       <c r="BJ63" s="11" t="n"/>
@@ -15665,7 +17996,66 @@
       <c r="E64" s="8" t="n">
         <v>34139</v>
       </c>
-      <c r="F64" s="8" t="n"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>HD:
+- Dor abdominal + alteração de enzimas hepáticas A/E (padrão hepatocelular)
+&gt; Migração de cálculo
+- Esofagite eosinolítica em EDA - aguarda resultado de Bx
+# HPMA: Paciente refere no início do mês quadro de forte intensidade de dor em dorso/ombro direito. Procurou atendimento médico em Salvador (Dr Paraná) e diagnosticado com colelitiase. Foi submetido a colecistectomia em servico externo há 15 dias a princípio sem intercorrências. Após alta evoluiu com quadro de dor em andar superior, mais HCD, com irradiação para dorso de forte intensidade, sendo necessário internação em UTI para investigação e controle álgico - referiu necessidade de morfina.
+Após alta, teve melhora dos sintomas.
+Há dois dias evoluiu com sintomas gripais (odinofagia, coriza, mialgia) e hoje após tomar café da manhã teve recorrência da dor abdominal/dorso muito intensa associado a náuseas. Negou outros sintomas. Fez uso apenas de dipirona e streplysis.
+# AP:
+- Nega comorbidades
+- Nega MUC
+- Etilismo social
+- HF: mãe com colelitiase
+# Evolução:
+Avalio paciente em leito de UI acompanhado pela mãe.
+Com melhora clínica significativa
+Amilase e lipase em queda. Enzimas hepáticas em queda.
+Abdome flacido, indolor. DB negativo.
+Exames complementares:
+LABORATÓRIO
+Externos:
+09/06 antiHAV IgG R / antiHAV IgM NR / antiHbc total NR / antiHbc IgM NR / antiHBS NR* / HbsAg NR / HCV NR 
+08/06 amilase 61 / Cr 0,85 / GGT 24 / glic 87 / K 4,6 / lipase 141 / Na 139 / PCR &lt;0,5 / TGO 43 (VR &lt;59) / TGP 56* (VR &lt;50) / Ur 35 / INR 1 / Hb 17,6 Ht 51,5 VCM 82,5 RDW 12,8 Leuco 8700 (7,4% eos) Plaq 197k 
+Atuais:
+27/06: BT 1 BD 0,5 / CaT 9,9 / Caio 1,33 / K 4,2 / procal 0,04 / Na 140 / amilase 58 / Cr 0,92 / FA 116 / GGT 261* / Hb 15,4 Ht 45,8 Leuco 13700 Plaq 240k / lipase 34 / PCR 0,44 / TGO 351* / TGP 244* / Ur 26
+28/06 ac fólico 5,1 / alb 4,7 / amilase 55 / BT 3,62* BD 2,45* / CA 19-9 15 / Caio 1,34 / CT 180 HDL 66 LDL 100 TG 54 / Cr 0,89 / CPK 49 / DHL 314 / ferritina 1418 / ferro 189 / FA 208* / GGT 529* / glic 99 / Hb 16 Ht 47,6 Leuco 7010 Plaq 215k / lipase 38 / K 4 / PCR 1,09 / IST 66% / Na 139 / TGO 592* / TGP 1037* / TSH 2 / Ur 18 / investigação ceruloplasmina 23 / IgG 1086 / IgM 119
+29/06: Amilase 44 BT 3,02 CAT 9,2 CAI 1,40 CR 0,86 FA 172 GGT 390 HB 13,8 L 5560 P 193.000 LIPASE 32 MG 1,9 K 4,0 K 3,9 PCR 0,67 NA 141 INR 1,28 TGO 255 TGP 667 UR 15
+30/06: AMILASE 317 LIPASE 1003 BT 2,02 FA 207 GGT 391 HB 15,7 L 7520 P 224.000 PCR 1,17 TGO 136 TGP 554 HDL 210 RETICULÓCITOS 67700, IFR 9,8% 
+Investigação:
+ceruloplasmina 23 / IgG 1086 / IgM 119 /
+AML NR
+Anti-LKM1 NR
+anti-HCV NR
+CMV IGG NR IGM NR
+ANTI-HAV IGM NR
+ANTI-HBC IGM NR ANTI-HBCT NR HBASG NR ANTI-HBS NR
+TOXO IGG NR IGM NR
+HIV NR
+FAN 1/80 Nucelar pontilhado fino/ 1/160 Nuclear pontilhado raros pontos isolados
+IMAGEM
+Externos:
+USG abdome superior 08/06/26: Figado sem alteraçoes. Ausencia de dilatação de VVBB. Porta pérvia. VB com paredes levemente espessadas, apresentando conteúdo anecoide com multiplos cálculos produtores de sombra acústica posterior em seu interior. Murphy ecográfico levemente positivo. 
+Atuais:
+EDA (29/05/26): Heterotopias de mucosa com aspecto colunar no esôfago cervical Esofagite eosinofílica ? Realizadas biópsias Esofagite erosiva no esôfago distal
+ECOEDA (29/06/26): Coledocolitíase Status pós colecistectomia
+CPRE (29/06/26): O exame do duodeno não revela qualquer alteração até a região da papila duodenal maior. Esta apresenta características endoscópicas dentro da normalidade. Realizada colangiopancreatografia após evidência de litiase biliar na ecoendoscopia. Realizada cateterização fácil e seletiva de via biliar. A colangiografia revelou falhas de enchimento na porção distal do colédoco. Vias biliares intra e extra-hepática dentro dos padrões radiológicos da normalidade. Realizado papilotomia endoscópica ampla que transcorreu sem intercorrências. Realizado retirada dos cálculos utilizando-se balão extrator com retirada de múltiplos cálculos e fragmentos. Colangiografia de oclusão final com adequado esvaziamento do contraste. Procedimento sem intercorrências
+AngioTC tórax negativa para TEP
+TC abdome com contraste: Fígado com dimensões normais, contornos regulares e atenuação preservada. Veias porta e hepáticas pérvias. Colecistectomia. Leve dilatação das vias biliares intra e extra-hepáticas, de aspecto adaptativo. Leve densificação dos planos adiposos na região da loja vesicular, que pode ser residual à cirurgia recente. Pâncreas com dimensões normais e atenuação habitual. Não há dilatação do ducto pancreático principal. Baço e adrenais sem particularidades. Apêndice cecal não completamente isolado, porém sem sinais de acometimento inflamatório pericecal. Ausência de líquido livre ou linfonodomegalias abdominais. Discreta densificação dos planos adiposos na região do hipogástrio, inespecífico
+ColangioRM 27/06: Sinais de colecistectomia com loja vesicular sem particularidades. Leve ectasia das vias biliares até à papila, de aspecto não obstrutivo, relacionada a colecistectomia.
+AP 10/06/26: VB com colecistite cronica calculosa. Fragmento hepático com proliferação ductular marginal portal discreta. Ausência de ductopenia ou colestase. CK7 positiva.  
+Conduta:
+- Paciente em condições de alta hospitalar.
+- Solicito coleta de exames lab na segunda feira e retorno em consultório com Dr. Parise e Dr. Raul na segunda feira à tarde.
+- Inicio ursacol 900mg/dia
+- Aguardo Bx de esôfago - EDA sugestiva de esofagite eosinoílica.
+- Mantenho inzelm
+. Alta dia 01/07/2026 14:20</t>
+        </is>
+      </c>
       <c r="G64" s="9" t="n"/>
       <c r="H64" s="9" t="n"/>
       <c r="I64" s="9" t="n"/>
@@ -15676,8 +18066,14 @@
       <c r="N64" s="9" t="n"/>
       <c r="O64" s="9" t="n"/>
       <c r="P64" s="9" t="n"/>
-      <c r="Q64" s="9" t="n"/>
-      <c r="R64" s="9" t="n"/>
+      <c r="Q64" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R64" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S64" s="10" t="n"/>
       <c r="T64" s="10" t="n"/>
       <c r="U64" s="10" t="n"/>
@@ -15718,7 +18114,9 @@
       <c r="BD64" s="11" t="n"/>
       <c r="BE64" s="11" t="n"/>
       <c r="BF64" s="11" t="n"/>
-      <c r="BG64" s="11" t="n"/>
+      <c r="BG64" s="11" t="n">
+        <v>0.86</v>
+      </c>
       <c r="BH64" s="11" t="n"/>
       <c r="BI64" s="11" t="n"/>
       <c r="BJ64" s="11" t="n"/>
@@ -15845,7 +18243,63 @@
       <c r="E65" s="8" t="n">
         <v>34177</v>
       </c>
-      <c r="F65" s="8" t="n"/>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>AP: - AVCi ACM direita 28/01/26
+&gt; Trombólise às 00h05min 28/01 
+&gt;&gt; Trombectomia mecânica TICI 2C 
+&gt;&gt;&gt; Etiologia: Embolia Cardio-Aortica 
+- Bradicardia sinusal com BAV 1o grau 
+- FA paroxistica? 
+Doença do nó sinusal? 
+- Quadro demencial leve?
+ - Doença coronariana estável 
+- Angiotomografia de coronárias com doença coronariana obstrutiva (sic) 
+- Endarterectomia de Cárótida (lateralidade?) 
+- HAS 
+- Pré-diabetes/glicemia de jejum alterada Internação em 2021 - PO (09/11) Implante MP bicameral DDD 
+- Síndrome bradi-Taqui (DNS) + pré-síncope 
+- FAAR 10/11 - revertida c/ propafenona 
+- Hipotensão + derrame pericárdico pequeno sem tamponamento 11/11 
+- IRA KDIGO 2 - 13/11: nova FAAR + tamponamento cardiaco com drenagem em CC - 13/11 falso trajeto SVD - IOT 13/11 -16/11
+ - ITU (meropenem)
+ MUC: Exelon, quetiapina, keppra, melatonina e donaren 
+HPMA: Somos chamdos pela familia a respeito do apcietne que ficou internado previamente aos cuidados da equipe e está em acompanhamento ambulatorial com Dr Ricardo Nogueira. Segundo relato da esposa e da cuidadora, hoje pela manhã foi notado hematuria importante, alem de piora da tosse produtiva e confusão mental. Na sexta apresentou episodio de hematuria, sendo interrompido uso de AAS. Neste mesmo dia recebeu uma dose de macrodantina. Nega febre, cefaleia, crise epileptica, novo deficit neurologico ou piora do deficit motor previo. Segundo esposa há 15 dias, durante troca da SVD, foi interrompido uso do xarelto 2,5mg/dia visto relato de hematuria Paciente estava em uso de azitromicina 3x/semana, sendo interrompido há 2 semanas. 
+Avalio paciente em unidade de observação, vigil, calmo e colaborativo. Apresenta paroxismos de tosse produtiva e dificuldade em mobilizar secreções de vias aereas superiores. Sem queixas algicas no momento. Segundo esposa, pacietne ficou sonolento durante todo o dia, despertando pos volta das 16h. 
+EVOLUÇÃO:
+Acompanhado do cuidador e filha.
+Dormiu bem. Sem intercorrências ou novas queixas.
+No momento, bem desperto, cooperativo, responde a comandos e solicitações coerentemente.
+Diurese clara, sem hematuria.
+Realizado troca de SVD em 30/06.
+Urocultura 9/7: E. coli.
+Caso discutido em equipe. Iniciamos Ceurozxima 250mg 12/12 por 7 dias e repetir exames em 1 semana.
+Alta hospitalar e continuará reabilitação em casa (família dispensou homecare).
+TC cranio 9/7: sem alterações agudas
+EEG: aumento de ondas lentas, sem paroxismos ou crises eletrográficas
+K: 5,1&gt;4,9&gt;4,5
+Urocultura 9/7: parcial negativa
+Ao exame neurologico: 
+Alerta, calmo e colaborativo, bom contato. Obedeceu comandos simples, desorientado T/E. 
+Fm grau V em MSD e MID, grau 3 proximaais em MSE e MIE. Observo certa espasticidade em MSE.
+ROT hipoativos globalmente. Normoativo em MSE. 
+MOE sem alteração. PIFR. Face simetrica 
+Sem sinais de rigidez cervical 
+AR: MVF, roncos difusos. 
+Desidratado+
+Exames complementares: 
+28/06: Urina 1: leucocituria e hematuria não dismorfica. Nitrito negativo. 
+Na 139, PCR 6,87, Hb 14,3, leuco 11710, PQT 221mil
+29/06: Cr 0,59, Mg 1,5, K 3,4, PCR 12,8, Na 144, Hb 11, leuco 6550, PQT 166mil
+TC de torax: Moderado acúmulo de secreção na traqueia. Espessamento difuso das paredes brônquicas, compatível com broncopatia inflamatória.. Espessamento difuso das paredes brônquicas, com impactações mucoides sobretudo nos lobos inferiores, de aspecto inflamatório. Opacidades em vidro fosco e micronódulos centrolobulares e consolidações com componente atelectásico nos lobos inferiores e mais acentuadas à esquerda de aspecto inflamatório, incluindo etiologia infecciosa e/ou aspirativa. Foco de opacificação do parênquima pulmonar alongado na transição entre os segmentos basais posterior e medial do lobo inferior direito, semelhante em comparação com o exame anterior de 11/06/2024, podendo ter natureza atelectásica. Tênues opacidades reticulares subpleurais na periferia do lobo médio, podendo representar discretas alterações intersticiais. 
+Tc de abdome total: Sonda vesical normoposicionada. Cálculos vesicais. Densificação dos planos perivesicais, podendo representar processo inflamatório/infeccioso (cistite). Moderada distensão fecal do reto.
+US joelho E (07/07/2026):  Exame realizado à beira do leito. Pequeno derrame articular no recesso suprapatelar, com corpos livres calcificados no seu interior. Tendões quadricipital e patelar de espessura e ecogenicidade habituais. Redução dos compartimentos femorotibiais com osteófitos marginais.
+Doppler venoso de MIE (07/07/2026):  Impressão Diagnóstica: Não há sinais de trombose venosa profunda.
+Impressao: Paciente com provavel intercorrencia infecciosa (BCP/ITU), evoluindo com delirium hipoativo. Hematuria resolvida. Término de abterapia. Ainda secretivo, mais que o habitual. Dor no joelho esquerdo de provavel etiologia degenerativa, porem visto historico recente de artrite reativa, opto por investigar. 
+Conduta:
+- Alta hospitalar Alta dia 14/07/2026 15:12</t>
+        </is>
+      </c>
       <c r="G65" s="9" t="n"/>
       <c r="H65" s="9" t="n"/>
       <c r="I65" s="9" t="n"/>
@@ -15856,8 +18310,14 @@
       <c r="N65" s="9" t="n"/>
       <c r="O65" s="9" t="n"/>
       <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="9" t="n"/>
-      <c r="R65" s="9" t="n"/>
+      <c r="Q65" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="R65" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S65" s="10" t="n"/>
       <c r="T65" s="10" t="n"/>
       <c r="U65" s="10" t="n"/>
@@ -15865,12 +18325,20 @@
       <c r="W65" s="10" t="n"/>
       <c r="X65" s="10" t="n"/>
       <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="10" t="n"/>
+      <c r="Z65" s="10" t="inlineStr">
+        <is>
+          <t>Desorientado</t>
+        </is>
+      </c>
       <c r="AA65" s="10" t="n"/>
       <c r="AB65" s="10" t="n"/>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
-      <c r="AE65" s="10" t="n"/>
+      <c r="AE65" s="10" t="inlineStr">
+        <is>
+          <t>Tubo</t>
+        </is>
+      </c>
       <c r="AF65" s="10" t="n"/>
       <c r="AG65" s="10" t="n"/>
       <c r="AH65" s="10" t="n"/>
@@ -15889,7 +18357,11 @@
       <c r="AU65" s="10" t="n"/>
       <c r="AV65" s="10" t="n"/>
       <c r="AW65" s="10" t="n"/>
-      <c r="AX65" s="10" t="n"/>
+      <c r="AX65" s="10" t="inlineStr">
+        <is>
+          <t>SVD - Sonda vesical de demora</t>
+        </is>
+      </c>
       <c r="AY65" s="11" t="n"/>
       <c r="AZ65" s="11" t="n"/>
       <c r="BA65" s="11" t="n"/>
@@ -15898,7 +18370,9 @@
       <c r="BD65" s="11" t="n"/>
       <c r="BE65" s="11" t="n"/>
       <c r="BF65" s="11" t="n"/>
-      <c r="BG65" s="11" t="n"/>
+      <c r="BG65" s="11" t="n">
+        <v>0.59</v>
+      </c>
       <c r="BH65" s="11" t="n"/>
       <c r="BI65" s="11" t="n"/>
       <c r="BJ65" s="11" t="n"/>
@@ -16025,7 +18499,16 @@
       <c r="E66" s="8" t="n">
         <v>34462</v>
       </c>
-      <c r="F66" s="8" t="n"/>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>Sou chamada para fazer avaliação medular da paciente com suspeita de mastocitose. Converso com a paciente sobre os riscos do procedimentos e assinamos o termo de consentimento.
+Paciente com anafilaxias de repetição, com elevação da triptase sérica.
+Pelo histórico clínico, Dr. Pedro realizou dessensibilização com lidocaína e indicou difenidramina de pré-medicação. Por precaução, deixamos o carrinho de parada próximo ao quarto e avisamos a enfermagem do andar. 
+Paciente colocada em decúbito lateral direito e realizada anestesia local com lidocaína 2% sem vaso constritor. Paciente não relatou nenhum sintoma durante a anestesia.
+Realizada biópsia de medula óssea em crista ilíaca postero superior esquerda, sem intercorrência, na primeira tentativa. Realizada compressão local e feito curativo oclusivo. Sem sinais de sangramento.
+Amostra identificada e encaminhada ao laboratório.. Alta dia 30/06/2026 14:53</t>
+        </is>
+      </c>
       <c r="G66" s="9" t="n"/>
       <c r="H66" s="9" t="n"/>
       <c r="I66" s="9" t="n"/>
@@ -16036,8 +18519,14 @@
       <c r="N66" s="9" t="n"/>
       <c r="O66" s="9" t="n"/>
       <c r="P66" s="9" t="n"/>
-      <c r="Q66" s="9" t="n"/>
-      <c r="R66" s="9" t="n"/>
+      <c r="Q66" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="R66" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S66" s="10" t="n"/>
       <c r="T66" s="10" t="n"/>
       <c r="U66" s="10" t="n"/>
@@ -16205,7 +18694,36 @@
       <c r="E67" s="8" t="n">
         <v>35071</v>
       </c>
-      <c r="F67" s="8" t="n"/>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>MÚLTIPLAS MORBIDADES: ASMA, ICO, FA (USO DE ELIQUIS), BARIÁTRICA, DRGE, CIRROSE, ETILISMO, ESTENOSE DE CANAL LOMBAR (MÚLTIPLAS CIRURGIAS).
+ESTEVE INTERNADO ATÉ 04.07.26 EM TRATAMENTO DE BCP ASPIRATIVA. SAIU DE ALTA BEM NA MANHÃ DE 05.07.26.
+EM 05.07.26, NO ENTANTO, TEVE NOVO EPISÓDIO DE BRONCOASPIRAÇÃO SEGUNDO O CUIDADOR, COM DESSATURAÇÃO ATÉ 80 %. NA CHEGADA, SONOLENTO,  SATO2 ~ 93% AA,  FC ~ 70 - A,  MV+ BILAT COM ALGUNS RONCOS E SIBILOS
+CT TÓRAX:
+ Em comparação com a TC de 21/05/2026, nota-se: 
+- aumento da secreção na via aérea central; - acentuação das alterações brônquicas inflamatórias, sobretudo no lobo inferior esquerdo; 
+- discreto aumento das opacidades pulmonares bilaterais de aspecto inflamatório, podendo ter etiologia infecciosa e/ou aspirativa; 
+- discreto aumento do derrame pleural à esquerda e redução do derrame pleural à direita. Demais estruturas sem alterações evolutivas significativas. 
+ATB -- MERO E TEICO, ALÉM DE MICAFUNGINA -- CANDIDA EM URINA.
+EM 07.07.26, AINDA MUITO SONOLENTO E COM MUITA SIALORREIA.
+VIDEODEGLUTOGRAMA:
+ Incoordenação da língua e do palato mole associada a retardo no disparo do reflexo da deglutição, que ocorre ao nível das valéculas glossoepiglóticas. Aumento do tempo de trânsito oral, principalmente com as consistências semissólida e sólida. Mastigação anteriorizada. Redução da força de ejeção oral. Ausência de refluxo nasofaríngeo. Redução da amplitude da elevação laríngea. Estase parcial dos contrastes nas valéculas glossoepiglóticas, eliminada com deglutições múltiplas subsequentes, principalmente das consistências semissólida e sólida. Seios piriformes livres. Observaram-se pequenos episódios de aspiração silentes e com resíduo durante a deglutição da consistência líquida. Esôfago pérvio, tortuoso, com esvaziamento preservado. 
+Classificação Rosenbek - Robbins: Categoria 8. 
+TEM MANTIDO ATITUDE MUITO AGRESSIVA E BELIGERANTE EM RELAÇÃO AOS PROFISSIONAIS (ENFERMAGEM, FISIO), O QUE DIFICULTA SOBREMANEIRA SEU ATENDIMENTO. 
+MANTÉM ALTO RISCO DE BRONCOASPIRAÇÕES REPETIDAS.
+NO MOMENTO:
+FC ~ 70
+SATO2 ~ 95% AA
+PACIENTE, MESMO APÓS EU EXPLICAR EXAUSTIVAMENTE, A NECESSIDADE DE PROSSEGUIR TRATAMENTO CLÍNICO, INCLUINDOREABILITAÇÃO COM FISIO E FONO, DESEJA DE FORMA IRREDUTÍVEL TER ALTA HOSPITALAR.
+DIANTE DISSO, FAREMOS ALTA A PEDIDO DO PACIENTE.
+ESTÁ CIENTE QUANTO AOS RISCOS DE NOVOS EPISÓDIOS DE BRONCOASPIRAÇÃO.
+ORIENTADO EM RELAÇÃO À DIETA, QUE DEVE SER PASTOSA/SEMI-SÓLIDA. DEVE SER OFERECIDA A DIETA SOMENTE COM O PACIENTE BEM ACORDADO E SENTADO. NÃO COMER E DEITAR EM SEGUIDA.
+ORIENTADO EM RELAÇÃO ÀS MEDICAÇÕES.
+CUIDADOR FELIPE TAMBÉM ORIENTADO.
+ORIENTADO ESPECIALMENTE QUANTO À IMPORTÂNCIA DE NÃO INGERIR BEBIDAS ALCOÓLICAS.
+Alta dia 13/07/2026 11:23</t>
+        </is>
+      </c>
       <c r="G67" s="9" t="n"/>
       <c r="H67" s="9" t="n"/>
       <c r="I67" s="9" t="n"/>
@@ -16216,8 +18734,14 @@
       <c r="N67" s="9" t="n"/>
       <c r="O67" s="9" t="n"/>
       <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="9" t="n"/>
-      <c r="R67" s="9" t="n"/>
+      <c r="Q67" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="R67" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S67" s="10" t="n"/>
       <c r="T67" s="10" t="n"/>
       <c r="U67" s="10" t="n"/>
@@ -16225,7 +18749,11 @@
       <c r="W67" s="10" t="n"/>
       <c r="X67" s="10" t="n"/>
       <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
+      <c r="Z67" s="10" t="inlineStr">
+        <is>
+          <t>Letárgico</t>
+        </is>
+      </c>
       <c r="AA67" s="10" t="n"/>
       <c r="AB67" s="10" t="n"/>
       <c r="AC67" s="10" t="n"/>
@@ -16385,7 +18913,53 @@
       <c r="E68" s="8" t="n">
         <v>35570</v>
       </c>
-      <c r="F68" s="8" t="n"/>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HPMA: Paciente com quadro de arritmia recorrente nos ultimos 2 anos, interna para realização de EEF e ablação. Realização Ablação de TRN com sucesso.  
+ Objetivo de cuidado conforme discutido com paciente e/ou familiares/ responsáveis, em caso de deterioração clínica:  
+ Status Pleno. Paciente candidato a medidas de suporte artificial de vida (RCP, IOT, etc.). :  sim  
+ Paciente candidato a medidas clínicas não-invasivas. Contraindicadas medidas invasivas de suporte artificial de vida. :  não  
+ Garantir controle de sintomas e permitir processo de morte de forma mais natural e mais confortável possível. :  não  
+ Paciente com necessidade de controle de sintomas:  
+ Equipe Médica :  Mauricio Ibrahim Scanavacca 
+Felix Ramires  
+ Alergias :  Nega existência de Alergias, 
+Nega alergia alimentar,Nega existência de Alergias, 
+ Diagnósticos e Lista de problemas :  - PO ( 30/06) Ablação de TRN ( Isolamento de Dupla via nodal)  
+ Antecedentes Pessoais :  Dislipidemia 
+CMH septal assimetrica não obstrutiva  
+ Diagnósticos Sindrômicos durante a internação  
+ Profilaxias  
+ Avaliação TEV não se aplica. Paciente menor de 18 anos. :  não  
+ Evolução  
+ Evolução/Impressão Clínica :  Evolução Diurna - UCO 3D 
+Avalio paciente em leito de UCO, sem acompanhantes no momento, sem queixas clinicas, com boa evolução pós operatória de Ablação de TRN.  
+Estável hemodinamicamente, sem aminas vasoativas,  
+Eupneico em ar ambiente, com bom padrão respiratório 
+Diurese espontânea preservada, função renal estável.  
+Local de punção femoral direita com curativo compressivo, sem sinais de complicações locais 
+Boa aceitação da dieta oral, evacuações ainda ausentes.  
+Sem intercorrências no período.  
+Controles: PAM: 104-47 | T.max: 36.1 | FC: 133-53 | FR: 24-8 | SpO2: 100-91 | Diu espontânea | Evac - 
+Ao Exame: 
+Geral: BEG, corado, afebril, anictérico, acianótico, eupneico 
+Neuro: consciente, orientado, sem déficits focais 
+ACV: RCR 2T BNF sem sopros 
+AR: MVFD sem RA 
+Abd: flácido, RHA+, sem VCM, indolor 
+Ext: curativo compressivo em Região inguinal D, sem sinais de complicações.  
+# Exames complementares: 
+- ECG: ARV + BAV 1° Grau 
+- Eco TT: FE preservada, Miocárdico com sinais de remodelamento concêntrico, espessura aumentada do septo sugerindo miocardiopatia hipertrófica assimétrica não obstrutiva.   
+# Exames Laboratoriais: 
+- 29/06/26:  Cr 1,06 | eGFR 80 | Ur 49 | Na 140 | K 4,5  | Hb 16,0 | Ht 45,8 | Leuco 11020 | Plaq 312000 | INR 1,12 | TTPA 31,0/1,03  
+ Condutas :  - Vigilância de ritmo 
+- Cuidados pós operatórios de ablação 
+- Avaliado por equipe de arritmia clinica e prescrito alta hospitalar com retorno ambulatorial em até 15 dias para reavaliação.  
+- Alta hospitalar 01/07/2026 13:54
+</t>
+        </is>
+      </c>
       <c r="G68" s="9" t="n"/>
       <c r="H68" s="9" t="n"/>
       <c r="I68" s="9" t="n"/>
@@ -16396,23 +18970,51 @@
       <c r="N68" s="9" t="n"/>
       <c r="O68" s="9" t="n"/>
       <c r="P68" s="9" t="n"/>
-      <c r="Q68" s="9" t="n"/>
-      <c r="R68" s="9" t="n"/>
-      <c r="S68" s="10" t="n"/>
+      <c r="Q68" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="R68" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T68" s="10" t="n"/>
       <c r="U68" s="10" t="n"/>
-      <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n"/>
-      <c r="X68" s="10" t="n"/>
+      <c r="V68" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="W68" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="X68" s="10" t="n">
+        <v>91</v>
+      </c>
       <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="10" t="n"/>
+      <c r="Z68" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA68" s="10" t="n"/>
       <c r="AB68" s="10" t="n"/>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
-      <c r="AE68" s="10" t="n"/>
+      <c r="AE68" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF68" s="10" t="n"/>
-      <c r="AG68" s="10" t="n"/>
+      <c r="AG68" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH68" s="10" t="n"/>
       <c r="AI68" s="10" t="n"/>
       <c r="AJ68" s="10" t="n"/>
@@ -16438,7 +19040,9 @@
       <c r="BD68" s="11" t="n"/>
       <c r="BE68" s="11" t="n"/>
       <c r="BF68" s="11" t="n"/>
-      <c r="BG68" s="11" t="n"/>
+      <c r="BG68" s="11" t="n">
+        <v>1.06</v>
+      </c>
       <c r="BH68" s="11" t="n"/>
       <c r="BI68" s="11" t="n"/>
       <c r="BJ68" s="11" t="n"/>
@@ -16565,7 +19169,27 @@
       <c r="E69" s="8" t="n">
         <v>35727</v>
       </c>
-      <c r="F69" s="8" t="n"/>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Paciente esta com lesão em perna direita há 2 meses. Estava viajando este tempo e voltou agora ao Brasil . 
+Apresenta dor perilesional 
+AP ex tabagista
+DLP , hipotireoidismo
+Med Puran, Zetcin 
+Alergia a medicação nega
+AF Nega 
+EF
+Nodulo com ceratose central em perna direita de aproximadamente 5cm com bordo levemente infiltrado 
+HD
+CEC? Queratoacantoma
+CD
+Internação para agendamento cirurgia amanha as 14:30 
+Jejum a partir das 06:30 (8 horas) de sólido e agua. 
+Converso com paciente em relação a cirurgia, extensão e necessidade de retalho assim como dor no pós operatório e risco de infecção. Paciente ciente e decide por internar e resolver, Exérese de Carcinoma Espinocelular na região pré tibial D, até o tecido muscular com reconstruçao por retalhos de avanço e rotação combinados.
+Cirurgia sem intercorrências.
+Alta 02/07 13:54.</t>
+        </is>
+      </c>
       <c r="G69" s="9" t="n"/>
       <c r="H69" s="9" t="n"/>
       <c r="I69" s="9" t="n"/>
@@ -16576,8 +19200,14 @@
       <c r="N69" s="9" t="n"/>
       <c r="O69" s="9" t="n"/>
       <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="9" t="n"/>
-      <c r="R69" s="9" t="n"/>
+      <c r="Q69" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="R69" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S69" s="10" t="n"/>
       <c r="T69" s="10" t="n"/>
       <c r="U69" s="10" t="n"/>
@@ -16745,7 +19375,54 @@
       <c r="E70" s="8" t="n">
         <v>36129</v>
       </c>
-      <c r="F70" s="8" t="n"/>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Paciente interna com dor abdominal e alteração TGI - tem HF positiva para cancer colon (filho e irma), CEA elevado e tirou polipo em 2024. 
+# Antecedentes: 
+- FA/TA paroxística com ablações prévias -  ablação 2022 em uso de Lixiana (CHADS 2 pts)
+- Dois episódios de síncope desliga-liga na última semana com TCE -  Looper diagnosticou BAVT com pausa maior que 30 segundos.
+- Novo BRE 02/2026
+- PO Implante de MPD - DDD (17/04/2026)  = Síndrome Bradi-Taqu
+- Doença de Parkinson (?) 
+- Incontinência urinária 
+- Hipotireoidismo 
+- Dislipidemia 
+- DAC não-obstrutiva (escore de cálcio 9, redução luminal disc.em DA) 
+- SAHOS (PSG 2025) 
+- Histerectomia 
+- Molestia Diverticular (colono 2024) 
+# Exames anteriores:
+- USG D. A e V de MMII (04/2026): normal
+- RNM de coração (04/2026): FEVE 50% à custa de dissincronia
+intraventricular septo-parede lateral, FEVD 53. Mapa T1 e T2 normal. Pericárdio de espessura preservada, sem sinais de derrame. Ectasia da aorta ascendente; tronco pulmonar com calibres aumentados.
+- TC abd (04/2026): H. hiatal. Provaveis cistos hepaticos de até 4,6cm. Retrações renais. Provaveis Cistos renais de até 3,9cm. Ateromatose. Diverticulos de colon. Histerectomia. Anel Vaginal. Alteração textural do sacro, podendo ser melhor avaliado por estudo dirigido
+- TC de ombro E (04/2026): Alteração degenerativa acromio-clavicular com espessamento cápsulo-ligamentar, reação osteofitária marginal e pequenos cistos nas margens articulares apostas. Alteração degenerativa leve das articulações esterno-claviculares. Pequenas calcificações em topografia paralabral superior e junto ao tubérculo maior do úmero, por provável depósito cálcico.
+- TC cranio (04/2026); Glicose/Micronangiopatia. Calcificações palidais. Hiperostose. Osteomas.
+- AngioTC torax (10/2025): Angiotomografia negativa para tromboembolismo pulmonar agudo. broncopatia inflamatória. Leve ectasia do tronco da artéria pulmonar (3,2 cm).
+- AngioTC coronarias (10/2025): 9 Classificação CAC-DRS: A1 / N1. Reduçaõ luminal discreta em DA
+- PSG (10/2025): SAHOS acentuada. SARVAS mod.
+- EDA (04/2024): Esofagite grau A. H. hiatal. Gastrite Antral
+- colono (04/2024); Pólipo de ceco (1). Realizada a polipectomia. Moléstia diverticular universal dos cólons.
+# Evolução: 
+Paciente realizou EDA e colonoscopia ontem, retirado 2 pólipos e implantado 2 clipes. Não apresentou sangramento após. 
+Apresentou calafrios durante preparo de colonoscopia, realizou antibioticoterapia profilática antes do procedimento (ampicilina + gentamicina) por implante de MP recente. Após procedimento, recebeu rocefin + metronidazol - permanece em uso (hoje D2).
+Exames laboratoriais com PCR baixo 0,6 e estável; afebril, sem recorrência dos calafrios desde procedimento.
+Orientado pela equipe do Dr Raul a manter sem Lixiana ontem por clipes em colonoscopia. 
+# Ao exame:
+- Geral: BEG, corada, hidratada, acianótica.
+- Neuro: Consciente, orientada, sem défcits
+- Cardiovasc: RCR, bulhas NF 2T sem sopros, TEC&lt;3s
+- Resp: MV presente bilat sem RA
+- Abdome: normotenso, indolor, sem VCM
+- Extremidades: sem edema, sem sinais de TVP
+# Condutas:
+- Orientado pela equipe do Dr Raul Cutait a manter sem Lixiana imediatamente após procedimento. Conversado com Dr. Roger: sem contra-indicação para reinicio da medicação. Conversado com Dr. Kalil em visita: optado por reiniciar após 72 horas da clipagem realização em colonoscopia (reiniciaremos em 05/07/26). 
+- Manteremos ATB até D5. Optado por troca por Ciprofloxacino para alta hospitalar. 
+- Orientada analgesia e tratamento clinico pela equipe de Ortopedia. 
+- Suporte clínico. ALTA DIA 04/07 14:10</t>
+        </is>
+      </c>
       <c r="G70" s="9" t="n"/>
       <c r="H70" s="9" t="n"/>
       <c r="I70" s="9" t="n"/>
@@ -16756,16 +19433,30 @@
       <c r="N70" s="9" t="n"/>
       <c r="O70" s="9" t="n"/>
       <c r="P70" s="9" t="n"/>
-      <c r="Q70" s="9" t="n"/>
-      <c r="R70" s="9" t="n"/>
-      <c r="S70" s="10" t="n"/>
+      <c r="Q70" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="R70" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S70" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T70" s="10" t="n"/>
       <c r="U70" s="10" t="n"/>
       <c r="V70" s="10" t="n"/>
       <c r="W70" s="10" t="n"/>
       <c r="X70" s="10" t="n"/>
       <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
+      <c r="Z70" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA70" s="10" t="n"/>
       <c r="AB70" s="10" t="n"/>
       <c r="AC70" s="10" t="n"/>
@@ -16925,7 +19616,75 @@
       <c r="E71" s="8" t="n">
         <v>36284</v>
       </c>
-      <c r="F71" s="8" t="n"/>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motivo da avaliação: Nova descompensação da cirrose hepática em ascite. Paciente realizou hoje paracentese de alívio com retirada de 5 litros e reposição de albumina 100ml. Encaminhado material para análise, sem PBE. Função renal boa. Estava em uso de aldactone 25mg/dia em casa e sem furosemida. Voltou a tomar furosemida há 2-3 dias. Não observo sinais de encefalopatia hepática. 
+Diagnóstico oncológico: 
+TNE bem diferenciado de pâncreas, G1 (ki-67 &lt;2%), funcionante (ACTH, Cortisol e Prolactina) 
+Histórico Oncológico:
+1. TNE bem diferenciado de pâncreas, G1 (ki-67 &lt;2%), funcionante (ACTH, Cortisol e Prolactina)
+2. Desde Dezembro/2011: Sandostatin LAR
+3. Fevereiro/2016: Adrenalectomia bilateral
+4. 1ª linha: Everolimus
+5. 2ª linha: Sunitinib
+6. 3ª linha: CapTEM
+7. 4ª linha Cisplatina + Irinotecano
+8. 5ª linha: Lu-177-octreotate x 4 aplicações (até mai/2017)
+9. Novembro/2018: TACE em lesão hepática no seg V (nov/2018)
+10. Outubro/2021: TACE com doxorrubina
+11. 6ª linha: re-exposição ao Everolimus 2019 a 2023
+12. 7ª linha: Cabozantinib 60mg/dia (Iniciado em 09/12/2023. Ajuste de dose por toxicidade para 40 mg em Janeiro/2024 ainda com baixa tolerância. Suspenso em 01/02/2024 por toxicidade limitante)
+13. 8ª linha: 19/03/24 a 09/07/24 re-exposição a Lu-177.
+14. 04/02/25 à 19/03/25 - 9ª LINHA - FOLFOX x 4. Suspenso por beneficio máximo.
+15. 10/10/2025 - Embolização hepática das fístulas tumorais
+16. 16/10/2025 - Ligaduras das varizes esofágicas
+17. Fev/2026 - Progressão de doença hepática e óssea.
+18. 11/02/2026 - C1D1 CAPTEM
+19. 17.03.24 - Internacao para embolização do ramo portal  D + cateterização da artéria hepática D (ramo da artéria mesentérica superior).
+20. 18.04.26 - Internacao por lombalgia por discoptia
+20. 27.04.26 - Internacao : Infeccao de sitio tumoral / dor lombar por discopatia. Realizadas paracenteses de alívio em 28/04 e 03/05, com retirada de líquido ascítico.
+21. 30.04.26 - Na internacao Recebeu Sandostatin LAR 30 mg  
+22. 10/06/26 - Internação: Lutécio 177 + Paracentese de Alívio + Sandostatim LAR
+Antecedentes Pessoais: Psoríase / HAS / Dislipidemia / Diabetes mellitus
+Alergias: metoclopramida
+MUC: Pregabalina 75 12/12h (começou nesta internação, há 6 dias), Levotiroxina 75, Jardiance 25, Florinefe 0,01, Prednisona 10, rifaximina, Ursacol, Carvedilol, pramipexol 
+Motivo da internação atual: Paciente procura PA devido distensão abdominal com desconforto respiratório importante ao decúbito. Solicitado laboratoriais e TC de abdome para avaliação e internação para compensação clínica.
+- 30/06/26: Paracentese de Alívio ~5L serohemático
+Evolução: 
+Paciente em UI acompanhado da esposa.
+Realizou paracentese hoje com saida de 4 litros, realizado 02 frascos de albumina.
+Estavel clinicamente e hemodinamicamente 
+Acordado, orientado, ausência de flapping. 
+Afebril 
+Dormiu bem a noite 
+Evacuação presente pastosa 1 x 
+Exames laboratoriais com aumento de enzimas colestáticas, mas sem aumento de bilirrubina. 
+Abdome globoso,ascitico,  com semi circulo de Skoda presente
+Ausencia de edema de MMII 
+PCR 10 &gt; 7 &gt; 6,0 &gt; 6,61 
+Bilirrubinas normais estaveis 
+HMC 03/07 PN - recebe meropenem 
+Labs: 
+(09/07): Alb:3,6 BT: 0,95 Cai:1,24 Cr:0,95 FA:282 GGT:569 Hb:9,6 Leuco; 5800 plaq:53mil K:4,6 PCR:6,61 INR:1,29 TGO:48 TGP:19 Ur:70
+BT 0,74 / Caio 1,26 / Cr 1,16 / FA 175 / P 2,8 / GGT 360 / gasov pH 7,37 BIC 20 / Hb 8,9 Ht 26,4 Leuco 7740 Plaq 46k / lactato 19,1 / Mg 1,7 / K 4,7 / PCR 12,6 Na 138 / TGO 115 / TGP 22 / Ur 81 
+Realizada ligadura elástica no dia 01/07/26 com duas banda de cordão varicoso de médio calibre, procedimento sem intercorrências.
+Diagnósticos:
+- Ascite sec. à Hipertensão Portal
+ -- paracentese 30/06 ~5L
+ -- paracentese (09/07) ~ 4L 
+Condutas
+- Prescrevo mais 02 frascos de albumina para realizar a tarde 
+- Previsão de alta amanhã 
+- Sem contraindicação pela hepatologia para alta 
+- Entrego receita com diureticoterapia + Ursacol 
+- Entrego pedido de exames laboratoriais para coleta ambulatorial 
+- Mantido Meropenem
+- Mantenho medidas para EH: Hepa-merz, lactulose (aumento dose) e rifaximina 
+- Mantenho aldactone 25mg/dia e furosemida 40mg/dia em dias alternados
+- Suporte clinico  . ALTA DIA 10/07/2026 15:09
+</t>
+        </is>
+      </c>
       <c r="G71" s="9" t="n"/>
       <c r="H71" s="9" t="n"/>
       <c r="I71" s="9" t="n"/>
@@ -16936,8 +19695,14 @@
       <c r="N71" s="9" t="n"/>
       <c r="O71" s="9" t="n"/>
       <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="9" t="n"/>
-      <c r="R71" s="9" t="n"/>
+      <c r="Q71" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="R71" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S71" s="10" t="n"/>
       <c r="T71" s="10" t="n"/>
       <c r="U71" s="10" t="n"/>
@@ -16978,9 +19743,13 @@
       <c r="BD71" s="11" t="n"/>
       <c r="BE71" s="11" t="n"/>
       <c r="BF71" s="11" t="n"/>
-      <c r="BG71" s="11" t="n"/>
+      <c r="BG71" s="11" t="n">
+        <v>1.16</v>
+      </c>
       <c r="BH71" s="11" t="n"/>
-      <c r="BI71" s="11" t="n"/>
+      <c r="BI71" s="11" t="n">
+        <v>7.37</v>
+      </c>
       <c r="BJ71" s="11" t="n"/>
       <c r="BK71" s="11" t="n"/>
       <c r="BL71" s="11" t="n"/>
@@ -17105,7 +19874,34 @@
       <c r="E72" s="8" t="n">
         <v>36704</v>
       </c>
-      <c r="F72" s="8" t="n"/>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Síndrome Auto-inflamatória VEXAS negativo (duas pesquisas negativas - Einstein / FMUSP-RP) - 
+AHAI ==&gt; SMD 5q- (R-IPSS intermediário / M-IPSS alto)
+ Anemia Hemolitica Autoimune + plaquetopenia autoimune - Coomb direto positivo C3d =&gt; componente extravascular - hapto normal - episódios de condrite (pavilhão auricular e nasal) - esplenomegalia em crescimento - 2 episódios de TEP (2020/2022) 
+- pancreatite com azatioprina 
+- Diabetes Melitus secundário a corticosteroides 
+- Broncoscopia + Bx Transbrônquica em 2024 -&gt; Pneumonia intersticial organizante 
+- Avaliação medular (2 ocasiões ) - características displásicas (medula de stress??) ==&gt; Painel mieloide negativo (2023) ==&gt; Exoma negativo (PK adquirida?) ==&gt; Pesquisa HPN negativa (2020) # 3 avaliação medular ==&gt; Cariótipo 5q- ==&gt; EPO elevada - Lenalidomida iniciada em 14-20/05/2026 Hipertensão arterial Sistêmica Herpes Zoster 2021
+Atual: Neutropenia febril - diarreia, febre e hipotensão
+Evolução: Paciente em leito de UCG. Registrado erroneamente febre no sistema. Segue com PCR baixo, sem novos sintomas de infecção.
+ Evolução  
+ Evolução/Impressão Clínica :  sem novos sangramentos 
+Neuro: consciente, orientado, PIFR ; Sem deficit neurologico focal 
+Resp: confortável, em AA 
+MV + bilateral ; sem RA ;  
+Hemo: estável, sem DVA sinusal ; bem perfundido ; 
+Abdome flácido e indolor, dieta via oral, Evacuação ++2x ontem (1  com sangue  e a outra sem ) 
+Diurese 700 ml + perdas  
+Afebril sem sangramentos ; Hb 8,8 ( ontem recebeu 1 CH) e plaquetas 13 mil  
+sem ATB  
+Granulokine  
+ Condutas :  vigilância a sangramentos 
+transfusão de  aférese de plaquetas 
+aguarda anatomopatológico de biopsia de fronte. ALTA DIA 08/07 18:11  
+</t>
+        </is>
+      </c>
       <c r="G72" s="9" t="n"/>
       <c r="H72" s="9" t="n"/>
       <c r="I72" s="9" t="n"/>
@@ -17116,8 +19912,14 @@
       <c r="N72" s="9" t="n"/>
       <c r="O72" s="9" t="n"/>
       <c r="P72" s="9" t="n"/>
-      <c r="Q72" s="9" t="n"/>
-      <c r="R72" s="9" t="n"/>
+      <c r="Q72" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R72" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S72" s="10" t="n"/>
       <c r="T72" s="10" t="n"/>
       <c r="U72" s="10" t="n"/>
@@ -17125,7 +19927,11 @@
       <c r="W72" s="10" t="n"/>
       <c r="X72" s="10" t="n"/>
       <c r="Y72" s="10" t="n"/>
-      <c r="Z72" s="10" t="n"/>
+      <c r="Z72" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA72" s="10" t="n"/>
       <c r="AB72" s="10" t="n"/>
       <c r="AC72" s="10" t="n"/>
@@ -17135,7 +19941,11 @@
       <c r="AG72" s="10" t="n"/>
       <c r="AH72" s="10" t="n"/>
       <c r="AI72" s="10" t="n"/>
-      <c r="AJ72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="inlineStr">
+        <is>
+          <t>Oral</t>
+        </is>
+      </c>
       <c r="AK72" s="10" t="n"/>
       <c r="AL72" s="10" t="n"/>
       <c r="AM72" s="10" t="n"/>
@@ -17285,7 +20095,28 @@
       <c r="E73" s="8" t="n">
         <v>36712</v>
       </c>
-      <c r="F73" s="8" t="n"/>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+HDA: paciente vem em uso de Zinnat para E. coli sensível ao antibiótico escolhido, porem evoluindo com bacteremia, hipotensão e piora do estado geral. Teve atendimentos recentes neste PS por QPA e passado recente de hematoma subdural, com drenagem e, em segunda internação, embolização de artéria meníngea media.
+HPP: resistencia inslulínica / hipotireoidismo / Neoplasia de próstata tratada com prostatectomia radical isolada em 2017 / Ex tabagista 40am / TEP em PO de Redução Incruenta + fixação interna com 3 parafusos canulados de fratura do colo do femur esquerdo (21/11/2024) / Gastrectomia total VLP com linfadenectomia D2 e reconstrução em Y de Roux (24/07/24) / Adenocarcinoma de junção esofago-gastrica T3 NI / Suboclusão intestinal - 01/03/2024 - Biópsia endoscópica de lesão em transição esôfago-gástrica: adenocarcinoma invasico, ulcerado - IH 05/03/24: Anti citoqueratina 20+, anti SATB2+, Anti CDX-2+ - 07/03/2024 - Ecoendoscopia digestiva alta: Neoplasia avançada da cárdia uT3N1MX - 04/24-05/24: FLOT neoadjuvante: C1 02/04/24, C2 16/04/24, C3 30/04/24, C4 14/05/24
+EVOLUÇÃO: estavel, sem febre, ha 48 horas D7 de Rocefin para foco pulmonar (TC de torax com BCP). Urina normal, cultura negativa
+Evacuacao amolecida em melhora, nao recorreu mais diarreia, mais alerta nesta manha
+LAB ontem sustentando queda de PCR, FR normalizada e plaquetas em ascencao, com Hb estavel.
+Teve hemoptise nos primeiros dois dias de internacao, desde 03/07 sem recorrencia e com enoxa profilatica desde 04/07
+Pneumologia mantem seguimento, deixa fluimucil
+Fono e FST acompanhando, sem sinais de desconforto ou piora para deglutição
+Neurologicamente continua melhor, sono adequado à noite, mais acordado hoje, comportamento ok
+EN: menos sonolento, atento, desorientado, sem alterações de linguagem ou disatria
+NNCC inalterados
+Força grau V Sensibilidade simétrica e sem déficits
+Eumetria bilateral 
+IMPRESSAO: sepse de foco pulmonar + delirium
+CD:
+- Oriento alta e seguimento ambulatorial. ALTA DIA 09/07/2025 13:14
+</t>
+        </is>
+      </c>
       <c r="G73" s="9" t="n"/>
       <c r="H73" s="9" t="n"/>
       <c r="I73" s="9" t="n"/>
@@ -17296,8 +20127,14 @@
       <c r="N73" s="9" t="n"/>
       <c r="O73" s="9" t="n"/>
       <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="9" t="n"/>
-      <c r="R73" s="9" t="n"/>
+      <c r="Q73" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R73" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S73" s="10" t="n"/>
       <c r="T73" s="10" t="n"/>
       <c r="U73" s="10" t="n"/>
@@ -17305,7 +20142,11 @@
       <c r="W73" s="10" t="n"/>
       <c r="X73" s="10" t="n"/>
       <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
+      <c r="Z73" s="10" t="inlineStr">
+        <is>
+          <t>Desorientado</t>
+        </is>
+      </c>
       <c r="AA73" s="10" t="n"/>
       <c r="AB73" s="10" t="n"/>
       <c r="AC73" s="10" t="n"/>
@@ -17465,7 +20306,47 @@
       <c r="E74" s="8" t="n">
         <v>36737</v>
       </c>
-      <c r="F74" s="8" t="n"/>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>História oncológica
+1. Mixofibrossarcoma de alto grau histológico em perna E. 
+- s/p ressecção ampliada e RT adjuvante até 12/2020. 
+- seguimento até 10/2023, evoluindo com recidiva local confirmada por biópsia 
+- s/p resgate cirúrgico em 12/2023 
+- ago/2025 - recidiva local multifocal -&gt; 06/09/25 s/p resgate cirúrgico Atual: em seguimento oncológico 
+- Jul/2026 - recidiva local multifocal 
+2. Adenocarcinoma de reto alto pT1aN0. 
+3. Lesão em fêmur E - imagem rediscutida com radiologia HSL - sem sinais de agressividade
+HMA
+Paciente acompanhada da filha Lúcia. Relata que a paciente apresenta quadro de dor intermitente no membro inferior E, com melhora com massagem ou analgésicos simples. Associado, apresentou abaulamento na região do sítio cirúrgico do MIE. Sem sinais infecciosos.
+AP
+- DM2, HAS, hipotireoidismo, constipação crônica
+- Histórico de CA de colo de útero com necessidade de conização em 1970 e CA de bexiga em 1980 com realização de RTU e diversas aplicações de BCG.
+MUC
+Losartana; Jardiance; Levotiroxina; Domperidona; Bisoprolol; Furosemida; Espironolactona; Doraren; Quetiapina
+Evolução
+Paciente em UI, acompanhada da filha. Mantém estabilidade clínica, sem queixa álgica. D5 de RT planejada para 12h
+Exame físico
+Calma, colaborativa, consciente e orientada
+MV+, sem RA. Eupneica
+BCRNF, 2 tempos, sem sopros
+Abdome globoso, indolor à palpação
+MIE com extensa cicatriz com áreas nodulares de infiltração neoplásica  locorregional, sem sinais infecciosos secundários
+Exames de imagem
+- RM de joelho e perna E 02/07/26:
+Lesão nodular infiltrativa junto da porção superior do leito cirúrgico no terço superior da face lateral da perna proximal, comprometendo planos de partes moles superficiais e o ventre muscular do gastrocnêmio lateral adjacente, com realce pós-contraste sólido e pequeno foco hipovascularizado de permeio, em contato com a cabeça da fíbula, sem sinais de invasão óssea, medindo cerca de 5,1 x 3,5 x 2,7 cm (CC x AP x LL), compatível com recorrência da doença de base. Na porção inferior da cicatriz cirúrgica, nota-se pequena área de espessamento e realce da derme/subcutâneo, de limites parcialmente definidos e medindo cerca de 1,4 cm (axial), sem configuração nodular bem definida e adjacente aos tendões fibulares. Lesões com realces nodulares sólidos em planos de partes moles superficiais no terço inferior da perna, na face posteromedial medindo cerca de 2,2 x 1,4 x 0,7 cm (LL x CC x AP) e na face anterior com, aproximadamente, 1,8 x 1,1 x 0,6 cm (CC x LL x AP), devendo representar comprometimento pela doença de base. Também notam-se áreas alongadas com realce pós-contraste, de limites parcialmente definidos no presente estudo, em planos de partes moles superficiais nas faces anteromedial (4,5 x 3,4 x 1,0 cm - LL x CC x AP) e anterolateral (3,6 x 3,6 x0,7 cm - LL x CC x AP) na perna distal / tornozelo, devendo-se considerar a possibilidade de comprometimento pela doença de base.
+Impressão
+Paciente idosa com história de mixofibrossarcoma de alto grau recidivante em perna E, aprestando quadro de dor no mesmo membro, associado a abaulamento no local do sítio cirúrgico. Em RM de MIE, identificados múltiplos focos de recidiva de doença, tanto no leito cirúrgico, quanto na região distal do mesmo membro. Programação de 5 sessões de RT.
+Conduta
+- Avaliada pelo Dr. Fabio Ferreira, considerada magnitude cirúrgica desproporcional (amputação transfemoral), sem condutas neste momento.
+- Avaliada pelo Dr. Matheus, radioterapeuta da equipe do Dr. Samir - em realização de RT, iniciada em 10/07/26, quinta fração hoje
+- Mantenho medidas laxativas
+- Em acompanhamento com equipe de cardiologia (Dr. Eduardo Dante)
+- Suporte clínico.
+- Oriento e acolho paciente e acompanhantes, cientes e de acordo
+- Programação de alta amahã pela manhã. ALTA DIA 16/07/2026 13:10</t>
+        </is>
+      </c>
       <c r="G74" s="9" t="n"/>
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="9" t="n"/>
@@ -17476,8 +20357,14 @@
       <c r="N74" s="9" t="n"/>
       <c r="O74" s="9" t="n"/>
       <c r="P74" s="9" t="n"/>
-      <c r="Q74" s="9" t="n"/>
-      <c r="R74" s="9" t="n"/>
+      <c r="Q74" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R74" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S74" s="10" t="n"/>
       <c r="T74" s="10" t="n"/>
       <c r="U74" s="10" t="n"/>
@@ -17485,12 +20372,20 @@
       <c r="W74" s="10" t="n"/>
       <c r="X74" s="10" t="n"/>
       <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
+      <c r="Z74" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA74" s="10" t="n"/>
       <c r="AB74" s="10" t="n"/>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
-      <c r="AE74" s="10" t="n"/>
+      <c r="AE74" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF74" s="10" t="n"/>
       <c r="AG74" s="10" t="n"/>
       <c r="AH74" s="10" t="n"/>
@@ -17645,7 +20540,43 @@
       <c r="E75" s="8" t="n">
         <v>36747</v>
       </c>
-      <c r="F75" s="8" t="n"/>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">História oncológica: 
+1. Melanoma em MSD com esvaziamento axilar em 1999 (00/23) 
+- status BRAF pendente 
+- seguimento entre 1999 e 2022 
+- evoluindo com recidiva na forma de satelitose/lesão em trânsito s/p ressecção e ampliação inicial com margens comprometidas s/p reampliação 
+- s/p Pembrolizumabe até 07/2023 
+Atual: Desde 14/02/2023 ­- Ipi 1/Nivo 3 (neoadjuvância) x 4 ciclos -&gt; Nivolumabe de manutenção até 20/05/2026
+-&gt; RP após C#2; RP sustentada após C#4
+-&gt; 15/07/2025 - Ressecção de lesão em antebraço D
+2. Psoríase/artrite psoríásica - s/p secuquinumabe, com melhora expressiva - atualmente sob tratamento com Risanquizumabe.
+3. Prostatite recorrente relacionada à HPB -&gt; s/p RTUp em 11/04/2025 - AP compatível com HPB
+HMA
+Paciente passou em consulta ambulatorial de retorno. Compareceu com dessaturação (86-88%), piorando aos pequneos esforços, caindo até 80%. Além disso, queixa-se de piora clínica desde a alta hospitalar. Interna para investigação do quadro. 
+AP
+Psoríase, HAS, DSLP, RTU por HPB, marca passo implantado em 2022
+MUC
+Alopurinol 100mg 1x/dia, Escitalopram 10mg 1x/dia, Vitamina D 7000UI/sem, Levotiroxina 75mcg manhã, lisinopril 10mg meio cp manhã, prednisona 40mg/dia, rosuvastatina 10mg à noite, rizanquizumabe 1amp a cada 12 semanas
+Evolução:
+Paciente em leito de Ui, acompanhado. Recebendo 2L/min de O2 em CN, com melhora da dispneia. Mantém estabilidade clínica 
+Exame físico
+BEG, LOTE
+MV+, diminuido globalmente, com crepitos em bases
+BCRNF, 2 tempos, sem sopros
+Abdome plano, indolor à palpação
+MMII sem empastamento ou edema
+Exames microbiológicos
+- RespMol 16/07: Negativo 
+Conduta
+- Internação hospitalar
+- Solicito laboratoriais para agora com BNP e procalcitonina
+- Solicito AngioTC protocolo TEP para investigar dessaturação
+- Solicito ECOTT para diagnóstico diferencial de dispneia
+- Solicito RespMol para diferencial </t>
+        </is>
+      </c>
       <c r="G75" s="9" t="n"/>
       <c r="H75" s="9" t="n"/>
       <c r="I75" s="9" t="n"/>
@@ -17656,16 +20587,30 @@
       <c r="N75" s="9" t="n"/>
       <c r="O75" s="9" t="n"/>
       <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="9" t="n"/>
-      <c r="R75" s="9" t="n"/>
-      <c r="S75" s="10" t="n"/>
+      <c r="Q75" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R75" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S75" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T75" s="10" t="n"/>
       <c r="U75" s="10" t="n"/>
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
       <c r="X75" s="10" t="n"/>
       <c r="Y75" s="10" t="n"/>
-      <c r="Z75" s="10" t="n"/>
+      <c r="Z75" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA75" s="10" t="n"/>
       <c r="AB75" s="10" t="n"/>
       <c r="AC75" s="10" t="n"/>
@@ -17825,7 +20770,48 @@
       <c r="E76" s="8" t="n">
         <v>37078</v>
       </c>
-      <c r="F76" s="8" t="n"/>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAURO SERGIO TESTONI, 61 anos, hipertenso, portador de intolerancia à glicose e hipercolesterolemia, histórico familiar de coronariopatia precoce (mãe revasc miocardica aos 50 anos), apresenta ha 1 semana episodios de opressão retroesternal aos esforços. ECG: alterações da repolarização ventricular parede lateral (inversao de onda T V4-V6).
+PA 14X7 FC 75
+Ausculta pulmonar limpa
+BRNF, 2T, sopro sistolico BEE 2+
+Sem edemas
+Diagnostico: Angina de recente inicio - Angina instável
+Necessita de hospitalização para monitoração e estratificação do risco de eventos isquêmicos. Tipo evolução :  UCO  
+ Transferência :  não  
+ História Clínica :  Admito paciente pos cateterismo cardiaco realizado sem intercorrencias, com lesoes tri-arteriais.  
+ Objetivo de cuidado conforme discutido com paciente e/ou familiares/ responsáveis, em caso de deterioração clínica:  
+ Status Pleno. Paciente candidato a medidas de suporte artificial de vida (RCP, IOT, etc.). :  sim  
+ Paciente candidato a medidas clínicas não-invasivas. Contraindicadas medidas invasivas de suporte artificial de vida. :  não  
+ Garantir controle de sintomas e permitir processo de morte de forma mais natural e mais confortável possível. :  não  
+ Paciente com necessidade de controle de sintomas:  
+ Equipe Médica :  Pedro de Azevedo Nunes  
+ Alergias :  Nega existência de Alergias, 
+Nega existência de Alergias, 
+Nega alergia alimentar,Nega existência de Alergias, 
+ Diagnósticos e Lista de problemas :  DAC Tri-arterial  
+ Antecedentes Pessoais :  DAC triarterial 
+Historico familiar de DAC 
+HAS 
+DLP  
+ Diagnósticos Sindrômicos durante a internação  
+ Profilaxias  
+ Úlcera de Estresse :  sim  
+ Avaliação TEV não se aplica. Paciente menor de 18 anos. :  não  
+ Evolução  
+ Evolução/Impressão Clínica :  paciente hemodinamicamente estável, sem queixas. 
+Exame fisico: 
+BEG, corado, hidratado, orientado, PIFR, sem deficits aparentes. 
+AR: MV + s/ RA. Confortavel em ar ambiente. 
+ACV: RC regular, sem sopros. Boa perfusão. Ausência de EJ e RHJ. 
+Abdome flácido, indolor, sem visceromegalias. RHA +.  
+Extremidades sem edemas, sem sinais de TVP.  
+ Condutas :  Aguarda aval Equipe Dr Fabio Jatene 
+Suporte UCO. ALTA DIA 02/07/2026 12:02 
+</t>
+        </is>
+      </c>
       <c r="G76" s="9" t="n"/>
       <c r="H76" s="9" t="n"/>
       <c r="I76" s="9" t="n"/>
@@ -17836,12 +20822,24 @@
       <c r="N76" s="9" t="n"/>
       <c r="O76" s="9" t="n"/>
       <c r="P76" s="9" t="n"/>
-      <c r="Q76" s="9" t="n"/>
-      <c r="R76" s="9" t="n"/>
-      <c r="S76" s="10" t="n"/>
+      <c r="Q76" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R76" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S76" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T76" s="10" t="n"/>
       <c r="U76" s="10" t="n"/>
-      <c r="V76" s="10" t="n"/>
+      <c r="V76" s="10" t="n">
+        <v>75</v>
+      </c>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="10" t="n"/>
       <c r="Y76" s="10" t="n"/>
@@ -17850,9 +20848,17 @@
       <c r="AB76" s="10" t="n"/>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
-      <c r="AE76" s="10" t="n"/>
+      <c r="AE76" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF76" s="10" t="n"/>
-      <c r="AG76" s="10" t="n"/>
+      <c r="AG76" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH76" s="10" t="n"/>
       <c r="AI76" s="10" t="n"/>
       <c r="AJ76" s="10" t="n"/>
@@ -18005,7 +21011,46 @@
       <c r="E77" s="8" t="n">
         <v>38059</v>
       </c>
-      <c r="F77" s="8" t="n"/>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>História Clínica :  Paciente Maurício Berto, 53 anos, residente atualmente em Xangai (China), encaminhado para tratamento cirúrgico eletivo após diagnóstico incidental de massa intracardíaca localizada na valva aórtica durante investigação cardiológica.  
+Realizou Ecocardiograma Transesofágico que evidenciou massa de aproximadamente 21,6 × 6,6 mm, com características altamente sugestivas de fibroelastoma papilar, implantada na comissura entre as cúspides coronarianas esquerda e direita, estendendo-se para a cúspide coronariana direita.  
+A lesão apresenta discreta mobilidade, porém dimensões expressivas, ocasionando restrição mecânica da mobilidade valvar, má coaptação dos folhetos e insuficiência aórtica moderada.  
+Apesar da ausência de sintomas cardiovasculares, como dor torácica, dispneia, síncope, palpitações ou limitação funcional, a localização em câmaras esquerdas, o tamanho da lesão, a interferência funcional sobre a valva e o risco potencial de fenômenos embólicos sistêmicos configuram indicação formal de ressecção cirúrgica eletiva.  
+A angiotomografia coronária demonstrou ainda doença aterosclerótica significativa da artéria descendente anterior, com múltiplas placas calcificadas e mistas determinando estenose estimada entre 50 e 70% nos segmentos proximal e médio, achado que poderá modificar a estratégia cirúrgica caso seja confirmada doença obstrutiva significativa ao estudo invasivo.  
+Paciente mantém capacidade funcional, encontra-se fisicamente ativo, sem história de acidente vascular cerebral, embolização periférica, infarto do miocárdio ou insuficiência cardíaca.  
+A função sistólica biventricular permanece preservada, com FEVE estimada em aproximadamente 60% 
+Vem para essa unidade após a realização de cateterismo cardiaco diagnostico, peri-operatorio   
+ Objetivo de cuidado conforme discutido com paciente e/ou familiares/ responsáveis, em caso de deterioração clínica:  
+ Status Pleno. Paciente candidato a medidas de suporte artificial de vida (RCP, IOT, etc.). :  sim  
+ Paciente candidato a medidas clínicas não-invasivas. Contraindicadas medidas invasivas de suporte artificial de vida. :  não  
+ Garantir controle de sintomas e permitir processo de morte de forma mais natural e mais confortável possível. :  não  
+ Paciente com necessidade de controle de sintomas:  
+ Equipe Médica :  Fabio Biscegli Jatene 
+Fábio Fernandes  
+ Alergias :  Queijos, 
+Queijos maturados, 
+ Diagnósticos e Lista de problemas :  Fibroelastoma papilar  
+ Antecedentes Pessoais :  -- Fibroelastoma papilar da valva aórtica  
+-- Insuficiência aórtica moderada secundária à interferência mecânica da massa sobre a coaptação valvar.  
+-- Valva aórtica bicúspide  
+-- Doença aterosclerótica coronária com estenose moderada/importante (50&amp;#x2013;70%) em segmentos proximal e médio da artéria descendente anterior.  
+ Diagnósticos Sindrômicos durante a internação  
+ Profilaxias  
+ Úlcera de Estresse :  sim  
+ Avaliação TEV não se aplica. Paciente menor de 18 anos. :  não  
+ Evolução  
+ Evolução/Impressão Clínica :  Evolução UCO 
+Paciente evoluindo estável hemodinamicamente, confortável em ar ambiente, sem queixas. Sitio de punção de ARD sem sinais de complicações. Em programação de alta hospitalar hoje. 
+Exame Fisico  
+RCR em 2 tempos, Sopro aspirativo e FAo acessorio 2+/6+ 
+MV audivel bilateralmente SRA  
+Abdome Inocente 
+Extremidades sem edemas, pulsos simetricos  
+ Condutas :  Alta hospitalar  
+ALTA DIA 29/06/2026 11:30</t>
+        </is>
+      </c>
       <c r="G77" s="9" t="n"/>
       <c r="H77" s="9" t="n"/>
       <c r="I77" s="9" t="n"/>
@@ -18016,8 +21061,14 @@
       <c r="N77" s="9" t="n"/>
       <c r="O77" s="9" t="n"/>
       <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="9" t="n"/>
-      <c r="R77" s="9" t="n"/>
+      <c r="Q77" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R77" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S77" s="10" t="n"/>
       <c r="T77" s="10" t="n"/>
       <c r="U77" s="10" t="n"/>
@@ -18030,9 +21081,17 @@
       <c r="AB77" s="10" t="n"/>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
-      <c r="AE77" s="10" t="n"/>
+      <c r="AE77" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF77" s="10" t="n"/>
-      <c r="AG77" s="10" t="n"/>
+      <c r="AG77" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH77" s="10" t="n"/>
       <c r="AI77" s="10" t="n"/>
       <c r="AJ77" s="10" t="n"/>
@@ -18185,7 +21244,33 @@
       <c r="E78" s="8" t="n">
         <v>39140</v>
       </c>
-      <c r="F78" s="8" t="n"/>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Atual: 
+- DAC / 1° PO ATC de CD com stent farmacológico - 03/07/2026
+Antecedentes: DAC, Dislipidemia, Tabagista (1 maço/dia há 20 anos), Pré-DM, Sobrepeso, Esteatose hepática, SAHOS, AIT c/ fechamento de FOP em 13/04/2026, Dça diverticular.
+Cirurgias prévias: hemorroidectomia.
+Medicamentos em uso: Coleduo, AAS, Plavix 75mg 
+Exames prévios:
+- Ecocardiograma: AE= 21m/m² , S= PP= 8, VE 31x48, FE=66% | sem alteração segmentar. IMi mínima, IAo mínima. Sugestivo de FOP.
+- AngioTC coronária: escore de cálcio discreto. Redução luminal coronariana importante em terço médio de CD. 
+- Cintilografia miocárdica DIPI/MIBI 10/04: negativa para isquemia. FEVE 68/68%.
+- Perfil lipidico: CT=183, HDL=46, LDL=114, TG=121
+- HbA1C=5,7%
+HMA: Paciente encaminhado para cate que mostrou CD com lesão de 60% em terço médio com IVUS mostrandl ALM=3,6mm² e carga de placa=72%
+Evolução:
+Vigil, orientado e contactuante.
+Hemodinamicamente estável. 
+Eupneico, ausculta pulmonar limpa.
+Abdome nl
+Sem edema mmii
+Sítio de punção em MSD com hematoma estável, pulso amplo, boa perfusão distal.
+Exames Recentes:  Hemoglobina13,9 Leucócitos6550 Plaquetas172000 Sódio140 Potássio4,2 Uréia35 Creatinina0,75
+Conduta:
+- Mantida DAPT com AAS e clopidogrel
+- Se doppler MSD sem complicações, alta hospitalar com orientação de seguimento ambulatorial. Deixo orientações e receita.ALTA DIA 04/07 12:12</t>
+        </is>
+      </c>
       <c r="G78" s="9" t="n"/>
       <c r="H78" s="9" t="n"/>
       <c r="I78" s="9" t="n"/>
@@ -18196,8 +21281,14 @@
       <c r="N78" s="9" t="n"/>
       <c r="O78" s="9" t="n"/>
       <c r="P78" s="9" t="n"/>
-      <c r="Q78" s="9" t="n"/>
-      <c r="R78" s="9" t="n"/>
+      <c r="Q78" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="R78" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S78" s="10" t="n"/>
       <c r="T78" s="10" t="n"/>
       <c r="U78" s="10" t="n"/>
@@ -18210,7 +21301,11 @@
       <c r="AB78" s="10" t="n"/>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="10" t="n"/>
+      <c r="AE78" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF78" s="10" t="n"/>
       <c r="AG78" s="10" t="n"/>
       <c r="AH78" s="10" t="n"/>
@@ -18238,7 +21333,9 @@
       <c r="BD78" s="11" t="n"/>
       <c r="BE78" s="11" t="n"/>
       <c r="BF78" s="11" t="n"/>
-      <c r="BG78" s="11" t="n"/>
+      <c r="BG78" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="BH78" s="11" t="n"/>
       <c r="BI78" s="11" t="n"/>
       <c r="BJ78" s="11" t="n"/>
@@ -18365,7 +21462,62 @@
       <c r="E79" s="8" t="n">
         <v>39733</v>
       </c>
-      <c r="F79" s="8" t="n"/>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t># Atual: 
+- Tosse produtiva há cerca de 1 semana 
+-- Respmol com rinovirus positivo 
+# HMA: 
+- Paciente relata tosse produtiva com expectoração amarelada há pouco mais de 7 dias. Refere sensação de obstrução nasal, porém sem coriza ou rinorreia. Nega febre, nega odinofagia, nega mialgia, mesmo no inicio do quadro. 
+Nega dor torácica, nega palpitação, nega tontura ou pré-sincope. 
+Nega queixas gastrointestinais. Nega sintomas urinários. 
+# Antecedentes: 
+- Lesões de pele (passou com dermatologista, sugeriu vacina de HPV, "queimou" lesões)
+- Bronquiolite na infancia
+- Dislipidemia (Triglicérides elevados) 
+- Nega cirurgias ou internações
+- Nega COVID - vacinado
+- Nega alergias
+- Nega tabagismo (relata uso esporádico no inicio da adolescência)
+- Etilismo social (finais de semana) 
+- Sedentário atualmente 
+# Familiar: 
+- Pai DLP
+- Avó paterna DAC com ATC 70 anos
+- Avô paterno CA de prostata
+- Avô paterno DAC, Parkinson, HPN 
+- Primo Morte subita durante a formatura 
+# MUC: 
+Nega uso de medicações. 
+Nega uso de analogos de GLP-1
+Nega uso de vitaminas ou suplementos hormonais. 
+# Exames prévios:
+-- EcoTT 010/2025: FEVE 64, sem alterações 
+-- USG tireoide 01/2025: sem alterações
+-- TC de S. face 01/2025: Desvio de septo para E, Discreto espessamento da mucosa dos seios maxilares e de algumas células etmoidais, sem formação de nível líquido. Aumento da tonsila faríngea (adenoide). Discretas alterações degenerativas nos côndilos mandibulares.
+-- TC tórax 01/2025: Tênue opacidade focal em vidro fosco no lobo médio, inespecífica. Micronódulo não calcificado no lobo superior esquerdo medindo 0,4 cm, inespecífico.
+# Ao exame:
+- Geral: BEG, corado, hidratado, acianótico, anictérico 
+- Neuro: Consciente, orientado, sem déficits
+- Cardiovasc: RCR, bulhas NF em 2T sem sopros, TEC&lt;3s 
+- Resp: MV presente bilat sem RA. 
+- Abdome: semigloboso, normotenso, sem massas, sem VCM, RHA normais. 
+- Extremidades: sem edema, sem sinais de TVP 
+# Exames desta internação: 
+- Respmol: rinovirus positivo
+- TC tórax 29/06/26: broncopatia inflamatória
+- TC seios da face 29/06/26: aumento da adenoide, discreto espessamento mucosa
+- USG abdome 30/06/26: sem alterações
+- USG tireoide 30/06/26: sem alterações
+- USG MMII 30/06/26: sem alterações
+- USG carótidas 30/06/26: sem alterações 
+- ECOTT 30/06/26: fração de ejeção preservada, sem alterações 
+# Condutas:  
+- Inicio rocefin por broncopatia inflamatoria + sintomas
+- Suspendo teste ergométrico por infecção ativa 
+- Suporte clínico  ALTA DIA 01/07/2026 10:45</t>
+        </is>
+      </c>
       <c r="G79" s="9" t="n"/>
       <c r="H79" s="9" t="n"/>
       <c r="I79" s="9" t="n"/>
@@ -18376,16 +21528,30 @@
       <c r="N79" s="9" t="n"/>
       <c r="O79" s="9" t="n"/>
       <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="9" t="n"/>
-      <c r="R79" s="9" t="n"/>
-      <c r="S79" s="10" t="n"/>
+      <c r="Q79" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="R79" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="S79" s="10" t="inlineStr">
+        <is>
+          <t>BEG – Bom Estado Geral</t>
+        </is>
+      </c>
       <c r="T79" s="10" t="n"/>
       <c r="U79" s="10" t="n"/>
       <c r="V79" s="10" t="n"/>
       <c r="W79" s="10" t="n"/>
       <c r="X79" s="10" t="n"/>
       <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="10" t="n"/>
+      <c r="Z79" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
       <c r="AA79" s="10" t="n"/>
       <c r="AB79" s="10" t="n"/>
       <c r="AC79" s="10" t="n"/>
@@ -18725,7 +21891,41 @@
       <c r="E81" s="8" t="n">
         <v>39862</v>
       </c>
-      <c r="F81" s="8" t="n"/>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>HMA: Paciente dormiu por volta de 22:30-23:30 do dia 05/07/2026, assintomática. Despertou por volta das 08hs do dia 06/07/2026 com queixas vagas, de fraqueza no corpo todo e dificuldade de deambular, associada a diplopia e disartria. Veio direto ao PA para avaliação. Tem cirurgia cardíaca recente (21/05 troca valvar por prótese biológica e 28/05 colocação de MP). 
+AP: cirurgia de troca valvar biológica em 21/05, cirurgia de colocação de MO dia 28/05, HAS OP Hipotireoidismo Glaucoma
+- em uso de: Synthroid 50 mcg Cymbalta 60 mg Rosuvastatina 30 mg Metroprolol 25 mg Azorga colírio Suplemento Neovite
+EN inicial:
+- Vigil, consciente, orientada, sem déficit de linguagem, sem heminegligência.
+- Força aparentemente preservada nos membros, com velocidade de movimento preservada, sem queda nas manobras deficitárias, ROTs normoativos e simétricos, CP flexor bilateral
+- Sem alteração de sensibilidade superficial
+- Hemiataxia E (predominando em MIE)
+- Discreta assimetria pupilar (D&lt;E), com pouca diferença no claro e escuro, OIN à D, dúvida se alguma restrição do olhar conjugado para a D, paresia facial central E, disartria muito sutil
+NIH 3 (4.2 / 7.1)
+Evolução 12/07/2026 
+Paciente em poltrona, acompanhada de cuidadora. 
+Estável, sem intercorrências, refere melhora importante do quadro neurológico. 
+Apresenta também melhora do prurido. Sem novas queixas.  
+Exame neurológico 12/07 
+Consciente, orientada, melhora da fala 
+Sem deficits motores aparentes
+Ataxia com dismetria e decomposição a E (predomínio crural) mas tem em MID 
+Facial central E, OIN a D discreta 
+Complementares:
+- Labs 06/07: Cai 1,19 Cr 1,31 gaso V pH 7,39 pCO2 43 bic 26 Hb 11,1 leuco 7690 plaq 173000 VHS 59 lactato 11 Mg 2,0 K 3,5 PCR 3,44 Na 138 TGO 49 TGP 44 Tropo T 197 Ur 67 
+- TC protocolo AVC 06/07: sem sangramentos ASPECTS 9 perfusão core 0ml penumbra 0ml Alargamento difuso dos espaços liquóricos intracranianos inferindo redução volumétrica encefálica. Múltiplos focos hipoatenuantes na substância branca dos hemisférios cerebelares, confluentes ao redor dos ventrículos laterais, inespecíficos, mais comumente relacionadas a gliose / microangiopatia. Área focal de perda tecidual hipoatenuante córtico-subcortical na região do lóbulo parietal inferior à esquerda de aspecto vascular sequelar. Área focal hipoatenuante na cabeça do caudado esquerdo de datação indeterminada. Restante do parênquima encefálico de aspecto habitual. Calota craniana sem lesões focais. Achados adicionais: sinusopatia maxilar esquerda associado a material hiperatenuante / espesso / hiperproteico. Pequeno derrame pleural à esquerda. Sinais de manipulação cirúrgica torácica. 
+- AngioTC protocolo AVC 06/07: Irregularidades dos contornos associadas a extensas placas mistas predominantemente não calcificadas destacando-se ulcerações no arco aórtico. Placa mista na emergência da artéria subclávia direita determinando estenose acentuada focal. Pequena placas parietais calcificadas associadas a irregularidades dos contornos na emergência da artéria subclávia esquerda, determinando estenose leve. Restante do arco aórtico, tronco braquiocefálico e porções proximais das artérias subclávias com trajeto e calibre preservados. Placas parietais calcificadas nos bulbos carotídeos e segmentos intracranianos das artérias carótidas internas, inferindo ateromatose leve sem estenoses significativas. Restante das artérias carótidas comuns, internas e externas, vertebrais e basilar de calibre e contornos normais. Artérias cerebrais anteriores, médias e posteriores de calibre, trajeto e contornos preservados. Demais artérias intracranianas detectadas por esta técnica apresentando calibre, trajeto e contornos preservados. Ausência de estenoses hemodinamicamente significativas ou dilatações aneurismáticas.
+- TC cranio controle 11/07: estável inalterada em relação a de 09/07/26, sem hemorragias 
+- ECOTT 06/07: Presença de trombo intracardiaco 
+Impressão: AVCi cardoembólico embora tenha ateromatose difusa principalmente art subclavia à D. 
+Conduta: Discutida com Dra. Gisela Tinone
+- Alinhada alta hospitalar hoje, sem contraindicações pela Neurologia
+- Profilaxia novos eventos: Apixabana 2,5 mg 12/12h e Rosuvastatina 10 mg 
+- Faço relatório para fisioterapia motora - foco em equilíbrio e reabilitação de ataxia
+- Oriento sinais de alarme, uso de medicações. Programamos seguimento ambulatorial com retorno precoce.ALTA DIA 12/07/2026 9:55</t>
+        </is>
+      </c>
       <c r="G81" s="9" t="n"/>
       <c r="H81" s="9" t="n"/>
       <c r="I81" s="9" t="n"/>
@@ -18736,8 +21936,14 @@
       <c r="N81" s="9" t="n"/>
       <c r="O81" s="9" t="n"/>
       <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="9" t="n"/>
-      <c r="R81" s="9" t="n"/>
+      <c r="Q81" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="R81" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S81" s="10" t="n"/>
       <c r="T81" s="10" t="n"/>
       <c r="U81" s="10" t="n"/>
@@ -18745,8 +21951,16 @@
       <c r="W81" s="10" t="n"/>
       <c r="X81" s="10" t="n"/>
       <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="10" t="n"/>
-      <c r="AA81" s="10" t="n"/>
+      <c r="Z81" s="10" t="inlineStr">
+        <is>
+          <t>Orientado</t>
+        </is>
+      </c>
+      <c r="AA81" s="10" t="inlineStr">
+        <is>
+          <t>Deambulando</t>
+        </is>
+      </c>
       <c r="AB81" s="10" t="n"/>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -18778,9 +21992,13 @@
       <c r="BD81" s="11" t="n"/>
       <c r="BE81" s="11" t="n"/>
       <c r="BF81" s="11" t="n"/>
-      <c r="BG81" s="11" t="n"/>
+      <c r="BG81" s="11" t="n">
+        <v>1.31</v>
+      </c>
       <c r="BH81" s="11" t="n"/>
-      <c r="BI81" s="11" t="n"/>
+      <c r="BI81" s="11" t="n">
+        <v>7.39</v>
+      </c>
       <c r="BJ81" s="11" t="n"/>
       <c r="BK81" s="11" t="n"/>
       <c r="BL81" s="11" t="n"/>
@@ -29165,7 +32383,27 @@
       <c r="E139" s="8" t="n">
         <v>49207</v>
       </c>
-      <c r="F139" s="8" t="n"/>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+#Definido por internação
+Ertepenem empírico
+Sintomáticos
+Exames séricos, urina e culturas
+Reconciliação medicamentosa. Hoje melhor dos sintomas urinários. Sentada na poltrona, conversando normalmente
+PA bem controlada mCoração rítmico. FC um pouco mais elevada
+Pulmão OK sem roncos ou sibilos
+Evacuou normal e se alimenta bem
+Sem edemas mas MIE regiãso pré tibial com hiperemia maior do que anteriormente; Lesão em 2o artelho do pé E com inflamação importante
+Laboaratório de ontem sem repewrcussão sistêmica importante. Urina com mais de 1 milh~çao de leucócitos e nitrito positivo Aguarda cultura. Mantem-se clinicamente bem. melhora dos sintomas urinários
+PA controlada com a medicação habitual e Coração rítmico 
+Pulmão OK sem dispneia, em ar ambiente OK.
+Abd. evacuando, se alimenta bem
+Melhora da hiperemia na região tibial MIE após introdução da Teicoplanina
+Laboratório parâmetros de infecção/ inflamação est~so bem.
+Dificuldades com acesso para mnedicação e coleta de exames</t>
+        </is>
+      </c>
       <c r="G139" s="9" t="n"/>
       <c r="H139" s="9" t="n"/>
       <c r="I139" s="9" t="n"/>
@@ -29176,8 +32414,14 @@
       <c r="N139" s="9" t="n"/>
       <c r="O139" s="9" t="n"/>
       <c r="P139" s="9" t="n"/>
-      <c r="Q139" s="9" t="n"/>
-      <c r="R139" s="9" t="n"/>
+      <c r="Q139" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R139" s="9" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
       <c r="S139" s="10" t="n"/>
       <c r="T139" s="10" t="n"/>
       <c r="U139" s="10" t="n"/>
@@ -29190,9 +32434,17 @@
       <c r="AB139" s="10" t="n"/>
       <c r="AC139" s="10" t="n"/>
       <c r="AD139" s="10" t="n"/>
-      <c r="AE139" s="10" t="n"/>
+      <c r="AE139" s="10" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="AF139" s="10" t="n"/>
-      <c r="AG139" s="10" t="n"/>
+      <c r="AG139" s="10" t="inlineStr">
+        <is>
+          <t>Ar ambiente</t>
+        </is>
+      </c>
       <c r="AH139" s="10" t="n"/>
       <c r="AI139" s="10" t="n"/>
       <c r="AJ139" s="10" t="n"/>
